--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -542,10 +544,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history built and checked 2026-10-22.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name built and checked 2026-10-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -558,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -570,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -577,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -632,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -682,6 +689,62 @@
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 3 -- Preferred name</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>models/auth.py, routers/auth.py, shared/names.py, routers/desk.py, routers/brief.py, components/ProfileDialog.js, lib/names.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Every greeting takes the first word of the full name, so 'S Rhea' is greeted 'S' - and initial-first names are the normal way to write a name in Tamil Nadu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>docs/PREFERRED_NAME_PLAN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -698,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +790,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 23 of 27 items Done  (85%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (2026-10-22).</t>
+          <t>Epic 11 progress: 28 of 32 items Done  (88%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (built 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -831,6 +894,39 @@
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Client FEATURE-08: read notifications stay reachable. New and History on the Notifications page, Notification history under Settings -&gt; Account, the list pages back past the newest 100, true counts, Move back to New; the bell's always-0 'need you' badge fixed. Plan: docs/NOTIFICATION_HISTORY_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Preferred name</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Client FEATURE-03: a Preferred name in the profile, used by the greetings ('Good afternoon, Rhea', not 'S'); people who never set one are greeted by the first word of their name that is not an initial. Plan: docs/PREFERRED_NAME_PLAN.md.</t>
         </is>
       </c>
     </row>
@@ -845,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2436,6 +2532,286 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NF-3.1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>models/auth.py ProfileUpdateInput, routers/auth.py update_profile</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Preferred name on the profile</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>preferred_name on the user (each company's record, like the name): set from PATCH /api/auth/profile, trimmed, max 40, blank clears; /auth/me returns it.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Client FEATURE-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NF-3.2</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>shared/names.py; routers/desk.py, routers/brief.py, services/ai/brain_rbac.py</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Greeting</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>One greeting-name rule</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Preferred name if set, else the first word of the name that is not an initial ('S Rhea' -&gt; Rhea, 'K. Ramesh' -&gt; Ramesh), else 'there'. Desk greeting, phone brief greeting, Dex's messages.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md Also skips a title (Mr, Mrs, Ms, Dr, Prof, Er, Smt) and two-or-three capitals before another word; 'S.Rhea' counts as 'S. Rhea'.</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Client FEATURE-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NF-3.3</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>components/ProfileDialog.js ProfileForm (Settings -&gt; Your profile)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Preferred name field with a live preview</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Under the name: 'We'll greet you as: Good afternoon, Rhea'. Owner and member views.</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Client FEATURE-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NF-3.4</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>lib/names.js; pages/Brain.js DexWelcome, pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Greeting</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>The same rule on the screen side</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>The Dex welcome and the Ops 'Hi ...' line use it.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Client FEATURE-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NF-3.5</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>tests/, browser (scratch DB)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Tests and a browser check</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>The rule (initials, dotted initials, preferred name wins, blank clears), the profile save, the Desk greeting; browser: set 'Rhea', Desk says Good ..., Rhea.</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md tests/test_preferred_name.py: 23 tests incl. a guard that the screen-side rule matches the server's. Browser (scratch DB, 'S Rhea'): Desk 'Good morning, Rhea.' with nothing set; preferred 'Riya' -&gt; Desk, Dex welcome and Ops all say Riya; preview updates as you type.</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Client FEATURE-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -507,7 +506,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 (Requests). Founder 2026-10-22: every new feature the client asks for is a sprint of this epic.</t>
+          <t>2026-10-21 (Requests). Founder 2026-10-22: every new feature the client asks for is a sprint of this epic, and the substantial bugs fixed along the way are Sprint 4 - Bugs.</t>
         </is>
       </c>
     </row>
@@ -519,7 +518,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Client feature requests: the Requests plan (Requests_Feature_Plan.png, decisions 2026-10-21) and FEATURE-08 Notification history (2026-10-22).</t>
+          <t>Client feature requests: the Requests plan (Requests_Feature_Plan.png, decisions 2026-10-21), FEATURE-08 Notification history and FEATURE-03 Preferred name (2026-10-22), Finance delete (2026-10-22); bugs from the client's Play Store build and the XCODITS QA report (2026-10-21).</t>
         </is>
       </c>
     </row>
@@ -535,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -544,11 +542,10 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name built and checked 2026-10-22.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141).</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -561,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -574,7 +570,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -582,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -638,7 +632,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -694,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -745,6 +737,116 @@
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4 -- Bugs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>routers/desk.py, routers/tasks.py, hooks/useUiScale.js, services/ingestion.py, pages/Captures.js, components/mobile/Walkthrough.jsx, lib/native/files.js, services/finance_trash.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>The substantial bugs fixed along the way: the client's four from the Play Store build, the XCODITS QA bugs, App Store 5.1.2 AI consent, the old Finance delete getting the books wrong, and files that would not save inside the app. Open: WhatsApp gave no reply to a PDF on 2026-10-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>XCODITS QA report 2026-10-21 (BUG-16, BUG-04, BUG-14, ACCESS-12, BUG-15); client fixes 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>In progress -- 12 of 13 Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 5 -- Finance delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_trash.py, routers/finance_trash.py, pages/finance/FinanceDelete.jsx, components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, pages/Captures.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>The client imported wrong records from Tally and could not take them out. One delete for every door that asks first, says what goes with it, keeps issued GST invoices, and can be put back for 30 days; Undo this import; select and delete; delete everything (owner, after a copy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>docs/FINANCE_DELETE_PLAN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -761,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -783,14 +885,14 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Features the client asks for, one sprint each: plan, build, test and ship the feature as a unit.</t>
+          <t>Features the client asks for, one sprint each: plan, build, test and ship the feature as a unit. Sprint 4 collects the substantial bugs fixed along the way.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 28 of 32 items Done  (88%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (built 2026-10-22).</t>
+          <t>Epic 11 progress: 48 of 53 items Done  (91%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141).</t>
         </is>
       </c>
     </row>
@@ -927,6 +1029,72 @@
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Client FEATURE-03: a Preferred name in the profile, used by the greetings ('Good afternoon, Rhea', not 'S'); people who never set one are greeted by the first word of their name that is not an initial. Plan: docs/PREFERRED_NAME_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Bugs</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Substantial bugs fixed along the way: the client's four fixes from the Play Store build (Delayed vs Overdue, people on a task, the Workflows tile, phone scale with a bigger font), the XCODITS QA bugs (BUG-16, BUG-04, BUG-14, ACCESS-12, BUG-15), App Store 5.1.2 AI consent, the old Finance delete, files saving inside the app. Open: WhatsApp gave no reply to a PDF (2026-10-22).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Finance delete</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Client: a wrong Tally import and no way to delete it. One delete for every door - one record, a selection, an import undone, everything - that asks first, says what goes with it, keeps issued GST invoices, and can be put back for 30 days. Plan: docs/FINANCE_DELETE_PLAN.md.</t>
         </is>
       </c>
     </row>
@@ -941,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2075,7 +2243,7 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Was NH-1.1 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Was NH-1.1 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2131,7 +2299,7 @@
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Also fixed: the bell's 'need you' badge tested a `kind` field no notification carries, so it was always 0; the server counts the asks now (services/notifications.NEEDS_YOU_TYPES). Was NH-1.2 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Also fixed: the bell's 'need you' badge tested a `kind` field no notification carries, so it was always 0; the server counts the asks now (services/notifications.NEEDS_YOU_TYPES). Was NH-1.2 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2187,7 +2355,7 @@
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Was NH-1.3 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Was NH-1.3 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -2243,7 +2411,7 @@
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Was NH-1.4 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Was NH-1.4 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2299,7 +2467,7 @@
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md tests/test_notification_history.py: 8 tests. Was NH-1.5 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md tests/test_notification_history.py: 8 tests. Was NH-1.5 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2355,7 +2523,7 @@
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Was NH-2.1 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Was NH-2.1 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2411,7 +2579,7 @@
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Opens on the latest five with Show more, so the sections below stay in reach; links to Notifications. Was NH-2.2 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Opens on the latest five with Show more, so the sections below stay in reach; links to Notifications. Was NH-2.2 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2467,7 +2635,7 @@
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Was NH-2.3 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Was NH-2.3 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2523,7 +2691,7 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/NOTIFICATION_HISTORY_PLAN.md Checked as Priya on the scratch DB: badge 3 need you / 24 new; read -&gt; History with Undo; History paged to the oldest (36); Move back to New; Settings section; phone width. Was NH-2.4 (briefly Epic 12).</t>
+          <t>Done 2026-10-22 - 46bb6a0. docs/NOTIFICATION_HISTORY_PLAN.md Checked as Priya on the scratch DB: badge 3 need you / 24 new; read -&gt; History with Undo; History paged to the oldest (36); Move back to New; Settings section; phone width. Was NH-2.4 (briefly Epic 12).</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2579,7 +2747,7 @@
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md</t>
+          <t>Done 2026-10-22 - 6c9bdf1. docs/PREFERRED_NAME_PLAN.md</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2635,7 +2803,7 @@
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md Also skips a title (Mr, Mrs, Ms, Dr, Prof, Er, Smt) and two-or-three capitals before another word; 'S.Rhea' counts as 'S. Rhea'.</t>
+          <t>Done 2026-10-22 - 6c9bdf1. docs/PREFERRED_NAME_PLAN.md Also skips a title (Mr, Mrs, Ms, Dr, Prof, Er, Smt) and two-or-three capitals before another word; 'S.Rhea' counts as 'S. Rhea'.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2691,7 +2859,7 @@
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md</t>
+          <t>Done 2026-10-22 - 6c9bdf1. docs/PREFERRED_NAME_PLAN.md</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2747,7 +2915,7 @@
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md</t>
+          <t>Done 2026-10-22 - 6c9bdf1. docs/PREFERRED_NAME_PLAN.md</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2803,12 +2971,1258 @@
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/PREFERRED_NAME_PLAN.md tests/test_preferred_name.py: 23 tests incl. a guard that the screen-side rule matches the server's. Browser (scratch DB, 'S Rhea'): Desk 'Good morning, Rhea.' with nothing set; preferred 'Riya' -&gt; Desk, Dex welcome and Ops all say Riya; preview updates as you type.</t>
+          <t>Done 2026-10-22 - 6c9bdf1. docs/PREFERRED_NAME_PLAN.md tests/test_preferred_name.py: 23 tests incl. a guard that the screen-side rule matches the server's. Browser (scratch DB, 'S Rhea'): Desk 'Good morning, Rhea.' with nothing set; preferred 'Riya' -&gt; Desk, Dex welcome and Ops all say Riya; preview updates as you type.</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>Client FEATURE-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>routers/desk.py _delayed_count, routers/tasks.py list_tasks, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Desk / My Work</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Delayed tile opens the same list it counts</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Client, on the Play Store build: Desk said Delayed 18 and the Overdue list it opened was empty. The task list returned only the newest tasks, so on a company with hundreds finished the late ones fell off. The list now returns every open task plus the newest 500 finished, and the tile counts with the list's own query, in IST days.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc (client Fix 1).</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.2</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>services/tasks.py, lib/taskAccess.js, pages/MyWork.js, pages/Tasks.js</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Any number of people on a task, and Everyone</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>A task held at most 10 helpers. No cap now, and the people picker starts with Everyone (N) once there are two or more.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc (client Fix 2).</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.3</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>pages/desk/WorkflowsTile.jsx, pages/Workflows.js, index.css</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Desk / Workflows</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Workflows tile: no Approve, one Open in Workflows</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Approve left the tile (approving belongs on the card). One full-width Open in Workflows opens the board on the card's stage with the card glowing; picking another board no longer jumps back.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc (client Fix 3).</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.4</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>hooks/useUiScale.js, android MainActivity.java</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Phone scale on OnePlus / OPPO / Realme (OxygenOS, ColorOS 16)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>With the system font size above normal, the web view zoomed the text twice and the Desk broke (tiles cut off). useUiScale measures type and boxes separately; the fallback viewport sets setUseWideViewPort. Checked on a OnePlus 13s and the emulator.</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc (client Fix 4).</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.5</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>services/ingestion.py upload_scope, routers/finance.py, pages/Captures.js, pages/finance/ReviewPanel.js</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Finance / Inbox</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BUG-16: uploaded bills appear in Pending and Filed</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>A bill read but not filed waited nowhere, and one filed was never seen again by someone without Finance. Pending and Filed list uploads (the owner and Finance: the company's; others: their own), Discard works, and the toast says where the record went.</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc.</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>XCODITS QA 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.6</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>routers/tasks.py, services/recurrence.py, services/task_timing.py, pages/MyWork.js, bootstrap/lifecycle.py</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>BUG-04: how late a task was stays after it closes</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Closing from the checklist did not stamp the completion, so the lateness was lost. Overdue shows 'Overdue - N days', finished shows 'Finished N days late' or 'on time', a finished task's due date is locked until reopened, and a recurring task's next one is due today, not in the past. Migration task_completed_at_v2 backfills.</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc.</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>XCODITS QA 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.7</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>android AndroidManifest.xml, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>BUG-14: camera buttons open the camera</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>On Android 11 and later the camera intent was invisible to the app (no &lt;queries&gt;), so Photo opened the gallery; picking the same photo twice did nothing.</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc.</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>XCODITS QA 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.8</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/Walkthrough.jsx</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>ACCESS-12: the walkthrough teaches only what you can do</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>It taught Decide and the books to people without them. The steps follow the person's role and permissions.</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - e46b7cc.</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>XCODITS QA 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.9</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>pages/Ledger.js</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>BUG-15: the Money 'index box' button</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>An unlabelled tray icon on the phone's Quick capture card that did nothing on the Inbox. Gone (the Inbox tab carries the count), and a one-cell tab bar is no longer drawn.</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e46b7cc, e352141.</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>XCODITS QA 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.10</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>MicDictateButton.js, useDexCapture.js, lib/aiConsent.js, pages/Settings.js</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>AI / App Store</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>App Store 5.1.2: AI consent asked first, every provider named</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Dex sent voice and text to AI providers before asking. It asks first, and names each provider.</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 - c6182c3.</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>App Store review</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.11</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>routers/ledger.py deletes -&gt; services/finance_trash.py</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Deleting in Finance got the books wrong</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>A deleted payment left its invoice 'received'; a deleted invoice deleted a payment split across other invoices; a deleted expense left its bill in Bills to pay and its asset behind; one tap deleted with no question, no undo and no record; deleting the latest issued invoice reissued its number; Dex kept quoting deleted records. Fixed by Sprint 5's one delete.</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.12</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>lib/native/files.js; MoneyActions, BrainDocuments, DexAnswer, Captures, RequestCard, MyWork, financeKit, ReviewPanel</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Files save inside the Android and iOS apps</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>The app's web view has no download handler: invoice PDF, Brain document and Dex export buttons did nothing, and links to bills and attachments opened a browser that was not signed in. In the app a file now goes to the share sheet (save to Files or Drive, or send on WhatsApp or mail); the web is unchanged. @capacitor/filesystem 8.1.4, @capacitor/share 8.0.3.</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141. Checked on the Android emulator; iOS has the plugins, not yet run on a device.</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Found 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>NF-4.13</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>services/whatsapp.py, integrations/whatsapp.py, routers/whatsapp.py</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>A PDF sent on WhatsApp got no reply</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22: the client's PDF got no 'Received' reply. No inbound WhatsApp code changed since 8 Oct, so likely an expired Meta token, the sender not routed to a workspace (pending member, number in two workspaces), or the webhook not delivered. A reply Meta refuses is never logged today. Next: a read-only look at production wa_events for that number, then log Meta's refusals on each event.</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>Investigated 2026-10-22 in code; waiting on the production check.</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>One delete for every door</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.2</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Every delete asks first, and has Undo</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.3</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Select and delete on every list</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.2</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.4</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Finance / Inbox</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Undo this import</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.5</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Recently deleted, for 30 days</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.6</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>routers/finance_trash.py everything / export</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Delete all Finance records (owner)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.7</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Finance / GST</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.8</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Tests and checks</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 - e352141.</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -542,10 +544,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141).</t>
-        </is>
-      </c>
-    </row>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -558,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -570,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -577,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -632,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -687,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -742,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -797,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -849,6 +859,61 @@
       <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 6 -- Admin console redesign</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/* (AdminPortal shell, adminUi.jsx, adminLabels.js, WorkspacePage.js, AdminInvite.js), routers/admin_overview.py, routers/admin_invites.py, services/admin_workspaces.py, services/admin_invites.py, routers/admin.py, routers/admin_rbac.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>17 tabs in one row with no addresses, a workspace spread over four screens, an Overview of raw counts, test companies inside every total, destructive buttons on every row, passwords typed for other admins, and a 2FA sign-in that never finished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>docs/ADMIN_UI_REDESIGN_PLAN.md (screenshots before/after in docs/admin-ui-audit/, not committed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>In progress -- 18 of 20 Done</t>
         </is>
       </c>
     </row>
@@ -863,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +957,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 48 of 53 items Done  (91%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141).</t>
+          <t>Epic 11 progress: 66 of 73 items Done  (90%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open).</t>
         </is>
       </c>
     </row>
@@ -1095,6 +1160,39 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Client: a wrong Tally import and no way to delete it. One delete for every door - one record, a selection, an import undone, everything - that asks first, says what goes with it, keeps issued GST invoices, and can be put back for 30 days. Plan: docs/FINANCE_DELETE_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Admin console redesign</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>The platform admin console redone end to end: grouped sidebar with addresses, Find, one workspace page, an Overview that says what needs you, rupees, test workspaces hidden, reasons in the audit log, admin invites, 2FA fixed. Two follow-ups open (view-as that opens the workspace; 2FA required for super admins). Plan: docs/ADMIN_UI_REDESIGN_PLAN.md.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4226,6 +4324,1126 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.1</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminPortal.js</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Grouped sidebar with an address for every place</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.2</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Find (Ctrl K)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.3</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminPortal.js</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>One-line provider alert and counts on the sidebar</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.4</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>The app's own design language, finished</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.5</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Phone width</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.6</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Test workspaces told apart, and hidden by default</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.7</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Workspaces list</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.8</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>One workspace page</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.9</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminSections.js UsersSection</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Users directory</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.10</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>An Overview that leads with what needs an operator</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.11</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Health with Observability; Audit log with view-as sessions</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.12</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>AI cost in rupees</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.13</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.14</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Admin invite links</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.15</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Sign-in and two-step sign-in fixed</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.16</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/*</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Each admin sees only what they can do</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.17</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>The rest of the sections redone</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.18</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Tests and a browser check</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.19</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>View as actually opens the workspace</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Found during the redesign 2026-10-22; not started.</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.20</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin.py login, AdminPortal.js</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Require two-step sign-in for super admins</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Found during the redesign 2026-10-22; not started.</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -535,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -544,11 +542,10 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations built 2026-10-23; P2-P5 planned.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -561,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -574,7 +570,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -582,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -638,7 +632,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -694,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -750,7 +742,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -806,7 +797,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -914,6 +904,61 @@
       <c r="B50" s="4" t="inlineStr">
         <is>
           <t>In progress -- 18 of 20 Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 7 -- Admin console v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>services/presence.py, services/rollups.py, services/lifecycle.py, services/milestones.py, routers/admin_analytics.py, routers/auth_otp.py, routers/auth.py, core/deps.py, workers/schedulers.py, pages/admin/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>The console could show a customer but not whether they are healthy, slipping or reaching value: the main sign-in was not recorded, there was no daily history, plan changes overwrote each other, and retention can purge what trends need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>In progress -- P1 done (8 of 13)</t>
         </is>
       </c>
     </row>
@@ -928,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -957,7 +1002,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 66 of 73 items Done  (90%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open).</t>
+          <t>Epic 11 progress: 74 of 86 items Done  (86%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 built).</t>
         </is>
       </c>
     </row>
@@ -1193,6 +1238,39 @@
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>The platform admin console redone end to end: grouped sidebar with addresses, Find, one workspace page, an Overview that says what needs you, rupees, test workspaces hidden, reasons in the audit log, admin invites, 2FA fixed. Two follow-ups open (view-as that opens the workspace; 2FA required for super admins). Plan: docs/ADMIN_UI_REDESIGN_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Admin console v2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>The console that runs the business: P1 data foundations (sign-ins incl. phone code, daily presence, a daily count per workspace kept for good, lifecycle events, milestones and activation) built; P2 customers, P3 analytics, P4 support depth, P5 polish planned. Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5444,6 +5522,734 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.1</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Sign-in and last seen, phone code included</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.2</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>services/presence.py presence_days</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Who was here each day, kept for good</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.3</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Daily count per workspace, kept for good</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.4</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Backfill from what still exists</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="n"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.5</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Lifecycle events</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.6</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>services/milestones.py; core/__init__.log_activity</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>First-value milestones and activation</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.7</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>The console shows the foundations</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.8</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Tests and a scratch check</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.9</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Customers list, health score, stages</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>P2 Customers</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Health score, stage and the customer list</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.10</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Customer page tabs; notes, tags, owner</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>P2 Customers</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Customer page in tabs, with timeline and notes</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.11</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>P3 Analytics</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Analytics pages and Home</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.12</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Outbound message log, ticket SLA, NPS</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>P4 Support</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Support depth</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="n"/>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.13</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Density, dark mode, detail drawer</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>P5 Polish</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="n"/>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -542,10 +544,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations built 2026-10-23; P2-P5 planned.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers built 2026-10-23; P3-P5 planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -558,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -570,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -577,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -632,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -687,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -742,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -797,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -852,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
@@ -907,6 +918,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
@@ -958,7 +970,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>In progress -- P1 done (8 of 13)</t>
+          <t>In progress -- P1 pushed (1ea398d), P2 built (10 of 13)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1014,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 74 of 86 items Done  (86%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 built).</t>
+          <t>Epic 11 progress: 76 of 86 items Done  (88%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 built).</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1265,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5569,7 +5581,7 @@
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -5625,7 +5637,7 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -5681,7 +5693,7 @@
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -5737,7 +5749,7 @@
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -5793,7 +5805,7 @@
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -5849,7 +5861,7 @@
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -5905,7 +5917,7 @@
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -5961,7 +5973,7 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -6011,13 +6023,13 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23 (awaiting push). services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -6067,13 +6079,13 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23 (awaiting push). Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers built 2026-10-23; P3-P5 planned.</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics built 2026-10-23; P4-P5 planned.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>In progress -- P1 pushed (1ea398d), P2 built (10 of 13)</t>
+          <t>In progress -- P1 1ea398d, P2 a6a8215, P3 built (11 of 13)</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 76 of 86 items Done  (88%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 built).</t>
+          <t>Epic 11 progress: 77 of 86 items Done  (90%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 built).</t>
         </is>
       </c>
     </row>
@@ -1265,14 +1265,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6029,7 +6029,7 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -6085,7 +6085,7 @@
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -6135,13 +6135,13 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23 (awaiting push). services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics built 2026-10-23; P4-P5 planned.</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish built 2026-10-23.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>In progress -- P1 1ea398d, P2 a6a8215, P3 built (11 of 13)</t>
+          <t>Built -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built (13 of 13)</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 77 of 86 items Done  (90%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 built).</t>
+          <t>Epic 11 progress: 79 of 86 items Done  (92%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built).</t>
         </is>
       </c>
     </row>
@@ -1265,14 +1265,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6141,7 +6141,7 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6191,13 +6191,13 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23 (awaiting push). core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -6247,13 +6247,13 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Planned 2026-10-23 (founder: go with the recommendations). docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-23 (awaiting push). adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141).</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish built 2026-10-23.</t>
         </is>
       </c>
     </row>
@@ -849,6 +849,177 @@
       <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 6 -- Admin console redesign</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/* (AdminPortal shell, adminUi.jsx, adminLabels.js, WorkspacePage.js, AdminInvite.js), routers/admin_overview.py, routers/admin_invites.py, services/admin_workspaces.py, services/admin_invites.py, routers/admin.py, routers/admin_rbac.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>17 tabs in one row with no addresses, a workspace spread over four screens, an Overview of raw counts, test companies inside every total, destructive buttons on every row, passwords typed for other admins, and a 2FA sign-in that never finished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>docs/ADMIN_UI_REDESIGN_PLAN.md (screenshots before/after in docs/admin-ui-audit/, not committed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>In progress -- 18 of 20 Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 7 -- Admin console v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>services/presence.py, services/rollups.py, services/lifecycle.py, services/milestones.py, routers/admin_analytics.py, routers/auth_otp.py, routers/auth.py, core/deps.py, workers/schedulers.py, pages/admin/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>The console could show a customer but not whether they are healthy, slipping or reaching value: the main sign-in was not recorded, there was no daily history, plan changes overwrote each other, and retention can purge what trends need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Built -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built (13 of 13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sprint 8 -- Phone redesign</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js, pages/mywork/* (WorkDeck, TaskActionSlider, TaskNotes), pages/desk/* (DexReview, DexCapturePopup, FinishedWorkCard, DeskDexWell, WorkflowsTile), pages/onboarding/DexBuilder.jsx, components/mobile/* (Affirmation, DexWave, DockSlider, dockChoice), components/neuglass/DexSlider.jsx, components/requests/*, components/settings/DockCard.jsx, components/DecisionDialog.js, components/ui/dialog.jsx + alert-dialog.jsx, hooks/useDexCapture.js, index.css; services/auto_plan.py, services/decision_flow.py, services/voice.py, routers/tasks.py, routers/decisions.py, models/decisions.py + tasks.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>The founder's reference screens for My Work, Requests and Dex Decide, and the pilot client's ask that the owner hears when work is finished; plus the phone-wide polish found on the way (toasts, pop-ups, the wave, the dock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Founder messages and reference screens, 2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Done -- 20 of 20 (3ecf7bf + the 2026-10-29 push)</t>
         </is>
       </c>
     </row>
@@ -863,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +1063,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 48 of 53 items Done  (91%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141).</t>
+          <t>Epic 11 progress: 99 of 106 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push).</t>
         </is>
       </c>
     </row>
@@ -1095,6 +1266,105 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Client: a wrong Tally import and no way to delete it. One delete for every door - one record, a selection, an import undone, everything - that asks first, says what goes with it, keeps issued GST invoices, and can be put back for 30 days. Plan: docs/FINANCE_DELETE_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Admin console redesign</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>The platform admin console redone end to end: grouped sidebar with addresses, Find, one workspace page, an Overview that says what needs you, rupees, test workspaces hidden, reasons in the audit log, admin invites, 2FA fixed. Two follow-ups open (view-as that opens the workspace; 2FA required for super admins). Plan: docs/ADMIN_UI_REDESIGN_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Admin console v2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>The console that runs the business: P1 data foundations (sign-ins incl. phone code, daily presence, a daily count per workspace kept for good, lifecycle events, milestones and activation) built; P2 customers, P3 analytics, P4 support depth, P5 polish planned. Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Phone redesign</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>The phone app redone for the founder and the pilot client: My Work (tiles, bands, cards, the full-screen task with a slider foot and Notes), Dex drafting every checklist by itself, request cards, Dex Decide (reading checklist under Dex as a figure, the three-screen review, also from the Desk), the voice wave and pause, full-screen confirmations for every toast, pop-ups in place, your own dock, the owner told when work is finished. Plan: the founder's reference screens, 2026-10-29.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4226,6 +4496,2974 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.1</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminPortal.js</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Grouped sidebar with an address for every place</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.2</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Find (Ctrl K)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.3</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminPortal.js</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>One-line provider alert and counts on the sidebar</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.4</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>The app's own design language, finished</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.5</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Phone width</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.6</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Test workspaces told apart, and hidden by default</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.7</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Workspaces list</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.8</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>One workspace page</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.9</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminSections.js UsersSection</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Users directory</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.10</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>An Overview that leads with what needs an operator</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.11</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Health with Observability; Audit log with view-as sessions</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.12</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>AI cost in rupees</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.13</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.14</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Admin invite links</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.15</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Sign-in and two-step sign-in fixed</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.16</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>pages/admin/*</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Each admin sees only what they can do</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.17</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>The rest of the sections redone</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.18</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Tests and a browser check</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.19</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>View as actually opens the workspace</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Found during the redesign 2026-10-22; not started.</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>NF-6.20</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>routers/admin.py login, AdminPortal.js</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Require two-step sign-in for super admins</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Found during the redesign 2026-10-22; not started.</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.1</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Sign-in and last seen, phone code included</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.2</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>services/presence.py presence_days</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Who was here each day, kept for good</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.3</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Daily count per workspace, kept for good</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.4</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Backfill from what still exists</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="n"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.5</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Lifecycle events</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.6</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>services/milestones.py; core/__init__.log_activity</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>First-value milestones and activation</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.7</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>P1 Data</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>The console shows the foundations</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.8</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Tests and a scratch check</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.9</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Customers list, health score, stages</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>P2 Customers</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Health score, stage and the customer list</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.10</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Customer page tabs; notes, tags, owner</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>P2 Customers</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Customer page in tabs, with timeline and notes</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.11</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>P3 Analytics</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Analytics pages and Home</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.12</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Outbound message log, ticket SLA, NPS</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>P4 Support</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Support depth</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="n"/>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>NF-7.13</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Density, dark mode, detail drawer</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>P5 Polish</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="n"/>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-23 (awaiting push). adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-23 (admin console v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.1</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="n"/>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.2</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (mobileTaskView)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.3</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>My Work / Dex</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Dex drafts every task's checklist by itself</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.4</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>A request card that says where it stands</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="n"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.5</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Plan prices read Coming soon</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="n"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.6</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/DexWave.jsx</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.7</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Pause and carry on while speaking</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.8</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.9</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.10</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>components/DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Desk decisions open in the new review on the phone</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.11</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Phone-wide</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Every toast is full screen on the phone</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="n"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.12</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Phone-wide</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Pop-ups open in place</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="n"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.13</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Phone-wide</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>The Ask panel see-through; the page blurs behind More</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.14</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Preferences</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Your dock: choose its three places</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="n"/>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.15</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Blue buttons are the app's ink</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.16</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.17</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Client feedback</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>The owner hears when work is finished</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.18</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>routers/tasks.py (save_execution_plan)</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>A checklist never moves a task to Doing</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.19</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>The card's steps: a row of numbers above Next action</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.20</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>index.css (sky)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>No amber glow; Notifications wears Finance's sky</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -535,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -548,7 +546,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -561,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -574,7 +570,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -582,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -638,7 +632,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -694,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -750,7 +742,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -806,7 +797,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -862,7 +852,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
@@ -971,6 +960,66 @@
       <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Built -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built (13 of 13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sprint 8 -- Phone redesign</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js, pages/mywork/* (WorkDeck, TaskActionSlider, TaskNotes), pages/desk/* (DexReview, DexCapturePopup, FinishedWorkCard, DeskDexWell, WorkflowsTile), pages/onboarding/DexBuilder.jsx, components/mobile/* (Affirmation, DexWave, DockSlider, dockChoice), components/neuglass/DexSlider.jsx, components/requests/*, components/settings/DockCard.jsx, components/DecisionDialog.js, components/ui/dialog.jsx + alert-dialog.jsx, hooks/useDexCapture.js, index.css; services/auto_plan.py, services/decision_flow.py, services/voice.py, routers/tasks.py, routers/decisions.py, models/decisions.py + tasks.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>The founder's reference screens for My Work, Requests and Dex Decide, and the pilot client's ask that the owner hears when work is finished; plus the phone-wide polish found on the way (toasts, pop-ups, the wave, the dock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Founder messages and reference screens, 2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Done -- 20 of 20 (3ecf7bf + the 2026-10-29 push)</t>
         </is>
       </c>
     </row>
@@ -985,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1014,7 +1063,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 79 of 86 items Done  (92%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built).</t>
+          <t>Epic 11 progress: 99 of 106 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push).</t>
         </is>
       </c>
     </row>
@@ -1283,6 +1332,39 @@
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>The console that runs the business: P1 data foundations (sign-ins incl. phone code, daily presence, a daily count per workspace kept for good, lifecycle events, milestones and activation) built; P2 customers, P3 analytics, P4 support depth, P5 polish planned. Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Phone redesign</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>The phone app redone for the founder and the pilot client: My Work (tiles, bands, cards, the full-screen task with a slider foot and Notes), Dex drafting every checklist by itself, request cards, Dex Decide (reading checklist under Dex as a figure, the three-screen review, also from the Desk), the voice wave and pause, full-screen confirmations for every toast, pop-ups in place, your own dock, the owner told when work is finished. Plan: the founder's reference screens, 2026-10-29.</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6262,6 +6344,1126 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.1</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="n"/>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.2</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (mobileTaskView)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.3</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>My Work / Dex</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Dex drafts every task's checklist by itself</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.4</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>A request card that says where it stands</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="n"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.5</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Plan prices read Coming soon</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="n"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.6</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/DexWave.jsx</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.7</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Pause and carry on while speaking</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.8</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.9</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.10</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>components/DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Desk decisions open in the new review on the phone</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.11</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Phone-wide</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Every toast is full screen on the phone</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="n"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.12</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Phone-wide</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Pop-ups open in place</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="n"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.13</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Phone-wide</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>The Ask panel see-through; the page blurs behind More</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.14</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Preferences</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Your dock: choose its three places</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="n"/>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.15</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Blue buttons are the app's ink</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.16</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.17</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Client feedback</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>The owner hears when work is finished</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.18</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>routers/tasks.py (save_execution_plan)</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>A checklist never moves a task to Doing</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.19</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>The card's steps: a row of numbers above Next action</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.20</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>index.css (sky)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>No amber glow; Notifications wears Finance's sky</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -542,10 +544,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish built 2026-10-23.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 13 of 14 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods (feature) built 2026-10-29: Finance follows the financial year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -558,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -570,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -577,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -632,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -687,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -742,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -793,10 +802,11 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 12 of 13 Done</t>
-        </is>
-      </c>
-    </row>
+          <t>In progress -- 13 of 14 Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -852,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
@@ -959,7 +970,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Built -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built (13 of 13)</t>
+          <t>Done -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335 (13 of 13)</t>
         </is>
       </c>
     </row>
@@ -973,7 +984,6 @@
           <t>Sprint 8 -- Phone redesign</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -1020,6 +1030,61 @@
       <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Done -- 20 of 20 (3ecf7bf + the 2026-10-29 push)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 9 -- Finance periods</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/ledgerMath.js, pages/finance/PeriodPicker.jsx, pages/Ledger.js, pages/finance/FinanceOverview.jsx, components/CompanyDetails.js, models/tenant.py, routers/tenant_settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Client: records added in Finance were 'not reflecting' in Revenue, Received or Profit. They were saved - the Overview defaulted to the last 30 days and counts a record by its own date. Businesses work in financial years, halves and quarters: the Overview now opens on the financial year, any quarter or half of any year can be picked, the year's start month is a setting, and it rolls over by itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Done -- 5 of 5 (feature)</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1063,7 +1128,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 99 of 106 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push).</t>
+          <t>Epic 11 progress: 105 of 112 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods (feature).</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1280,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1326,12 +1391,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>The console that runs the business: P1 data foundations (sign-ins incl. phone code, daily presence, a daily count per workspace kept for good, lifecycle events, milestones and activation) built; P2 customers, P3 analytics, P4 support depth, P5 polish planned. Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
+          <t>The console that runs the business: P1 data foundations (1ea398d), P2 customers (a6a8215), P3 analytics (cf8da32), P4 support depth and P5 polish (47e0335). Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
         </is>
       </c>
     </row>
@@ -1365,6 +1430,39 @@
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>The phone app redone for the founder and the pilot client: My Work (tiles, bands, cards, the full-screen task with a slider foot and Notes), Dex drafting every checklist by itself, request cards, Dex Decide (reading checklist under Dex as a figure, the three-screen review, also from the Desk), the voice wave and pause, full-screen confirmations for every toast, pop-ups in place, your own dock, the owner told when work is finished. Plan: the founder's reference screens, 2026-10-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Finance periods</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, a setting for when the year starts, rolls over by itself. Plan: docs/FINANCE_PERIODS.md.</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4011,70 +4109,74 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>NF-4.14</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_trash.py (_expand, _consequences, plan_items, remove, _record); pages/finance/FinanceDelete.jsx; bootstrap/lifecycle.py</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Deleting a sales invoice took 4-8 seconds</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-29: 'it can't be deleted'. Found on the demo workspace: delete works for every record type (invoice, expense, asset, stock; undo and the tiles return exactly), but a sales invoice's confirm sheet sat loading 4-8 s with Delete greyed out, then the delete took ~7 s and the row stayed until every list reloaded. Profiled: the plan asked 15 database questions one after another (payments 6 times; every pass repeated every question, and 'payments on this invoice' was asked twice), the delete 23 writes one after another, ~0.2 s each on a hosted database; six lookups had no index. Fixed: each pass asks only about rows new since the last and asks them together; the payment lookup is one query and its answer is reused; the consequences are asked in one round; the delete's independent writes run together (the trash copy is still written first); six indexes added (inventory.invoice_id, assets.expense_id, expenses.payment_id, stock_movements.inventory_id, requests.expense_id, brain_context.related_ids.invoice_id); the deleted rows leave the lists the moment the server answers. Same results: the 60 delete / request / functional tests pass unchanged.</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
           <t>NF-5.1</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>One delete for every door</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-29 (fix). Plan 15 -&gt; 8 database calls, delete 23 -&gt; 16, each pass's calls together. On the test setup (laptop -&gt; hosted DB): bin -&gt; Delete ready 4-8 s -&gt; 2.1 s; Delete -&gt; row gone ~8 s -&gt; 2.8 s; on the server, next to its database, near-instant. New test: test_planning_an_invoice_delete_asks_each_question_once (no question twice, at most 9 for an invoice and its payment).</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Client 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4089,12 +4191,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -4104,7 +4206,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -4112,14 +4214,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -4131,12 +4229,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4151,12 +4249,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -4176,7 +4274,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -4193,12 +4291,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4208,17 +4306,17 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -4238,7 +4336,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -4255,12 +4353,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4270,27 +4368,27 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4317,12 +4415,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4337,12 +4435,12 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -4352,7 +4450,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -4379,12 +4477,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4394,27 +4492,27 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4441,12 +4539,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4456,17 +4554,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -4484,7 +4582,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -4499,30 +4601,32 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -4532,7 +4636,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -4540,27 +4644,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n"/>
+      <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -4573,12 +4677,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -4588,7 +4692,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -4611,12 +4715,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
@@ -4629,17 +4733,17 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4667,12 +4771,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -4680,27 +4784,27 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4723,12 +4827,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -4741,22 +4845,22 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -4779,12 +4883,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -4792,27 +4896,27 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -4835,12 +4939,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -4853,12 +4957,12 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -4891,12 +4995,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -4909,12 +5013,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -4924,7 +5028,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -4947,12 +5051,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -4965,22 +5069,22 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5003,12 +5107,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5016,22 +5120,22 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5059,12 +5163,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5072,22 +5176,22 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5115,12 +5219,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5128,17 +5232,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5148,7 +5252,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -5171,12 +5275,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5184,27 +5288,27 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5227,12 +5331,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5240,17 +5344,17 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -5283,12 +5387,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5301,12 +5405,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -5339,12 +5443,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5357,22 +5461,22 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5395,12 +5499,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5408,17 +5512,17 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -5428,7 +5532,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -5451,12 +5555,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5464,22 +5568,22 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5507,12 +5611,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5520,22 +5624,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5545,13 +5649,13 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -5563,12 +5667,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5581,22 +5685,22 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -5619,68 +5723,68 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -5693,12 +5797,12 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -5708,7 +5812,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -5731,12 +5835,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -5749,12 +5853,12 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -5764,7 +5868,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -5787,12 +5891,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -5805,12 +5909,12 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5820,7 +5924,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -5843,12 +5947,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -5861,12 +5965,12 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5876,7 +5980,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -5899,12 +6003,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -5917,12 +6021,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -5955,12 +6059,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -5973,17 +6077,17 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6011,12 +6115,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6024,22 +6128,22 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6067,12 +6171,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6080,17 +6184,17 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6100,7 +6204,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -6111,7 +6215,7 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -6123,12 +6227,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6141,12 +6245,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6167,7 +6271,7 @@
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -6179,12 +6283,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6192,17 +6296,17 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -6223,7 +6327,7 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6235,12 +6339,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6248,27 +6352,27 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -6279,7 +6383,7 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -6291,12 +6395,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6304,22 +6408,22 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6335,7 +6439,7 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -6347,40 +6451,40 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6391,24 +6495,24 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -6421,12 +6525,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6459,12 +6563,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6472,17 +6576,17 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6492,7 +6596,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6503,7 +6607,7 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -6515,12 +6619,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6528,22 +6632,22 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -6559,7 +6663,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -6571,12 +6675,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6584,17 +6688,17 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -6604,7 +6708,7 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -6615,7 +6719,7 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -6627,12 +6731,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -6640,17 +6744,17 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -6660,7 +6764,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -6671,7 +6775,7 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -6683,12 +6787,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -6701,12 +6805,12 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -6727,7 +6831,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -6739,12 +6843,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -6752,17 +6856,17 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -6795,12 +6899,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -6813,22 +6917,22 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -6839,7 +6943,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -6851,12 +6955,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -6869,12 +6973,12 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -6884,7 +6988,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -6895,7 +6999,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -6907,12 +7011,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -6920,17 +7024,17 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -6940,7 +7044,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -6951,7 +7055,7 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6963,12 +7067,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -6981,22 +7085,22 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -7007,7 +7111,7 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -7019,12 +7123,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7037,17 +7141,17 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7075,12 +7179,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7088,27 +7192,27 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -7131,12 +7235,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7144,17 +7248,17 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -7164,7 +7268,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7175,7 +7279,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -7187,12 +7291,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7200,27 +7304,27 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -7231,7 +7335,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -7243,12 +7347,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7256,17 +7360,17 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -7287,7 +7391,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7299,12 +7403,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7312,17 +7416,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7332,7 +7436,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -7343,7 +7447,7 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7355,12 +7459,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7373,17 +7477,17 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -7399,7 +7503,7 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -7411,12 +7515,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7424,22 +7528,22 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -7455,12 +7559,368 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.20</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>index.css (sky)</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>No amber glow; Notifications wears Finance's sky</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="n"/>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
           <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
-      <c r="L107" s="4" t="inlineStr">
+      <c r="L108" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Settings / Finance</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Financial year starts in (company setting)</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Overview opens on the financial year; every quarter and half</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.3</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Finance / UI</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>The period picker: kind, then which one</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.4</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>It rolls over by itself</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.5</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Date tests and checks</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 13 of 14 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods (feature) built 2026-10-29: Finance follows the financial year.</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 14 of 15 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 13 of 14 Done</t>
+          <t>In progress -- 14 of 15 Done</t>
         </is>
       </c>
     </row>
@@ -1033,6 +1033,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
@@ -1084,7 +1085,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Done -- 5 of 5 (feature)</t>
+          <t>Done -- 6 of 6 (feature)</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1129,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 105 of 112 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods (feature).</t>
+          <t>Epic 11 progress: 107 of 114 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods (feature).</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1281,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1445,10 +1446,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1462,7 +1463,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, a setting for when the year starts, rolls over by itself. Plan: docs/FINANCE_PERIODS.md.</t>
+          <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, one period for Overview, Revenue and Expenses (owed money never hidden), a setting for when the year starts, rolls over by itself. Plan: docs/FINANCE_PERIODS.md.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4171,17 +4172,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-4.15</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
+          <t>pages/finance/ledgerMath.js (inside, balanceAt, periodWindow countEnd)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -4191,12 +4192,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>One delete for every door</t>
+          <t>A record dated on the first day of a period counted in the period before</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+          <t>Found 2026-10-29 while adding the period to Revenue and Expenses: a window left out its own first moment (t &gt; start), so an invoice dated 1 April 2026 counted in FY 2025-26 and not in FY 2026-27 (or Q1); and a running quarter stopped at today, so an invoice dated next week in the same quarter counted nowhere. Fixed: a period includes its start and stops before its end; a running year / half / quarter counts everything dated inside it.</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -4206,7 +4207,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -4214,27 +4215,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-30 (fix). Tests: test_the_first_day_of_a_period_belongs_to_it (1 Apr 2026 and 31 Mar 2027 in FY 2026-27; 31 Mar 2026 in FY 2025-26; next week's invoice in the running quarter), test_a_record_is_in_a_period_by_its_own_date.</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Found 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4249,12 +4254,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -4264,7 +4269,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -4272,14 +4277,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4291,12 +4292,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4311,12 +4312,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -4336,7 +4337,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -4353,12 +4354,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4368,17 +4369,17 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -4398,7 +4399,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -4415,12 +4416,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4430,27 +4431,27 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -4477,12 +4478,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4497,12 +4498,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -4512,7 +4513,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4539,12 +4540,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4554,27 +4555,27 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -4601,12 +4602,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4616,17 +4617,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -4644,7 +4645,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -4659,30 +4664,32 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -4692,7 +4699,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -4700,27 +4707,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n"/>
+      <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
@@ -4733,12 +4740,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -4748,7 +4755,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4771,12 +4778,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -4789,17 +4796,17 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4827,12 +4834,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -4840,27 +4847,27 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -4883,12 +4890,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -4901,22 +4908,22 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -4939,12 +4946,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -4952,27 +4959,27 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -4995,12 +5002,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -5013,12 +5020,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -5051,12 +5058,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -5069,12 +5076,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -5084,7 +5091,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5107,12 +5114,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5125,22 +5132,22 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5163,12 +5170,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5176,22 +5183,22 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5219,12 +5226,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5232,22 +5239,22 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5275,12 +5282,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5288,17 +5295,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5308,7 +5315,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5331,12 +5338,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5344,27 +5351,27 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5387,12 +5394,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5400,17 +5407,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -5443,12 +5450,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5461,12 +5468,12 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -5499,12 +5506,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5517,22 +5524,22 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -5555,12 +5562,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5568,17 +5575,17 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -5588,7 +5595,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5611,12 +5618,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5624,22 +5631,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5667,12 +5674,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5680,22 +5687,22 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5705,13 +5712,13 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -5723,12 +5730,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -5741,22 +5748,22 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -5779,68 +5786,68 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -5853,12 +5860,12 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -5868,7 +5875,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -5891,12 +5898,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -5909,12 +5916,12 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5924,7 +5931,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -5947,12 +5954,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -5965,12 +5972,12 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5980,7 +5987,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -6003,12 +6010,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -6021,12 +6028,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -6036,7 +6043,7 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -6059,12 +6066,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -6077,12 +6084,12 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6115,12 +6122,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6133,17 +6140,17 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6171,12 +6178,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6184,22 +6191,22 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6227,12 +6234,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6240,17 +6247,17 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6260,7 +6267,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -6271,7 +6278,7 @@
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -6283,12 +6290,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6301,12 +6308,12 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -6327,7 +6334,7 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6339,12 +6346,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6352,17 +6359,17 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6383,7 +6390,7 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -6395,12 +6402,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6408,27 +6415,27 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6439,7 +6446,7 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -6451,12 +6458,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -6464,22 +6471,22 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6495,7 +6502,7 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -6507,40 +6514,40 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6551,24 +6558,24 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6581,12 +6588,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6619,12 +6626,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6632,17 +6639,17 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6652,7 +6659,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6663,7 +6670,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -6675,12 +6682,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6688,22 +6695,22 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -6719,7 +6726,7 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -6731,12 +6738,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -6744,17 +6751,17 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -6764,7 +6771,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -6775,7 +6782,7 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -6787,12 +6794,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -6800,17 +6807,17 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -6820,7 +6827,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -6831,7 +6838,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -6843,12 +6850,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -6861,12 +6868,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -6887,7 +6894,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -6899,12 +6906,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -6912,17 +6919,17 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -6955,12 +6962,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -6973,22 +6980,22 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -6999,7 +7006,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -7011,12 +7018,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -7029,12 +7036,12 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -7044,7 +7051,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -7055,7 +7062,7 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -7067,12 +7074,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -7080,17 +7087,17 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -7100,7 +7107,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -7111,7 +7118,7 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -7123,12 +7130,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7141,22 +7148,22 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7167,7 +7174,7 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -7179,12 +7186,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7197,17 +7204,17 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -7235,12 +7242,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7248,27 +7255,27 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7291,12 +7298,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7304,17 +7311,17 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -7324,7 +7331,7 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -7335,7 +7342,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -7347,12 +7354,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7360,27 +7367,27 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -7391,7 +7398,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7403,12 +7410,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7416,17 +7423,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7447,7 +7454,7 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7459,12 +7466,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7472,17 +7479,17 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -7492,7 +7499,7 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -7503,7 +7510,7 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -7515,12 +7522,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7533,17 +7540,17 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -7559,7 +7566,7 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -7571,12 +7578,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -7584,22 +7591,22 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -7615,7 +7622,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7627,35 +7634,35 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-8.20</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+          <t>index.css (sky)</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Settings / Finance</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Financial year starts in (company setting)</t>
+          <t>No amber glow; Notifications wears Finance's sky</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -7668,31 +7675,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
@@ -7700,17 +7703,17 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Settings / Finance</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Overview opens on the financial year; every quarter and half</t>
+          <t>Financial year starts in (company setting)</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -7720,7 +7723,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -7730,7 +7733,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
@@ -7747,12 +7750,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>NF-9.3</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -7760,17 +7763,17 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Finance / UI</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>The period picker: kind, then which one</t>
+          <t>Overview opens on the financial year; every quarter and half</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -7807,12 +7810,12 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>NF-9.4</t>
+          <t>NF-9.3</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
@@ -7820,17 +7823,17 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / UI</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>It rolls over by itself</t>
+          <t>The period picker: kind, then which one</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -7840,7 +7843,7 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -7867,12 +7870,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>NF-9.5</t>
+          <t>NF-9.4</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
@@ -7880,47 +7883,167 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>It rolls over by itself</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.5</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Date tests and checks</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="G114" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H113" s="4" t="inlineStr">
+      <c r="H114" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I113" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>NF-9.1</t>
         </is>
       </c>
-      <c r="K113" s="4" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
-      <c r="L113" s="4" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.6</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>One period for all of Finance</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 14 of 15 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance.</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 14 of 15 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Sprint 9 -- Finance periods</t>
+          <t>Sprint 9 -- Finance periods and bill review</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js, pages/finance/PeriodPicker.jsx, pages/Ledger.js, pages/finance/FinanceOverview.jsx, components/CompanyDetails.js, models/tenant.py, routers/tenant_settings.py</t>
+          <t>pages/finance/ledgerMath.js, pages/finance/PeriodPicker.jsx, pages/Ledger.js, pages/finance/FinanceOverview.jsx, components/CompanyDetails.js, models/tenant.py, routers/tenant_settings.py, pages/finance/FinanceForms.jsx, routers/ledger.py (read_bill)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Client: records added in Finance were 'not reflecting' in Revenue, Received or Profit. They were saved - the Overview defaulted to the last 30 days and counts a record by its own date. Businesses work in financial years, halves and quarters: the Overview now opens on the financial year, any quarter or half of any year can be picked, the year's start month is a setting, and it rolls over by itself.</t>
+          <t>Client: records added in Finance were 'not reflecting' in Revenue, Received or Profit. They were saved - the Overview defaulted to the last 30 days and counts a record by its own date. Businesses work in financial years, halves and quarters: the Overview now opens on the financial year, any quarter or half of any year can be picked, the year's start month is a setting, and it rolls over by itself. 2026-10-30: an attached bill is read first and its values filled in for the person to check before saving - nothing reaches the books unchecked.</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Done -- 6 of 6 (feature)</t>
+          <t>Done -- 7 of 7 (feature)</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 107 of 114 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods (feature).</t>
+          <t>Epic 11 progress: 108 of 115 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature).</t>
         </is>
       </c>
     </row>
@@ -1442,14 +1442,14 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Finance periods</t>
+          <t>Finance periods and bill review</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, one period for Overview, Revenue and Expenses (owed money never hidden), a setting for when the year starts, rolls over by itself. Plan: docs/FINANCE_PERIODS.md.</t>
+          <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, one period for Overview, Revenue and Expenses (owed money never hidden), a setting for when the year starts, rolls over by itself - and an attached bill is read first, filled in for the person to check, then saved. Plan: docs/FINANCE_PERIODS.md.</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8047,6 +8047,66 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.7</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Finance / AI</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>A bill is read, then confirmed</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1086,6 +1086,61 @@
       <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Done -- 7 of 7 (feature)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 10 -- Onboarding, first-week tour, Dex widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>pages/Signup.js, pages/onboarding/* (OsAssembly, OsMap, WaitStory, BasicsFlow, VoiceInterview, voice.js, BuildReveal, walkthrough/*), components/tour/FirstWeekTour.jsx, lib/firstTour.js, components/Layout.js, components/mobile/Walkthrough.jsx, pages/MyWork.js, pages/mywork/*, pages/desk/DeskDexWell.jsx + DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx, lib/native/quick.js, index.css; android (DexWidgetProvider, DexQuickActivity, widget resources); backend services/ai/onboarding.py, routers/signup.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>The founder: onboarding is where a client is won - it must show the company being built as they answer, never leave them waiting in silence, and end with what was made and where it lives in the app; plus Dex one tap from the home screen, desktop matching the phone's task design, a camera beside attach, and the phone's grey freeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Founder messages and screenshots, 2026-10-29 and 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>21 of 23 Done; open: NF-10.22 transcription mode (founder), NF-10.23 backend deploy</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1129,10 +1184,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 108 of 115 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 11 progress: 129 of 138 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1464,6 +1520,39 @@
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, one period for Overview, Revenue and Expenses (owed money never hidden), a setting for when the year starts, rolls over by itself - and an attached bill is read first, filled in for the person to check, then saved. Plan: docs/FINANCE_PERIODS.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding, first-week tour, Dex widget</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Signup redrawn as the company's OS taking shape (blueprint ground, the OS canvas fed by every answer, waits that say what is happening, interview pause, the summary with KPIs and the What Dex built explorer); the first-week tour over the real desktop app; Dex on the Android home screen; desktop takes the phone's task view and card; a camera beside attach; the phone's grey freeze on Decide fixed; release 1.1.0. Open: transcription mode (founder's call), backend deploy.</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8107,6 +8196,1340 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.1</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Dex widget</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Dex on the Android home screen</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.2</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>The widget layer opened black</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.3</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.4</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.5</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>"Your OS, taking shape" beside every signup step</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.6</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Each interview answer names what it added to the OS</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.7</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Client feedback</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Every wait says what is happening</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.8</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Pause and resume while answering the interview</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.9</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Basics and the language pick: pictures, fewer words</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.10</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>The build carries the picture on</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.11</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.12</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>The team map: hand-offs along the ring, plain panel</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - f65c54a.</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.13</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr"/>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 2b395c6.</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.14</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>The first-week tour, inside the real desktop app</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.15</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 0f1438c.</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.16</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Desktop parity</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Desktop opens the phone's task view</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr"/>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.17</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Desktop parity</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Desktop list cards are the phone's task card</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 56e7d44.</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.18</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>A proof photo tapped on the phone opened nothing</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 56e7d44.</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.19</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>A camera button beside attach</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.20</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>The phone froze grey on Decide's "What you said"</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.21</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>DecisionOS 1.1.0 release build</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30.</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.22</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Decide and Ask show a translation, not the words spoken</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>Waiting on the founder's call (2026-10-30).</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.23</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Railway backend</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Deploy the backend for the interview's live pieces</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>Needs a deploy go-ahead.</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -542,10 +544,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 12 of 13 fixed (e46b7cc, e352141); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish built 2026-10-23.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 14 of 15 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -558,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -570,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -577,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -632,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -687,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -742,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -793,10 +802,11 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 12 of 13 Done</t>
-        </is>
-      </c>
-    </row>
+          <t>In progress -- 14 of 15 Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -852,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
@@ -959,7 +970,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Built -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 built (13 of 13)</t>
+          <t>Done -- P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335 (13 of 13)</t>
         </is>
       </c>
     </row>
@@ -973,7 +984,6 @@
           <t>Sprint 8 -- Phone redesign</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -1020,6 +1030,117 @@
       <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Done -- 20 of 20 (3ecf7bf + the 2026-10-29 push)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 9 -- Finance periods and bill review</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/ledgerMath.js, pages/finance/PeriodPicker.jsx, pages/Ledger.js, pages/finance/FinanceOverview.jsx, components/CompanyDetails.js, models/tenant.py, routers/tenant_settings.py, pages/finance/FinanceForms.jsx, routers/ledger.py (read_bill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Client: records added in Finance were 'not reflecting' in Revenue, Received or Profit. They were saved - the Overview defaulted to the last 30 days and counts a record by its own date. Businesses work in financial years, halves and quarters: the Overview now opens on the financial year, any quarter or half of any year can be picked, the year's start month is a setting, and it rolls over by itself. 2026-10-30: an attached bill is read first and its values filled in for the person to check before saving - nothing reaches the books unchecked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Done -- 7 of 7 (feature)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 10 -- Onboarding, first-week tour, Dex widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>pages/Signup.js, pages/onboarding/* (OsAssembly, OsMap, WaitStory, BasicsFlow, VoiceInterview, voice.js, BuildReveal, walkthrough/*), components/tour/FirstWeekTour.jsx, lib/firstTour.js, components/Layout.js, components/mobile/Walkthrough.jsx, pages/MyWork.js, pages/mywork/*, pages/desk/DeskDexWell.jsx + DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx, lib/native/quick.js, index.css; android (DexWidgetProvider, DexQuickActivity, widget resources); backend services/ai/onboarding.py, routers/signup.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>The founder: onboarding is where a client is won - it must show the company being built as they answer, never leave them waiting in silence, and end with what was made and where it lives in the app; plus Dex one tap from the home screen, desktop matching the phone's task design, a camera beside attach, and the phone's grey freeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Founder messages and screenshots, 2026-10-29 and 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>21 of 23 Done; open: NF-10.22 transcription mode (founder), NF-10.23 backend deploy</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1063,10 +1184,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 99 of 106 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 11 progress: 129 of 138 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1215,14 +1337,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1326,12 +1448,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>The console that runs the business: P1 data foundations (sign-ins incl. phone code, daily presence, a daily count per workspace kept for good, lifecycle events, milestones and activation) built; P2 customers, P3 analytics, P4 support depth, P5 polish planned. Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
+          <t>The console that runs the business: P1 data foundations (1ea398d), P2 customers (a6a8215), P3 analytics (cf8da32), P4 support depth and P5 polish (47e0335). Plan: docs/ADMIN_CONSOLE_V2_PLAN.md.</t>
         </is>
       </c>
     </row>
@@ -1365,6 +1487,72 @@
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>The phone app redone for the founder and the pilot client: My Work (tiles, bands, cards, the full-screen task with a slider foot and Notes), Dex drafting every checklist by itself, request cards, Dex Decide (reading checklist under Dex as a figure, the three-screen review, also from the Desk), the voice wave and pause, full-screen confirmations for every toast, pop-ups in place, your own dock, the owner told when work is finished. Plan: the founder's reference screens, 2026-10-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Finance periods and bill review</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Feature: Finance follows the company's financial year - opens on the FY, any quarter or half of any year, custom range, one period for Overview, Revenue and Expenses (owed money never hidden), a setting for when the year starts, rolls over by itself - and an attached bill is read first, filled in for the person to check, then saved. Plan: docs/FINANCE_PERIODS.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding, first-week tour, Dex widget</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Signup redrawn as the company's OS taking shape (blueprint ground, the OS canvas fed by every answer, waits that say what is happening, interview pause, the summary with KPIs and the What Dex built explorer); the first-week tour over the real desktop app; Dex on the Android home screen; desktop takes the phone's task view and card; a camera beside attach; the phone's grey freeze on Decide fixed; release 1.1.0. Open: transcription mode (founder's call), backend deploy.</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4011,75 +4199,79 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>NF-4.14</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_trash.py (_expand, _consequences, plan_items, remove, _record); pages/finance/FinanceDelete.jsx; bootstrap/lifecycle.py</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Deleting a sales invoice took 4-8 seconds</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Client 2026-10-29: 'it can't be deleted'. Found on the demo workspace: delete works for every record type (invoice, expense, asset, stock; undo and the tiles return exactly), but a sales invoice's confirm sheet sat loading 4-8 s with Delete greyed out, then the delete took ~7 s and the row stayed until every list reloaded. Profiled: the plan asked 15 database questions one after another (payments 6 times; every pass repeated every question, and 'payments on this invoice' was asked twice), the delete 23 writes one after another, ~0.2 s each on a hosted database; six lookups had no index. Fixed: each pass asks only about rows new since the last and asks them together; the payment lookup is one query and its answer is reused; the consequences are asked in one round; the delete's independent writes run together (the trash copy is still written first); six indexes added (inventory.invoice_id, assets.expense_id, expenses.payment_id, stock_movements.inventory_id, requests.expense_id, brain_context.related_ids.invoice_id); the deleted rows leave the lists the moment the server answers. Same results: the 60 delete / request / functional tests pass unchanged.</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
           <t>NF-5.1</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>One delete for every door</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-29 (fix). Plan 15 -&gt; 8 database calls, delete 23 -&gt; 16, each pass's calls together. On the test setup (laptop -&gt; hosted DB): bin -&gt; Delete ready 4-8 s -&gt; 2.1 s; Delete -&gt; row gone ~8 s -&gt; 2.8 s; on the server, next to its database, near-instant. New test: test_planning_an_invoice_delete_asks_each_question_once (no question twice, at most 9 for an invoice and its payment).</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Client 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-4.15</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
+          <t>pages/finance/ledgerMath.js (inside, balanceAt, periodWindow countEnd)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -4089,12 +4281,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>A record dated on the first day of a period counted in the period before</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Found 2026-10-29 while adding the period to Revenue and Expenses: a window left out its own first moment (t &gt; start), so an invoice dated 1 April 2026 counted in FY 2025-26 and not in FY 2026-27 (or Q1); and a running quarter stopped at today, so an invoice dated next week in the same quarter counted nowhere. Fixed: a period includes its start and stops before its end; a running year / half / quarter counts everything dated inside it.</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -4104,7 +4296,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -4114,29 +4306,29 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-30 (fix). Tests: test_the_first_day_of_a_period_belongs_to_it (1 Apr 2026 and 31 Mar 2027 in FY 2026-27; 31 Mar 2026 in FY 2025-26; next week's invoice in the running quarter), test_a_record_is_in_a_period_by_its_own_date.</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Found 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4151,12 +4343,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -4166,7 +4358,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -4174,14 +4366,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.2</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4193,12 +4381,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4208,17 +4396,17 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -4255,12 +4443,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4275,22 +4463,22 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4300,7 +4488,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -4317,12 +4505,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4332,22 +4520,22 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4379,12 +4567,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4394,22 +4582,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4441,12 +4629,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4456,27 +4644,27 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -4484,7 +4672,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -4499,30 +4691,32 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>6</v>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -4532,7 +4726,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -4540,45 +4734,51 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -4596,22 +4796,22 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n"/>
+      <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -4629,22 +4829,22 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4667,12 +4867,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -4680,17 +4880,17 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -4700,7 +4900,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4723,12 +4923,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -4736,17 +4936,17 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -4779,12 +4979,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -4792,17 +4992,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -4812,7 +5012,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -4835,12 +5035,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -4848,27 +5048,27 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -4891,12 +5091,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -4909,12 +5109,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -4924,7 +5124,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -4947,12 +5147,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -4965,17 +5165,17 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5003,12 +5203,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5016,17 +5216,17 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5036,7 +5236,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5059,12 +5259,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5072,17 +5272,17 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -5115,12 +5315,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5128,27 +5328,27 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -5171,12 +5371,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5184,22 +5384,22 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5227,12 +5427,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5240,27 +5440,27 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5283,12 +5483,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5296,17 +5496,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -5339,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5357,22 +5557,22 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5395,12 +5595,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5408,22 +5608,22 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5451,12 +5651,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5464,27 +5664,27 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5507,12 +5707,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5520,17 +5720,17 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5545,13 +5745,13 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -5563,12 +5763,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5576,38 +5776,38 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -5619,35 +5819,35 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5657,53 +5857,53 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -5713,30 +5913,30 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -5749,12 +5949,12 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -5787,12 +5987,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -5805,12 +6005,12 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5843,12 +6043,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -5861,12 +6061,12 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5899,12 +6099,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -5917,12 +6117,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -5932,7 +6132,7 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -5955,12 +6155,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -5973,17 +6173,17 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6011,12 +6211,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6024,17 +6224,17 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6067,12 +6267,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6080,27 +6280,27 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -6111,7 +6311,7 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -6123,12 +6323,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6136,17 +6336,17 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6156,7 +6356,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -6167,7 +6367,7 @@
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -6179,12 +6379,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6192,17 +6392,17 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -6223,7 +6423,7 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6235,12 +6435,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6248,27 +6448,27 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -6279,7 +6479,7 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -6291,12 +6491,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6304,27 +6504,27 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6335,7 +6535,7 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23 (awaiting push). adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -6347,40 +6547,40 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6391,52 +6591,52 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6447,24 +6647,24 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6472,17 +6672,17 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6492,7 +6692,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6503,7 +6703,7 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -6515,12 +6715,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6528,27 +6728,27 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6559,7 +6759,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -6571,12 +6771,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6584,27 +6784,27 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -6615,7 +6815,7 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -6627,12 +6827,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -6640,17 +6840,17 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -6671,7 +6871,7 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -6683,12 +6883,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -6696,17 +6896,17 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -6716,7 +6916,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -6727,7 +6927,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -6739,12 +6939,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -6752,17 +6952,17 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -6783,7 +6983,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -6795,12 +6995,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -6808,27 +7008,27 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -6839,7 +7039,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -6851,12 +7051,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -6869,22 +7069,22 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -6907,12 +7107,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -6920,17 +7120,17 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -6940,7 +7140,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -6963,12 +7163,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -6976,22 +7176,22 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7019,12 +7219,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7037,22 +7237,22 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7063,7 +7263,7 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -7075,12 +7275,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7088,17 +7288,17 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -7108,7 +7308,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -7131,12 +7331,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7144,22 +7344,22 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -7175,7 +7375,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -7187,12 +7387,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7200,22 +7400,22 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -7231,7 +7431,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -7243,12 +7443,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7256,27 +7456,27 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -7287,7 +7487,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7299,12 +7499,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7317,12 +7517,12 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7332,7 +7532,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -7343,7 +7543,7 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7355,12 +7555,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7368,27 +7568,27 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -7399,7 +7599,7 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -7411,12 +7611,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7424,22 +7624,22 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -7455,12 +7655,1878 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.19</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>The card's steps: a row of numbers above Next action</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="n"/>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>NF-8.20</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>index.css (sky)</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>No amber glow; Notifications wears Finance's sky</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
           <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
-      <c r="L107" s="4" t="inlineStr">
+      <c r="L109" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-29 (phone redesign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Settings / Finance</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Financial year starts in (company setting)</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Overview opens on the financial year; every quarter and half</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.3</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Finance / UI</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>The period picker: kind, then which one</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.4</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>It rolls over by itself</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.5</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Date tests and checks</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.6</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>One period for all of Finance</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.7</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Finance / AI</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>A bill is read, then confirmed</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.1</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Dex widget</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Dex on the Android home screen</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.2</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>The widget layer opened black</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.3</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Dex Decide</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.4</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.5</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>"Your OS, taking shape" beside every signup step</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.6</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Each interview answer names what it added to the OS</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.7</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Client feedback</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Every wait says what is happening</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.8</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Pause and resume while answering the interview</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.9</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Basics and the language pick: pictures, fewer words</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.10</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>The build carries the picture on</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.11</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.12</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>The team map: hand-offs along the ring, plain panel</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - f65c54a.</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.13</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr"/>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 2b395c6.</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.14</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>The first-week tour, inside the real desktop app</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.15</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 0f1438c.</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.16</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Desktop parity</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Desktop opens the phone's task view</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr"/>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.17</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Desktop parity</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Desktop list cards are the phone's task card</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 56e7d44.</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.18</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>A proof photo tapped on the phone opened nothing</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-29 - 56e7d44.</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.19</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>A camera button beside attach</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.20</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>The phone froze grey on Decide's "What you said"</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.21</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>DecisionOS 1.1.0 release build</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30.</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.22</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Decide and Ask show a translation, not the words spoken</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>Waiting on the founder's call (2026-10-30).</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.23</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Railway backend</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Deploy the backend for the interview's live pieces</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>Needs a deploy go-ahead.</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 14 of 15 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed.</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 16 of 17 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17).</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 14 of 15 Done</t>
+          <t>In progress -- 16 of 17 Done</t>
         </is>
       </c>
     </row>
@@ -1089,6 +1089,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
@@ -1141,6 +1142,61 @@
       <c r="B74" s="4" t="inlineStr">
         <is>
           <t>21 of 23 Done; open: NF-10.22 transcription mode (founder), NF-10.23 backend deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 11 -- Decisions to owned work</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py (new), services/voice.py, services/decision_flow.py, services/workflow_engine.py, services/enrich.py, services/deprovisioning.py, services/finance_signals.py, routers/tasks.py, routers/decisions.py, routers/tenant_settings.py, pages/desk/NeedsPersonSheet.jsx (new), pages/Desk.js, pages/MyWork.js, components/DecisionDialog.js, pages/desk/DexReview.jsx, pages/Settings.js, pages/Tasks.js, lib/notif.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Complaint: a decision makes its tasks and most land with nobody - 93 of 148 open decision/workflow tasks in the dev data - and nobody is told. Team tasks went to whoever had the fewest tasks; founder: 'that's not the right way'. Now the team's queue first, its nearest managers for high priority, the owner when there is no team; reminders climb the reporting tree one level a day (team leads, head, owner) instead of piling onto the owner; Finance follow-ups follow the same rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>docs/WORK_NOBODY_HAS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Done -- 9 of 9 (feature)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1184,11 +1240,10 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 129 of 138 items Done  (93%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 11 progress: 140 of 149 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1337,14 +1392,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1553,6 +1608,39 @@
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Signup redrawn as the company's OS taking shape (blueprint ground, the OS canvas fed by every answer, waits that say what is happening, interview pause, the summary with KPIs and the What Dex built explorer); the first-week tour over the real desktop app; Dex on the Android home screen; desktop takes the phone's task view and card; a camera beside attach; the phone's grey freeze on Decide fixed; release 1.1.0. Open: transcription mode (founder's call), backend deploy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Decisions to owned work</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Feature: tasks never sit with nobody (decisions, stages, New Task, Finance follow-ups). Named person, else the team's one person, else the team's queue (Take it); high priority asks the nearest managers; no team asks the owner. Never by load. Reminders climb the reporting tree one level a day, the owner last. Needs a person on the Desk. Plan: docs/WORK_NOBODY_HAS.md.</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4323,32 +4411,30 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-4.16</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>services/voice.py pick_least_loaded_member; services/task_pickup.company</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Team / Work</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>One delete for every door</t>
+          <t>Older members dropped once one person was invited</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+          <t>Fix. Finding: 'who is active' was decided company-wide - if the company had ANY membership row, only active rows counted. An older company's people have no rows, so the day one new person was invited everyone from before dropped out: an auto-assigned task went to the newcomer, or to nobody. Found on the demo workspace (no rows at all) while checking Sprint 10. Now judged per person: a row that is not active leaves someone out; no row counts.</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -4358,7 +4444,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -4366,47 +4452,45 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-30 (fix). test_epic3_s9_autoassign::test_older_members_without_a_membership_row_still_count; test_work_nobody_has_finds_its_person.py::test_people_from_before_memberships_count_and_invitees_do_not.</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-4.17</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>routers/auth.py register</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Signup / Identity</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>A second company on the same number failed at the last step</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Fix. Team report 2026-10-30: an owner creating another company with the same number was told at the final step it 'already exists'. Findings, by running one number through several signups with the dev OTP and reading the DB: (1) typing the email they already use -&gt; 'This email already runs &lt;company&gt;' after the whole OS was built, although the confirmed mobile proved it was the same founder; (2) an employee whose number an owner added (never confirmed by a code) is offered 'start another' (no email asked) and register then said 'This number has no workspace yet'; (3) a retried Create on the number path (lost answer, double tap) made a duplicate workspace with the same name; (4) WhatsApp's home workspace was only set on the no-email path, so a number gaining a workspace another way had its WhatsApp dropped. Now: same founder + their own email -&gt; a second company (no sign-in email, the address becomes its support email); a just-confirmed number that reaches a live workspace makes its own company (nobody else's row marked confirmed); same number + same company name within 30 min opens the company already made; the first workspace stays the WhatsApp home whenever a number gains another.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -4424,31 +4508,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-30 (fix). Scratch backend, one number + dev OTP: 4 companies (first, no email, same email, from the session), each 1 user row + owner membership; switcher lists all 4 and switches to each and back; Mobile OTP sign-in offers all 4 and opens each; a retried Create opens the same company; an employee's own company made. test_second_company.py: same email -&gt; second company, someone else's email still refused, employee's number, Create pressed twice.</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Team report 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4463,12 +4543,12 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -4478,7 +4558,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4486,14 +4566,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.2</t>
-        </is>
-      </c>
+      <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4505,12 +4581,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4520,17 +4596,17 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -4567,12 +4643,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4587,22 +4663,22 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4612,7 +4688,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -4629,12 +4705,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4644,22 +4720,22 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4691,12 +4767,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4706,22 +4782,22 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4753,12 +4829,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4768,27 +4844,27 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -4796,7 +4872,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -4811,30 +4891,32 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>6</v>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -4844,7 +4926,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4852,45 +4934,51 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -4908,22 +4996,22 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J58" s="4" t="n"/>
+      <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -4941,22 +5029,22 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -4979,12 +5067,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -4992,17 +5080,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -5012,7 +5100,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -5035,12 +5123,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -5048,17 +5136,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -5091,12 +5179,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -5104,17 +5192,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -5124,7 +5212,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -5147,12 +5235,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -5160,27 +5248,27 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5203,12 +5291,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5221,12 +5309,12 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5236,7 +5324,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5259,12 +5347,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5277,17 +5365,17 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5315,12 +5403,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5328,17 +5416,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5348,7 +5436,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -5371,12 +5459,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5384,17 +5472,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5427,12 +5515,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5440,27 +5528,27 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5483,12 +5571,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5496,22 +5584,22 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5539,12 +5627,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5552,27 +5640,27 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5595,12 +5683,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5608,17 +5696,17 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -5651,12 +5739,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5669,22 +5757,22 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5707,12 +5795,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5720,22 +5808,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5763,12 +5851,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5776,27 +5864,27 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -5819,12 +5907,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -5832,17 +5920,17 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5857,13 +5945,13 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -5875,12 +5963,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -5888,38 +5976,38 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -5931,35 +6019,35 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -5969,53 +6057,53 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6025,30 +6113,30 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -6061,12 +6149,12 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -6099,12 +6187,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -6117,12 +6205,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -6155,12 +6243,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -6173,12 +6261,12 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6211,12 +6299,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6229,12 +6317,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6244,7 +6332,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -6267,12 +6355,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6285,17 +6373,17 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6323,12 +6411,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6336,17 +6424,17 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6379,12 +6467,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6392,27 +6480,27 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -6423,7 +6511,7 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6435,12 +6523,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6448,17 +6536,17 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6468,7 +6556,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -6479,7 +6567,7 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -6491,12 +6579,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6504,17 +6592,17 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -6535,7 +6623,7 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -6547,12 +6635,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -6560,27 +6648,27 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6591,7 +6679,7 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -6603,12 +6691,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -6616,27 +6704,27 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6647,7 +6735,7 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -6659,40 +6747,40 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6703,52 +6791,52 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6759,24 +6847,24 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6784,17 +6872,17 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -6804,7 +6892,7 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -6815,7 +6903,7 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -6827,12 +6915,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -6840,27 +6928,27 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -6871,7 +6959,7 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -6883,12 +6971,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -6896,27 +6984,27 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -6927,7 +7015,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -6939,12 +7027,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -6952,17 +7040,17 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -6983,7 +7071,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -6995,12 +7083,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -7008,17 +7096,17 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -7028,7 +7116,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -7039,7 +7127,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -7051,12 +7139,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -7064,17 +7152,17 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -7095,7 +7183,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -7107,12 +7195,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -7120,27 +7208,27 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -7151,7 +7239,7 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -7163,12 +7251,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -7181,22 +7269,22 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -7219,12 +7307,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7232,17 +7320,17 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -7252,7 +7340,7 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7275,12 +7363,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7288,22 +7376,22 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -7331,12 +7419,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7349,22 +7437,22 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7375,7 +7463,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -7387,12 +7475,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7400,17 +7488,17 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -7420,7 +7508,7 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -7443,12 +7531,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7456,22 +7544,22 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -7487,7 +7575,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7499,12 +7587,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7512,22 +7600,22 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -7543,7 +7631,7 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7555,12 +7643,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7568,27 +7656,27 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -7599,7 +7687,7 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -7611,12 +7699,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7629,12 +7717,12 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -7644,7 +7732,7 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -7655,7 +7743,7 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -7667,12 +7755,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -7680,27 +7768,27 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -7711,7 +7799,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7723,12 +7811,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
@@ -7736,22 +7824,22 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -7767,7 +7855,7 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -7779,35 +7867,35 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Settings / Finance</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Financial year starts in (company setting)</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -7820,59 +7908,55 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-8.20</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+          <t>index.css (sky)</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Overview opens on the financial year; every quarter and half</t>
+          <t>No amber glow; Notifications wears Finance's sky</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -7880,31 +7964,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>NF-9.1</t>
-        </is>
-      </c>
+      <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>NF-9.3</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
@@ -7912,17 +7992,17 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Finance / UI</t>
+          <t>Settings / Finance</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>The period picker: kind, then which one</t>
+          <t>Financial year starts in (company setting)</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -7932,7 +8012,7 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -7942,7 +8022,7 @@
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
@@ -7959,12 +8039,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>NF-9.4</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
@@ -7977,12 +8057,12 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>It rolls over by itself</t>
+          <t>Overview opens on the financial year; every quarter and half</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -7992,7 +8072,7 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -8019,12 +8099,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>NF-9.5</t>
+          <t>NF-9.3</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
@@ -8032,17 +8112,17 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance / UI</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Date tests and checks</t>
+          <t>The period picker: kind, then which one</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -8052,7 +8132,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -8079,12 +8159,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>NF-9.6</t>
+          <t>NF-9.4</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -8097,12 +8177,12 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>One period for all of Finance</t>
+          <t>It rolls over by itself</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -8112,7 +8192,7 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -8122,29 +8202,29 @@
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>NF-9.7</t>
+          <t>NF-9.5</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
@@ -8152,17 +8232,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Finance / AI</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>A bill is read, then confirmed</t>
+          <t>Date tests and checks</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -8172,7 +8252,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -8187,54 +8267,52 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>NF-10.1</t>
+          <t>NF-9.6</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Dex widget</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Dex on the Android home screen</t>
+          <t>One period for all of Finance</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -8242,47 +8320,49 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>NF-10.2</t>
+          <t>NF-9.7</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>DexQuickActivity.java, AndroidManifest.xml</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Finance / AI</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>The widget layer opened black</t>
+          <t>A bill is read, then confirmed</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -8292,7 +8372,7 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
@@ -8300,27 +8380,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>NF-10.3</t>
+          <t>NF-10.1</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -8330,17 +8414,17 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex widget</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+          <t>Dex on the Android home screen</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -8350,7 +8434,7 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -8361,7 +8445,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -8373,12 +8457,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>NF-10.4</t>
+          <t>NF-10.2</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -8388,22 +8472,22 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Signup background: a drawn blueprint, not a photograph</t>
+          <t>The widget layer opened black</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -8419,7 +8503,7 @@
       <c r="J120" s="4" t="inlineStr"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
@@ -8431,12 +8515,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>NF-10.5</t>
+          <t>NF-10.3</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -8446,27 +8530,27 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>"Your OS, taking shape" beside every signup step</t>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -8477,7 +8561,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -8489,12 +8573,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6</t>
+          <t>NF-10.4</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -8509,22 +8593,22 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Each interview answer names what it added to the OS</t>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -8535,7 +8619,7 @@
       <c r="J122" s="4" t="inlineStr"/>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
@@ -8547,12 +8631,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>NF-10.7</t>
+          <t>NF-10.5</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -8562,17 +8646,17 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Every wait says what is happening</t>
+          <t>"Your OS, taking shape" beside every signup step</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -8582,7 +8666,7 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -8593,7 +8677,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -8605,12 +8689,12 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>NF-10.8</t>
+          <t>NF-10.6</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -8625,22 +8709,22 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume while answering the interview</t>
+          <t>Each interview answer names what it added to the OS</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -8651,7 +8735,7 @@
       <c r="J124" s="4" t="inlineStr"/>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
@@ -8663,12 +8747,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>NF-10.9</t>
+          <t>NF-10.7</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -8678,27 +8762,27 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Basics and the language pick: pictures, fewer words</t>
+          <t>Every wait says what is happening</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -8709,7 +8793,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -8721,12 +8805,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>NF-10.10</t>
+          <t>NF-10.8</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -8741,12 +8825,12 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>The build carries the picture on</t>
+          <t>Pause and resume while answering the interview</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -8767,7 +8851,7 @@
       <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -8779,12 +8863,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>NF-10.11</t>
+          <t>NF-10.9</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -8799,22 +8883,22 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>The last signup screen: KPIs and "What Dex built"</t>
+          <t>Basics and the language pick: pictures, fewer words</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -8825,7 +8909,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -8837,12 +8921,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>NF-10.12</t>
+          <t>NF-10.10</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -8857,12 +8941,12 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>The team map: hand-offs along the ring, plain panel</t>
+          <t>The build carries the picture on</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -8872,7 +8956,7 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -8883,7 +8967,7 @@
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - f65c54a.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -8895,12 +8979,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>NF-10.13</t>
+          <t>NF-10.11</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -8910,27 +8994,27 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -8941,7 +9025,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 2b395c6.</t>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -8953,12 +9037,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>NF-10.14</t>
+          <t>NF-10.12</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -8973,22 +9057,22 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>The first-week tour, inside the real desktop app</t>
+          <t>The team map: hand-offs along the ring, plain panel</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -8999,7 +9083,7 @@
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+          <t>Done 2026-10-29 - f65c54a.</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -9011,12 +9095,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>NF-10.15</t>
+          <t>NF-10.13</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -9031,22 +9115,22 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>The tour pointed at the wrong things and drew its own UI</t>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -9057,7 +9141,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c.</t>
+          <t>Done 2026-10-30 - 2b395c6.</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -9069,12 +9153,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>NF-10.16</t>
+          <t>NF-10.14</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -9084,17 +9168,17 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Desktop opens the phone's task view</t>
+          <t>The first-week tour, inside the real desktop app</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -9104,7 +9188,7 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -9115,7 +9199,7 @@
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -9127,12 +9211,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>NF-10.17</t>
+          <t>NF-10.15</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -9142,22 +9226,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Desktop list cards are the phone's task card</t>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -9173,7 +9257,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-30 - 0f1438c.</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -9185,12 +9269,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>NF-10.18</t>
+          <t>NF-10.16</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -9200,27 +9284,27 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>A proof photo tapped on the phone opened nothing</t>
+          <t>Desktop opens the phone's task view</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -9231,7 +9315,7 @@
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -9243,12 +9327,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>NF-10.19</t>
+          <t>NF-10.17</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -9258,17 +9342,17 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>A camera button beside attach</t>
+          <t>Desktop list cards are the phone's task card</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -9278,7 +9362,7 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -9289,7 +9373,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -9301,12 +9385,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>NF-10.20</t>
+          <t>NF-10.18</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -9321,17 +9405,17 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>The phone froze grey on Decide's "What you said"</t>
+          <t>A proof photo tapped on the phone opened nothing</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -9347,7 +9431,7 @@
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9359,12 +9443,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>NF-10.21</t>
+          <t>NF-10.19</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -9374,22 +9458,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>DecisionOS 1.1.0 release build</t>
+          <t>A camera button beside attach</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -9405,7 +9489,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30.</t>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -9417,12 +9501,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>NF-10.22</t>
+          <t>NF-10.20</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -9432,22 +9516,22 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Decide and Ask show a translation, not the words spoken</t>
+          <t>The phone froze grey on Decide's "What you said"</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -9457,13 +9541,13 @@
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Waiting on the founder's call (2026-10-30).</t>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -9475,12 +9559,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>NF-10.23</t>
+          <t>NF-10.21</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Railway backend</t>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -9490,22 +9574,22 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Deploy the backend for the interview's live pieces</t>
+          <t>DecisionOS 1.1.0 release build</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -9515,18 +9599,670 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
+          <t>Done 2026-10-30.</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.22</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Decide and Ask show a translation, not the words spoken</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr"/>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Waiting on the founder's call (2026-10-30).</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.23</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Railway backend</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Deploy the backend for the interview's live pieces</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr"/>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
           <t>Needs a deploy go-ahead.</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="L141" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-29/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.1</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py Company.managers / level / ladder</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Decisions / Team</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>The team's managers, from Reports to</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="n"/>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Decisions / Work</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Work nobody has goes to the team's queue</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.1</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.3</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Take it</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.4</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>It keeps asking until someone has it</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.5</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Needs a person on the Desk</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.6</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>The review says where each task will go</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.7</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>Older work joins its queue; tests and browser check</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.8</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Reminders climb the reporting tree, one level a day</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.4</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.9</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Finance / Work</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Finance follow-ups join the Finance queue</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 16 of 17 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17).</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 18 of 19 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17), task steps drafted only when someone asks Dex (NF-4.18), Ops KPIs as rates (NF-4.19).</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 16 of 17 Done</t>
+          <t>In progress -- 18 of 19 Done</t>
         </is>
       </c>
     </row>
@@ -1145,6 +1145,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
@@ -1240,7 +1241,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 140 of 149 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
+          <t>Epic 11 progress: 142 of 151 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
         </is>
       </c>
     </row>
@@ -1392,14 +1393,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1655,7 +1656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4523,32 +4524,30 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-4.18</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>services/auto_plan.py; pages/MyWork.js; pages/mywork/WorkDeck.jsx; pages/Settings.js AutoStepsCard; models/tenant.py auto_plan_steps</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tasks / AI cost</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>One delete for every door</t>
+          <t>Task steps are drafted only when someone asks Dex</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+          <t>Fix (AI spend). Founder 2026-10-30: 'I don't want that automatically creating of execution steps. It should be an optional thing - we can't spend much on AI.' Finding: every task got an AI call for its checklist - on creation from every path (New Task, decision tasks, a task added to a decision, follow-ups, a routine's next occurrence, a locked task once approved), plus a background sweep (8 recent tasks per company per tick), plus My Work asking for up to 10 cards on screen and the task asking again when opened. Once per task (stamped), but a failed draft was retried up to 3 times. Now none of that runs unless an owner turns on Settings &gt; Task steps from Dex (tenant.auto_plan_steps, off by default). Ask Dex in the task (one call, on the tap) and Add manually are unchanged; a task with no steps says 'No steps yet. Add your own in Steps, or let Dex draft them.'</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -4558,7 +4557,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4569,44 +4568,42 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-30 (fix). Scratch backend: a new task had no steps and no stamp 8s later; opening My Work and the task made no AI request; Add manually + Ask Dex shown; one tap of Ask Dex = one request, 8 steps; Settings card Off. test_dex_drafts_the_checklist_on_its_own.py: off by default (no draft on creation, My Work or sweep; zero AI calls), the screens; existing drafting tests run with the company opted in.</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-4.19</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>services/operating_score.py _company_operating_view, _score_sales; pages/OperatingScore.js CATS; lib/neuglassScore.js</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops / KPIs</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>Ops KPIs are rates: Responsiveness no longer stuck at 0</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Fix. Founder 2026-10-30: 'Responsiveness is still zero - how are we calculating it, and are the other KPIs right?' Findings: Responsiveness = 100 - open complaints x 12 - overdue tasks x 3 subtracted COUNTS, so any company of real size read 0 for good (Tracole: 54 of 605 open tasks late, 9%, scored 0). Finance took 5 points per overdue invoice (a count) and summed every incoming payment - advances, standalone income, payments matched to no invoice - so it disagreed with Finance's own Outstanding. Decisions = approved / all scored a rejection as a failure. Execution (completion minus overdue share) was already a rate and is unchanged. Now: Responsiveness = on-time rate (dated work done by its date; open work past it counts late) x 70% + complaints resolved x 30% (on-time alone with no complaints; nothing judged yet = not scored); Finance = money received on due invoices / money due, read off the invoices like Finance's Outstanding, with money received but matched to no invoice named on the page; Decisions = decided (approved or rejected) / raised. Stats.outstanding uses Finance's definition. Task/decision reads raised from 2,000 to 20,000 (Tracole is at 1,736 tasks).</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -4624,31 +4621,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-30 (fix). Dev data (old -&gt; new): Tracole Responsiveness 0 -&gt; 41, Decisions 90 -&gt; 100, Finance on its books 11 (most payments unmatched to invoices; the page now says so). Scratch Ops page: Responsiveness 13 (not 0) with 14% on time, categories and hints read the new definitions. test_pilot1_operating_score.py: 4 new cases (rate not count, complaints 30%, finance on invoices + unmatched named, a rejection is a decision); test_ops_answers_for_a_period.py dates made relative (a fixed 25 Sep date had aged out).</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4663,12 +4656,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -4678,7 +4671,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4686,14 +4679,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.2</t>
-        </is>
-      </c>
+      <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4705,12 +4694,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4720,17 +4709,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -4767,12 +4756,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4787,22 +4776,22 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -4812,7 +4801,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -4829,12 +4818,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4844,22 +4833,22 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4891,12 +4880,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4906,22 +4895,22 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4953,12 +4942,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4968,27 +4957,27 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4996,7 +4985,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -5011,30 +5004,32 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>6</v>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -5044,7 +5039,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -5052,45 +5047,51 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -5108,22 +5109,22 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n"/>
+      <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5141,22 +5142,22 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -5179,12 +5180,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -5192,17 +5193,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -5212,7 +5213,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -5235,12 +5236,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -5248,17 +5249,17 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -5291,12 +5292,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5304,17 +5305,17 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5324,7 +5325,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5347,12 +5348,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -5360,27 +5361,27 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -5403,12 +5404,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5421,12 +5422,12 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5436,7 +5437,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -5459,12 +5460,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5477,17 +5478,17 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5515,12 +5516,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5528,17 +5529,17 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -5548,7 +5549,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5571,12 +5572,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5584,17 +5585,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -5627,12 +5628,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5640,27 +5641,27 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5683,12 +5684,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5696,22 +5697,22 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5739,12 +5740,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5752,27 +5753,27 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5795,12 +5796,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5808,17 +5809,17 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5851,12 +5852,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5869,22 +5870,22 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -5907,12 +5908,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -5920,22 +5921,22 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5963,12 +5964,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -5976,27 +5977,27 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -6019,12 +6020,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -6032,17 +6033,17 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -6057,13 +6058,13 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -6075,12 +6076,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -6088,38 +6089,38 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -6131,35 +6132,35 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6169,53 +6170,53 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6225,30 +6226,30 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -6261,12 +6262,12 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6299,12 +6300,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6317,12 +6318,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6355,12 +6356,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6373,12 +6374,12 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6411,12 +6412,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6429,12 +6430,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6444,7 +6445,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -6467,12 +6468,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6485,17 +6486,17 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6523,12 +6524,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6536,17 +6537,17 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6579,12 +6580,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6592,27 +6593,27 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6623,7 +6624,7 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -6635,12 +6636,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -6648,17 +6649,17 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -6668,7 +6669,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6679,7 +6680,7 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -6691,12 +6692,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -6704,17 +6705,17 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6735,7 +6736,7 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -6747,12 +6748,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6760,27 +6761,27 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6791,7 +6792,7 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -6803,12 +6804,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6816,27 +6817,27 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6847,7 +6848,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -6859,40 +6860,40 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -6903,52 +6904,52 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -6959,24 +6960,24 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -6984,17 +6985,17 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -7004,7 +7005,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -7015,7 +7016,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -7027,12 +7028,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -7040,27 +7041,27 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -7071,7 +7072,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -7083,12 +7084,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -7096,27 +7097,27 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -7127,7 +7128,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -7139,12 +7140,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -7152,17 +7153,17 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -7183,7 +7184,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -7195,12 +7196,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -7208,17 +7209,17 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -7228,7 +7229,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -7239,7 +7240,7 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -7251,12 +7252,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -7264,17 +7265,17 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -7295,7 +7296,7 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -7307,12 +7308,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7320,27 +7321,27 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7351,7 +7352,7 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -7363,12 +7364,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7381,22 +7382,22 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -7419,12 +7420,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7432,17 +7433,17 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -7452,7 +7453,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7475,12 +7476,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7488,22 +7489,22 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -7531,12 +7532,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7549,22 +7550,22 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -7575,7 +7576,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7587,12 +7588,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7600,17 +7601,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7620,7 +7621,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -7643,12 +7644,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7656,22 +7657,22 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -7687,7 +7688,7 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -7699,12 +7700,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7712,22 +7713,22 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -7743,7 +7744,7 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -7755,12 +7756,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -7768,27 +7769,27 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -7799,7 +7800,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7811,12 +7812,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
@@ -7829,12 +7830,12 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -7844,7 +7845,7 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -7855,7 +7856,7 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -7867,12 +7868,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
@@ -7880,27 +7881,27 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -7911,7 +7912,7 @@
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -7923,12 +7924,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -7936,22 +7937,22 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -7967,7 +7968,7 @@
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -7979,35 +7980,35 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Settings / Finance</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Financial year starts in (company setting)</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8020,59 +8021,55 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-8.20</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+          <t>index.css (sky)</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Overview opens on the financial year; every quarter and half</t>
+          <t>No amber glow; Notifications wears Finance's sky</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -8080,31 +8077,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>NF-9.1</t>
-        </is>
-      </c>
+      <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>NF-9.3</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
@@ -8112,17 +8105,17 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Finance / UI</t>
+          <t>Settings / Finance</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>The period picker: kind, then which one</t>
+          <t>Financial year starts in (company setting)</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -8132,7 +8125,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -8142,7 +8135,7 @@
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
@@ -8159,12 +8152,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>NF-9.4</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -8177,12 +8170,12 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>It rolls over by itself</t>
+          <t>Overview opens on the financial year; every quarter and half</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -8192,7 +8185,7 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -8219,12 +8212,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>NF-9.5</t>
+          <t>NF-9.3</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
@@ -8232,17 +8225,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance / UI</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Date tests and checks</t>
+          <t>The period picker: kind, then which one</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -8252,7 +8245,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -8279,12 +8272,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>NF-9.6</t>
+          <t>NF-9.4</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
@@ -8297,12 +8290,12 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>One period for all of Finance</t>
+          <t>It rolls over by itself</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -8312,7 +8305,7 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -8322,29 +8315,29 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>NF-9.7</t>
+          <t>NF-9.5</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -8352,17 +8345,17 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Finance / AI</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>A bill is read, then confirmed</t>
+          <t>Date tests and checks</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -8372,7 +8365,7 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
@@ -8387,54 +8380,52 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>NF-10.1</t>
+          <t>NF-9.6</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Dex widget</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Dex on the Android home screen</t>
+          <t>One period for all of Finance</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -8442,47 +8433,49 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J119" s="4" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>NF-10.2</t>
+          <t>NF-9.7</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>DexQuickActivity.java, AndroidManifest.xml</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Finance / AI</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>The widget layer opened black</t>
+          <t>A bill is read, then confirmed</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -8492,7 +8485,7 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -8500,27 +8493,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>NF-10.3</t>
+          <t>NF-10.1</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -8530,17 +8527,17 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex widget</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+          <t>Dex on the Android home screen</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -8550,7 +8547,7 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -8561,7 +8558,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -8573,12 +8570,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>NF-10.4</t>
+          <t>NF-10.2</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -8588,22 +8585,22 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Signup background: a drawn blueprint, not a photograph</t>
+          <t>The widget layer opened black</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -8619,7 +8616,7 @@
       <c r="J122" s="4" t="inlineStr"/>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
@@ -8631,12 +8628,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>NF-10.5</t>
+          <t>NF-10.3</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -8646,27 +8643,27 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>"Your OS, taking shape" beside every signup step</t>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -8677,7 +8674,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -8689,12 +8686,12 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6</t>
+          <t>NF-10.4</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -8709,22 +8706,22 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Each interview answer names what it added to the OS</t>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -8735,7 +8732,7 @@
       <c r="J124" s="4" t="inlineStr"/>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
@@ -8747,12 +8744,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>NF-10.7</t>
+          <t>NF-10.5</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -8762,17 +8759,17 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Every wait says what is happening</t>
+          <t>"Your OS, taking shape" beside every signup step</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -8782,7 +8779,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -8793,7 +8790,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -8805,12 +8802,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>NF-10.8</t>
+          <t>NF-10.6</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -8825,22 +8822,22 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume while answering the interview</t>
+          <t>Each interview answer names what it added to the OS</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -8851,7 +8848,7 @@
       <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -8863,12 +8860,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>NF-10.9</t>
+          <t>NF-10.7</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -8878,27 +8875,27 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Basics and the language pick: pictures, fewer words</t>
+          <t>Every wait says what is happening</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -8909,7 +8906,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -8921,12 +8918,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>NF-10.10</t>
+          <t>NF-10.8</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -8941,12 +8938,12 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>The build carries the picture on</t>
+          <t>Pause and resume while answering the interview</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -8967,7 +8964,7 @@
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -8979,12 +8976,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>NF-10.11</t>
+          <t>NF-10.9</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -8999,22 +8996,22 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>The last signup screen: KPIs and "What Dex built"</t>
+          <t>Basics and the language pick: pictures, fewer words</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -9025,7 +9022,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -9037,12 +9034,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>NF-10.12</t>
+          <t>NF-10.10</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -9057,12 +9054,12 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>The team map: hand-offs along the ring, plain panel</t>
+          <t>The build carries the picture on</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -9072,7 +9069,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -9083,7 +9080,7 @@
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - f65c54a.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -9095,12 +9092,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>NF-10.13</t>
+          <t>NF-10.11</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -9110,27 +9107,27 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -9141,7 +9138,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 2b395c6.</t>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -9153,12 +9150,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>NF-10.14</t>
+          <t>NF-10.12</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -9173,22 +9170,22 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>The first-week tour, inside the real desktop app</t>
+          <t>The team map: hand-offs along the ring, plain panel</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -9199,7 +9196,7 @@
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+          <t>Done 2026-10-29 - f65c54a.</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -9211,12 +9208,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>NF-10.15</t>
+          <t>NF-10.13</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -9231,22 +9228,22 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>The tour pointed at the wrong things and drew its own UI</t>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -9257,7 +9254,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c.</t>
+          <t>Done 2026-10-30 - 2b395c6.</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -9269,12 +9266,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>NF-10.16</t>
+          <t>NF-10.14</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -9284,17 +9281,17 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Desktop opens the phone's task view</t>
+          <t>The first-week tour, inside the real desktop app</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -9304,7 +9301,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -9315,7 +9312,7 @@
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -9327,12 +9324,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>NF-10.17</t>
+          <t>NF-10.15</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -9342,22 +9339,22 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Desktop list cards are the phone's task card</t>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -9373,7 +9370,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-30 - 0f1438c.</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -9385,12 +9382,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>NF-10.18</t>
+          <t>NF-10.16</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -9400,27 +9397,27 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>A proof photo tapped on the phone opened nothing</t>
+          <t>Desktop opens the phone's task view</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -9431,7 +9428,7 @@
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9443,12 +9440,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>NF-10.19</t>
+          <t>NF-10.17</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -9458,17 +9455,17 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>A camera button beside attach</t>
+          <t>Desktop list cards are the phone's task card</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -9478,7 +9475,7 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
@@ -9489,7 +9486,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -9501,12 +9498,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>NF-10.20</t>
+          <t>NF-10.18</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -9521,17 +9518,17 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>The phone froze grey on Decide's "What you said"</t>
+          <t>A proof photo tapped on the phone opened nothing</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -9547,7 +9544,7 @@
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -9559,12 +9556,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>NF-10.21</t>
+          <t>NF-10.19</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -9574,22 +9571,22 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>DecisionOS 1.1.0 release build</t>
+          <t>A camera button beside attach</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -9605,7 +9602,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30.</t>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -9617,12 +9614,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>NF-10.22</t>
+          <t>NF-10.20</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -9632,22 +9629,22 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Decide and Ask show a translation, not the words spoken</t>
+          <t>The phone froze grey on Decide's "What you said"</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -9657,13 +9654,13 @@
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Waiting on the founder's call (2026-10-30).</t>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -9675,12 +9672,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>NF-10.23</t>
+          <t>NF-10.21</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Railway backend</t>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -9690,22 +9687,22 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Deploy the backend for the interview's live pieces</t>
+          <t>DecisionOS 1.1.0 release build</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -9715,13 +9712,13 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>Needs a deploy go-ahead.</t>
+          <t>Done 2026-10-30.</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -9733,35 +9730,37 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>NF-11.1</t>
+          <t>NF-10.22</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py Company.managers / level / ladder</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="n">
-        <v>11</v>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Team</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>The team's managers, from Reports to</t>
+          <t>Decide and Ask show a translation, not the words spoken</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -9771,90 +9770,88 @@
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J142" s="4" t="n"/>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
+          <t>Waiting on the founder's call (2026-10-30).</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-10.23</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="n">
-        <v>11</v>
+          <t>Railway backend</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Work</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Work nobody has goes to the team's queue</t>
+          <t>Deploy the backend for the interview's live pieces</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.1</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
+          <t>Needs a deploy go-ahead.</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>NF-11.3</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
+          <t>services/task_pickup.py Company.managers / level / ladder</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
@@ -9862,17 +9859,17 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Decisions / Team</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Take it</t>
+          <t>The team's managers, from Reports to</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
+          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -9882,7 +9879,7 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I144" s="11" t="inlineStr">
@@ -9890,14 +9887,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -9909,12 +9902,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
+          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
@@ -9922,17 +9915,17 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Decisions / Work</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>It keeps asking until someone has it</t>
+          <t>Work nobody has goes to the team's queue</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -9942,7 +9935,7 @@
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
@@ -9952,12 +9945,12 @@
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -9969,12 +9962,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>NF-11.5</t>
+          <t>NF-11.3</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
+          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
@@ -9982,17 +9975,17 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Needs a person on the Desk</t>
+          <t>Take it</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -10017,7 +10010,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -10029,12 +10022,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>NF-11.6</t>
+          <t>NF-11.4</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
         </is>
       </c>
       <c r="C147" s="4" t="n">
@@ -10042,27 +10035,27 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Work / Notifications</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>The review says where each task will go</t>
+          <t>It keeps asking until someone has it</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
@@ -10077,7 +10070,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -10089,12 +10082,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>NF-11.7</t>
+          <t>NF-11.5</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
@@ -10102,17 +10095,17 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Older work joins its queue; tests and browser check</t>
+          <t>Needs a person on the Desk</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -10137,7 +10130,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
@@ -10149,12 +10142,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>NF-11.8</t>
+          <t>NF-11.6</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
@@ -10162,27 +10155,27 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Decisions</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Reminders climb the reporting tree, one level a day</t>
+          <t>The review says where each task will go</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr">
@@ -10192,12 +10185,12 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -10209,12 +10202,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>NF-11.9</t>
+          <t>NF-11.7</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
@@ -10222,45 +10215,165 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Older work joins its queue; tests and browser check</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.8</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>Reminders climb the reporting tree, one level a day</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.4</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.9</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
           <t>Finance / Work</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
+      <c r="E152" s="4" t="inlineStr">
         <is>
           <t>Finance follow-ups join the Finance queue</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr">
+      <c r="F152" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
         </is>
       </c>
-      <c r="G150" s="4" t="inlineStr">
+      <c r="G152" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr">
+      <c r="H152" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I150" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
         <is>
           <t>NF-11.2</t>
         </is>
       </c>
-      <c r="K150" s="4" t="inlineStr">
+      <c r="K152" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
         </is>
       </c>
-      <c r="L150" s="4" t="inlineStr">
+      <c r="L152" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30</t>
         </is>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>21 of 23 Done; open: NF-10.22 transcription mode (founder), NF-10.23 backend deploy</t>
+          <t>26 of 28 Done; open: NF-10.22 transcription mode (founder), NF-10.23 backend deploy</t>
         </is>
       </c>
     </row>
@@ -1241,10 +1241,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 142 of 151 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 11 progress: 147 of 156 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1591,14 +1592,14 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1608,7 +1609,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Signup redrawn as the company's OS taking shape (blueprint ground, the OS canvas fed by every answer, waits that say what is happening, interview pause, the summary with KPIs and the What Dex built explorer); the first-week tour over the real desktop app; Dex on the Android home screen; desktop takes the phone's task view and card; a camera beside attach; the phone's grey freeze on Decide fixed; release 1.1.0. Open: transcription mode (founder's call), backend deploy.</t>
+          <t>Signup redrawn as the company's OS taking shape (blueprint ground, the OS canvas fed by every answer, waits that say what is happening, interview pause, the summary with KPIs and the What Dex built explorer); the first-week tour over the real desktop app; Dex on the Android home screen; desktop takes the phone's task view and card; a camera beside attach; the phone's grey freeze on Decide fixed; release 1.1.0; then the desktop task card (one steps bar, every card the same shape, priority as a bottom glow) and desktop My Work as the Workspace with the owner's team board. Open: transcription mode (founder's call), backend deploy.</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L152"/>
+  <dimension ref="A1:L157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9846,35 +9847,37 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>NF-11.1</t>
+          <t>NF-10.24</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py Company.managers / level / ladder</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Team</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>The team's managers, from Reports to</t>
+          <t>Desktop task card: one steps bar, no Next action or buttons</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
+          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -9887,10 +9890,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J144" s="4" t="n"/>
+      <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -9902,40 +9905,42 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-10.25</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Work</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Work nobody has goes to the team's queue</t>
+          <t>Desktop task cards all the same shape</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
+          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
@@ -9943,14 +9948,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.1</t>
-        </is>
-      </c>
+      <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -9962,40 +9963,42 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>NF-11.3</t>
+          <t>NF-10.26</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Take it</t>
+          <t>Priority as a glow along the card's bottom edge</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
+          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I146" s="11" t="inlineStr">
@@ -10003,14 +10006,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -10022,35 +10021,37 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-10.27</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>It keeps asking until someone has it</t>
+          <t>Desktop My Work becomes the Workspace</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -10063,14 +10064,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -10082,35 +10079,37 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>NF-11.5</t>
+          <t>NF-10.28</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Needs a person on the Desk</t>
+          <t>The owner's team board</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -10123,14 +10122,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
@@ -10142,12 +10137,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>NF-11.6</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+          <t>services/task_pickup.py Company.managers / level / ladder</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
@@ -10155,22 +10150,22 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Decisions / Team</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>The review says where each task will go</t>
+          <t>The team's managers, from Reports to</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -10183,14 +10178,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -10202,12 +10193,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>NF-11.7</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
@@ -10215,17 +10206,17 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Decisions / Work</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Older work joins its queue; tests and browser check</t>
+          <t>Work nobody has goes to the team's queue</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -10235,7 +10226,7 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr">
@@ -10245,12 +10236,12 @@
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -10262,12 +10253,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>NF-11.8</t>
+          <t>NF-11.3</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
@@ -10275,17 +10266,17 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Reminders climb the reporting tree, one level a day</t>
+          <t>Take it</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -10305,12 +10296,12 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -10322,12 +10313,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>NF-11.9</t>
+          <t>NF-11.4</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
@@ -10335,45 +10326,345 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>It keeps asking until someone has it</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.5</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>Needs a person on the Desk</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.6</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>The review says where each task will go</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.7</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>Older work joins its queue; tests and browser check</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.8</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Reminders climb the reporting tree, one level a day</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.4</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.9</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
           <t>Finance / Work</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t>Finance follow-ups join the Finance queue</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr">
+      <c r="F157" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
         </is>
       </c>
-      <c r="G152" s="4" t="inlineStr">
+      <c r="G157" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
+      <c r="H157" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I152" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
         <is>
           <t>NF-11.2</t>
         </is>
       </c>
-      <c r="K152" s="4" t="inlineStr">
+      <c r="K157" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
         </is>
       </c>
-      <c r="L152" s="4" t="inlineStr">
+      <c r="L157" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30</t>
         </is>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 18 of 19 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17), task steps drafted only when someone asks Dex (NF-4.18), Ops KPIs as rates (NF-4.19).</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 23 of 24 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17), task steps drafted only when someone asks Dex (NF-4.18), Ops KPIs as rates (NF-4.19), New Task's team line, one place to approve requests, repeating tasks from the Decision Desk and the drawer, a Repeating filter (NF-4.20 to 4.24).</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 18 of 19 Done</t>
+          <t>In progress -- 23 of 24 Done</t>
         </is>
       </c>
     </row>
@@ -1241,11 +1241,10 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 147 of 156 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 11 progress: 152 of 161 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1394,14 +1393,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1657,7 +1656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L157"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4637,42 +4636,40 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-4.20</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>pages/Tasks.js NewTaskDialog (team line, group label)</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>One delete for every door</t>
+          <t>New Task's team line says where the task really goes</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+          <t>Fix. Found in the 2026-10-30 workflow/UX check: picking a team in New Task said 'Goes to whoever in Sales has the least open work' and the group read 'A team (least busy person)' — the rule Epic 11 Sprint 11 removed. The line now follows services/task_pickup: the team's one person ('Goes straight to Priya Nair, the only one in Sales'), nobody in it (the owner is asked), high priority (its managers are asked at once), else the queue. Neutral ('Goes to the Sales team') while the people list is still loading, so it never claims nobody is there.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4680,57 +4677,59 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Epic 11 S11</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-31. Browser walk on the scratch DB (demo owner), 22 checks, all pass: the Sales line reads 'Goes straight to Priya Nair, the only one in Sales.'; the group reads 'A team (its queue)'. The walk caught the loading-race wording, fixed the same day.</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-4.21</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>pages/Requests.js, components/requests/RequestsPanel.jsx</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Requests / Approvals</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>One place to approve: Requests loses its own 'To approve' tab</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Fix. Founder: 'everything goes to Approvals — why is there a separate approval here? And what does to be paid mean?' The phone's Requests page had a 'To approve' tab, a second door to the queue Approvals → Requests already holds (the desktop never had it). Removed; when something waits on you the page says 'N requests waiting for your approval — you approve them in Approvals' and links there. An old ?tab=approvals link (a notification already sent) lands in /approvals?sub=requests. 'To pay' is now 'Waiting for payment' (Finance's), with one line: approved; pay or buy each one, then Mark paid closes the request and its expense. The requester's tile reads 'Approved, awaiting payment'.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -4738,51 +4737,45 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-31. Browser walk on the scratch DB (demo owner), 22 checks, all pass: desktop and phone Requests show Mine / Waiting for payment / All, no approve tab; the hint shows; ?tab=approvals&amp;request=… redirects to Approvals → Requests with the request kept.</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-4.22</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>services/recurrence.from_words, services/voice.task_repeat + build_proposal + _create_decision_tasks + _reuse_existing_task, prompts/extraction 1.4, decision_flow.edit_proposal_task, DexReview, DecisionDialog, lib/repeat.js</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Decision Desk / Tasks</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>The Decision Desk makes repeating tasks ('every Monday')</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>Fix. Founder: tasks are mostly made from the Decision Desk, and 'check the stock every Monday' became a one-off — the Desk had no notion of a repeat. The extraction asks for repeat/repeat_interval (prompt 1.4) and the task's own words are read as well (from_words: daily, every Monday, on Mondays, weekly, every other Friday, fortnightly, the 20th of every month, monthly, quarterly; 'on Monday' alone stays one-off). The series starts on the day the words name (next Monday / next 20th), else the date said, else today. The review shows it and has a Repeats picker per task (desktop panel and phone review); approving makes a repeating task like New Task's; a reused existing task ('Use that task') becomes the routine, and a decision silent about a cadence never stops one.</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -4800,61 +4793,55 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.2</t>
-        </is>
-      </c>
+      <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-31. tests/test_routines_from_the_desk.py (30): words heard / one-offs not, the model's repeat wins, proposal first day, reviewer changes + timeline, approve -&gt; routine -&gt; close brings the next, no-date routine dated today, reused task becomes the routine. Browser walk on the scratch DB (demo owner), 22 checks, all pass: a typed capture 'check the finished goods stock every Monday … call Kumar Exports on Monday' came back with the stock check 'Every week' due Mon 2 Nov and the call 'Just once'; changed to every 2 weeks in the panel, held by the server, shown on /decisions/:id; approval made the routine. The phone review (DexReview) is built but not driven by script (the phone Dex opens by voice).</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-4.23</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>routers/tasks.update_task, services/tasks.edit_refusal, pages/MyWork.js RepeatLine + task hero, pages/Tasks.js</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>A task that exists can be made to repeat, or its cadence changed</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>Fix. The drawer offered only 'Stop repeating'; a cadence could be set only in New Task, and the Repeats row there stayed hidden until a date was picked. PATCH /tasks takes repeat_every / repeat_interval / repeat_until ('' = one-off), keeps the series id, needs an open dated task; who may change it is who may move the date (stopping included — before, anyone on the task could stop a routine). The drawer's top card has 'Repeats [Just once / Every day / week / 2 weeks / month / 3 months]' under the due date for them; New Task shows Repeats from the start.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -4862,56 +4849,50 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-31. tests/test_routines_from_the_desk.py: start, change, back to one-off, routine started later brings the next, needs a date and an open task, only the date's people. Browser walk on the scratch DB (demo owner), 22 checks, all pass: the drawer made a task weekly then every 2 weeks (API confirms, same series); New Task shows Repeats before a date.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-4.24</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>pages/MyWork.js STATUS_FILTER_OPTIONS, pages/mywork/WorkspaceHub.jsx</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>My Work: a 'Repeating' filter</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>Fix. There was nowhere to see every routine (the GST filing, the Monday stock count). 'Repeating' joins the status filter: a tile on the desktop Workspace fence (teal) and an entry in the phone's filter.</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4924,31 +4905,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-31. Browser walk on the scratch DB (demo owner), 22 checks, all pass: the Repeating tile lists the routine made in the drawer.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Founder 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4963,22 +4940,22 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4986,14 +4963,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -5005,12 +4978,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5020,17 +4993,17 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -5040,7 +5013,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -5067,12 +5040,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5082,17 +5055,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -5102,7 +5075,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -5110,7 +5083,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.2</t>
+        </is>
+      </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -5125,30 +5102,32 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>6</v>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -5166,50 +5145,56 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>6</v>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -5222,45 +5207,51 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J62" s="4" t="n"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>6</v>
+          <t>routers/finance_trash.py everything / export</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -5270,7 +5261,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5278,45 +5269,51 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n"/>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>6</v>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5326,7 +5323,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5334,50 +5331,56 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J64" s="4" t="n"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5390,27 +5393,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n"/>
+      <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -5418,17 +5421,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5461,12 +5464,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5474,17 +5477,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5494,7 +5497,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5517,12 +5520,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5530,27 +5533,27 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5573,12 +5576,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5586,27 +5589,27 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -5629,12 +5632,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5642,27 +5645,27 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5685,12 +5688,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5698,22 +5701,22 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5741,12 +5744,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5754,27 +5757,27 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5797,12 +5800,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5810,17 +5813,17 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5830,7 +5833,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -5853,12 +5856,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5866,22 +5869,22 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5909,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -5922,17 +5925,17 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5965,12 +5968,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -5978,17 +5981,17 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -5998,7 +6001,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -6021,12 +6024,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -6034,17 +6037,17 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -6054,7 +6057,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -6077,12 +6080,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -6090,17 +6093,17 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -6133,12 +6136,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -6151,17 +6154,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6171,13 +6174,13 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -6189,12 +6192,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -6207,33 +6210,33 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -6245,40 +6248,40 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -6289,52 +6292,52 @@
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -6345,42 +6348,42 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6401,136 +6404,136 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6543,12 +6546,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6581,12 +6584,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6599,22 +6602,22 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6637,12 +6640,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -6650,17 +6653,17 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -6693,12 +6696,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -6706,17 +6709,17 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6726,7 +6729,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6737,7 +6740,7 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -6749,12 +6752,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6762,17 +6765,17 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6782,7 +6785,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6793,7 +6796,7 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -6805,12 +6808,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6818,17 +6821,17 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6838,7 +6841,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6849,7 +6852,7 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -6861,12 +6864,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6874,17 +6877,17 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -6905,7 +6908,7 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -6917,12 +6920,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -6930,22 +6933,22 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -6961,7 +6964,7 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -6973,30 +6976,30 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -7017,42 +7020,42 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -7073,42 +7076,42 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -7118,7 +7121,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -7129,42 +7132,42 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -7185,52 +7188,52 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -7241,24 +7244,24 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -7266,27 +7269,27 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -7297,7 +7300,7 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -7309,12 +7312,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7322,27 +7325,27 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7353,7 +7356,7 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -7365,12 +7368,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7378,22 +7381,22 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -7409,7 +7412,7 @@
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -7421,12 +7424,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7434,27 +7437,27 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7465,7 +7468,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -7477,12 +7480,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7490,22 +7493,22 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -7521,7 +7524,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -7533,12 +7536,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7546,22 +7549,22 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -7577,7 +7580,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7589,12 +7592,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7602,17 +7605,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7622,7 +7625,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -7645,12 +7648,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7658,27 +7661,27 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -7701,12 +7704,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7714,27 +7717,27 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -7745,7 +7748,7 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -7757,12 +7760,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -7770,22 +7773,22 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -7801,7 +7804,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7813,12 +7816,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
@@ -7826,17 +7829,17 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -7857,7 +7860,7 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -7869,12 +7872,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
@@ -7882,27 +7885,27 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -7913,7 +7916,7 @@
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -7925,12 +7928,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -7938,22 +7941,22 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -7969,7 +7972,7 @@
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -7981,12 +7984,12 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
@@ -7994,17 +7997,17 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -8014,7 +8017,7 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -8037,12 +8040,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
@@ -8055,17 +8058,17 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -8081,7 +8084,7 @@
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -8093,30 +8096,30 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Settings / Finance</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Financial year starts in (company setting)</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -8126,7 +8129,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -8134,49 +8137,45 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Overview opens on the financial year; every quarter and half</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -8194,49 +8193,45 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>NF-9.1</t>
-        </is>
-      </c>
+      <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>NF-9.3</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Finance / UI</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>The period picker: kind, then which one</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -8246,7 +8241,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -8254,54 +8249,50 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>NF-9.1</t>
-        </is>
-      </c>
+      <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>NF-9.4</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>It rolls over by itself</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -8314,54 +8305,50 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>NF-9.1</t>
-        </is>
-      </c>
+      <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>NF-9.5</t>
+          <t>NF-8.20</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+          <t>index.css (sky)</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Date tests and checks</t>
+          <t>No amber glow; Notifications wears Finance's sky</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -8374,31 +8361,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>NF-9.1</t>
-        </is>
-      </c>
+      <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>NF-9.6</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
@@ -8406,17 +8389,17 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Settings / Finance</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>One period for all of Finance</t>
+          <t>Financial year starts in (company setting)</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -8426,7 +8409,7 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -8436,29 +8419,29 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>NF-9.7</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
@@ -8466,17 +8449,17 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Finance / AI</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>A bill is read, then confirmed</t>
+          <t>Overview opens on the financial year; every quarter and half</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -8501,54 +8484,52 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>NF-10.1</t>
+          <t>NF-9.3</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Dex widget</t>
+          <t>Finance / UI</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Dex on the Android home screen</t>
+          <t>The period picker: kind, then which one</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -8556,47 +8537,49 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J121" s="4" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>NF-10.2</t>
+          <t>NF-9.4</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>DexQuickActivity.java, AndroidManifest.xml</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>The widget layer opened black</t>
+          <t>It rolls over by itself</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -8614,52 +8597,54 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J122" s="4" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>NF-10.3</t>
+          <t>NF-9.5</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+          <t>Date tests and checks</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -8672,57 +8657,59 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J123" s="4" t="inlineStr"/>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>NF-10.4</t>
+          <t>NF-9.6</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Signup background: a drawn blueprint, not a photograph</t>
+          <t>One period for all of Finance</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -8730,47 +8717,49 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.2</t>
+        </is>
+      </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>NF-10.5</t>
+          <t>NF-9.7</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Finance / AI</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>"Your OS, taking shape" beside every signup step</t>
+          <t>A bill is read, then confirmed</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -8780,7 +8769,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -8788,27 +8777,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J125" s="4" t="inlineStr"/>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6</t>
+          <t>NF-10.1</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -8818,27 +8811,27 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Dex widget</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Each interview answer names what it added to the OS</t>
+          <t>Dex on the Android home screen</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -8849,7 +8842,7 @@
       <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -8861,12 +8854,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>NF-10.7</t>
+          <t>NF-10.2</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -8876,17 +8869,17 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Every wait says what is happening</t>
+          <t>The widget layer opened black</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -8896,7 +8889,7 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -8907,7 +8900,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -8919,12 +8912,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>NF-10.8</t>
+          <t>NF-10.3</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -8934,17 +8927,17 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume while answering the interview</t>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -8965,7 +8958,7 @@
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -8977,12 +8970,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>NF-10.9</t>
+          <t>NF-10.4</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -8997,17 +8990,17 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Basics and the language pick: pictures, fewer words</t>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -9023,7 +9016,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -9035,12 +9028,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>NF-10.10</t>
+          <t>NF-10.5</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -9055,22 +9048,22 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>The build carries the picture on</t>
+          <t>"Your OS, taking shape" beside every signup step</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -9081,7 +9074,7 @@
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -9093,12 +9086,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>NF-10.11</t>
+          <t>NF-10.6</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -9113,12 +9106,12 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>The last signup screen: KPIs and "What Dex built"</t>
+          <t>Each interview answer names what it added to the OS</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -9128,7 +9121,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -9139,7 +9132,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -9151,12 +9144,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>NF-10.12</t>
+          <t>NF-10.7</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -9166,22 +9159,22 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>The team map: hand-offs along the ring, plain panel</t>
+          <t>Every wait says what is happening</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -9197,7 +9190,7 @@
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - f65c54a.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -9209,12 +9202,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>NF-10.13</t>
+          <t>NF-10.8</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -9224,17 +9217,17 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+          <t>Pause and resume while answering the interview</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -9255,7 +9248,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 2b395c6.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -9267,12 +9260,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>NF-10.14</t>
+          <t>NF-10.9</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -9287,22 +9280,22 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>The first-week tour, inside the real desktop app</t>
+          <t>Basics and the language pick: pictures, fewer words</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -9313,7 +9306,7 @@
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -9325,12 +9318,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>NF-10.15</t>
+          <t>NF-10.10</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -9340,27 +9333,27 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>The tour pointed at the wrong things and drew its own UI</t>
+          <t>The build carries the picture on</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -9371,7 +9364,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -9383,12 +9376,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>NF-10.16</t>
+          <t>NF-10.11</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -9398,17 +9391,17 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Desktop opens the phone's task view</t>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -9418,7 +9411,7 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -9429,7 +9422,7 @@
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9441,12 +9434,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>NF-10.17</t>
+          <t>NF-10.12</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -9456,17 +9449,17 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Desktop list cards are the phone's task card</t>
+          <t>The team map: hand-offs along the ring, plain panel</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -9487,7 +9480,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-29 - f65c54a.</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -9499,12 +9492,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>NF-10.18</t>
+          <t>NF-10.13</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -9519,12 +9512,12 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>A proof photo tapped on the phone opened nothing</t>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -9545,7 +9538,7 @@
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-30 - 2b395c6.</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -9557,12 +9550,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>NF-10.19</t>
+          <t>NF-10.14</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -9572,27 +9565,27 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>A camera button beside attach</t>
+          <t>The first-week tour, inside the real desktop app</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
@@ -9603,7 +9596,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -9615,12 +9608,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>NF-10.20</t>
+          <t>NF-10.15</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -9635,12 +9628,12 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>The phone froze grey on Decide's "What you said"</t>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -9650,7 +9643,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I140" s="11" t="inlineStr">
@@ -9661,7 +9654,7 @@
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+          <t>Done 2026-10-30 - 0f1438c.</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -9673,12 +9666,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>NF-10.21</t>
+          <t>NF-10.16</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -9688,17 +9681,17 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>DecisionOS 1.1.0 release build</t>
+          <t>Desktop opens the phone's task view</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -9708,7 +9701,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
@@ -9719,7 +9712,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30.</t>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -9731,12 +9724,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>NF-10.22</t>
+          <t>NF-10.17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -9746,17 +9739,17 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Decide and Ask show a translation, not the words spoken</t>
+          <t>Desktop list cards are the phone's task card</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -9766,18 +9759,18 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Waiting on the founder's call (2026-10-30).</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
@@ -9789,12 +9782,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>NF-10.23</t>
+          <t>NF-10.18</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Railway backend</t>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -9804,17 +9797,17 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Deploy the backend for the interview's live pieces</t>
+          <t>A proof photo tapped on the phone opened nothing</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -9829,13 +9822,13 @@
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>Needs a deploy go-ahead.</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -9847,12 +9840,12 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>NF-10.24</t>
+          <t>NF-10.19</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -9862,17 +9855,17 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Desktop task card: one steps bar, no Next action or buttons</t>
+          <t>A camera button beside attach</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -9893,24 +9886,24 @@
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>NF-10.25</t>
+          <t>NF-10.20</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -9920,22 +9913,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Desktop task cards all the same shape</t>
+          <t>The phone froze grey on Decide's "What you said"</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -9951,24 +9944,24 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2.</t>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>NF-10.26</t>
+          <t>NF-10.21</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -9978,22 +9971,22 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Priority as a glow along the card's bottom edge</t>
+          <t>DecisionOS 1.1.0 release build</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -10009,24 +10002,24 @@
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
+          <t>Done 2026-10-30.</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>NF-10.27</t>
+          <t>NF-10.22</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -10036,17 +10029,17 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Desktop My Work becomes the Workspace</t>
+          <t>Decide and Ask show a translation, not the words spoken</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -10056,35 +10049,35 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
+          <t>Waiting on the founder's call (2026-10-30).</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>NF-10.28</t>
+          <t>NF-10.23</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+          <t>Railway backend</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -10094,17 +10087,17 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>The owner's team board</t>
+          <t>Deploy the backend for the interview's live pieces</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -10114,58 +10107,60 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2.</t>
+          <t>Needs a deploy go-ahead.</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>NF-11.1</t>
+          <t>NF-10.24</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py Company.managers / level / ladder</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Team</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>The team's managers, from Reports to</t>
+          <t>Desktop task card: one steps bar, no Next action or buttons</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
+          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -10178,10 +10173,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J149" s="4" t="n"/>
+      <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -10193,40 +10188,42 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-10.25</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Work</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Work nobody has goes to the team's queue</t>
+          <t>Desktop task cards all the same shape</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
+          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr">
@@ -10234,14 +10231,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.1</t>
-        </is>
-      </c>
+      <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -10253,40 +10246,42 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>NF-11.3</t>
+          <t>NF-10.26</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Take it</t>
+          <t>Priority as a glow along the card's bottom edge</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
+          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr">
@@ -10294,14 +10289,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -10313,35 +10304,37 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-10.27</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>It keeps asking until someone has it</t>
+          <t>Desktop My Work becomes the Workspace</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -10354,14 +10347,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
         </is>
       </c>
       <c r="L152" s="4" t="inlineStr">
@@ -10373,35 +10362,37 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>NF-11.5</t>
+          <t>NF-10.28</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Needs a person on the Desk</t>
+          <t>The owner's team board</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -10414,14 +10405,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -10433,12 +10420,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>NF-11.6</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+          <t>services/task_pickup.py Company.managers / level / ladder</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
@@ -10446,22 +10433,22 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Decisions / Team</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>The review says where each task will go</t>
+          <t>The team's managers, from Reports to</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -10474,14 +10461,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.2</t>
-        </is>
-      </c>
+      <c r="J154" s="4" t="n"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
@@ -10493,12 +10476,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>NF-11.7</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
@@ -10506,17 +10489,17 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Decisions / Work</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Older work joins its queue; tests and browser check</t>
+          <t>Work nobody has goes to the team's queue</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -10526,7 +10509,7 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I155" s="11" t="inlineStr">
@@ -10536,12 +10519,12 @@
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -10553,12 +10536,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>NF-11.8</t>
+          <t>NF-11.3</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
@@ -10566,17 +10549,17 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Reminders climb the reporting tree, one level a day</t>
+          <t>Take it</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -10596,12 +10579,12 @@
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
@@ -10613,12 +10596,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>NF-11.9</t>
+          <t>NF-11.4</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
@@ -10626,45 +10609,345 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>It keeps asking until someone has it</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.5</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Needs a person on the Desk</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.6</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>The review says where each task will go</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.7</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>Older work joins its queue; tests and browser check</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.8</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Reminders climb the reporting tree, one level a day</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.4</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.9</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
           <t>Finance / Work</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>Finance follow-ups join the Finance queue</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
         </is>
       </c>
-      <c r="G157" s="4" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H157" s="4" t="inlineStr">
+      <c r="H162" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I157" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
+      <c r="I162" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
         <is>
           <t>NF-11.2</t>
         </is>
       </c>
-      <c r="K157" s="4" t="inlineStr">
+      <c r="K162" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
         </is>
       </c>
-      <c r="L157" s="4" t="inlineStr">
+      <c r="L162" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30</t>
         </is>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -535,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -548,7 +546,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -561,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -574,7 +570,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -582,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -638,7 +632,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -694,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -750,7 +742,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -766,7 +757,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>routers/desk.py, routers/tasks.py, hooks/useUiScale.js, services/ingestion.py, pages/Captures.js, components/mobile/Walkthrough.jsx, lib/native/files.js, services/finance_trash.py</t>
+          <t>routers/desk.py, routers/tasks.py, hooks/useUiScale.js, services/ingestion.py, pages/Captures.js, components/mobile/Walkthrough.jsx, lib/native/files.js, services/finance_trash.py, routers/invoicing.py</t>
         </is>
       </c>
     </row>
@@ -802,11 +793,10 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 23 of 24 Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
+          <t>In progress -- 24 of 25 Done</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -862,7 +852,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
@@ -918,7 +907,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
@@ -1033,7 +1021,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
@@ -1089,7 +1076,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
@@ -1145,7 +1131,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
@@ -1198,6 +1183,62 @@
       <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Done -- 9 of 9 (feature)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 12 -- Everything links to CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>services/parties.py (new), prompts/extraction.py, services/voice.py, services/decision_flow.py, services/enrich.py, services/tasks.py, services/ingestion.py, routers/contacts.py, routers/crm.py, routers/finance.py, routers/tasks.py, routers/decisions.py, components/party/* (new), lib/party.js (new), components/DecisionDialog.js, pages/desk/DexReview.jsx, pages/Tasks.js, pages/MyWork.js, pages/CRM.js, pages/ContactProfile.js, pages/mobile/ContactProfileMobile.jsx, pages/Desk.js, App.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31: what the Decision Desk hears about a customer or supplier must connect to CRM, and missing details must be asked for. Decisions (0 of 486), tasks (0 of 2,009) and meetings were never linked; Tracole had 647 tasks naming a CRM party. Dex proposes, the person decides, nothing new reaches CRM without the review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>docs/CRM_LINKS_PLAN.md (the eight pieces and every edge case)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Done -- 8 of 8 (feature)</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1241,7 +1282,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 152 of 161 items Done  (94%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature).</t>
+          <t>Epic 11 progress: 161 of 170 items Done  (95%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature), Sprint 12 Everything links to CRM (feature).</t>
         </is>
       </c>
     </row>
@@ -1393,10 +1434,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1410,7 +1451,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Substantial bugs fixed along the way: the client's four fixes from the Play Store build (Delayed vs Overdue, people on a task, the Workflows tile, phone scale with a bigger font), the XCODITS QA bugs (BUG-16, BUG-04, BUG-14, ACCESS-12, BUG-15), App Store 5.1.2 AI consent, the old Finance delete, files saving inside the app. Open: WhatsApp gave no reply to a PDF (2026-10-22).</t>
+          <t>Substantial bugs fixed along the way: the client's four fixes from the Play Store build (Delayed vs Overdue, people on a task, the Workflows tile, phone scale with a bigger font), the XCODITS QA bugs (BUG-16, BUG-04, BUG-14, ACCESS-12, BUG-15), App Store 5.1.2 AI consent, the old Finance delete, files saving inside the app, seven single-process tests nobody was running. Open: WhatsApp gave no reply to a PDF (2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -1642,6 +1683,39 @@
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Feature: tasks never sit with nobody (decisions, stages, New Task, Finance follow-ups). Named person, else the team's one person, else the team's queue (Take it); high priority asks the nearest managers; no team asks the owner. Never by load. Reminders climb the reporting tree one level a day, the owner last. Needs a person on the Desk. Plan: docs/WORK_NOBODY_HAS.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sprint 12</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Everything links to CRM</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Every decision, task, meeting and workflow about an outside party carries its CRM record: one matcher, Dex names the party, the review decides (every edge case changeable), approval links, Needs details followed up, New Task field, the page reads links, old data by review.</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4920,42 +4994,40 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-4.25</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>routers/invoicing.py create_gst_invoice; tests (ai_keys, finance_says_what_is_true_now, founder_mobile, member_loop, rbac_p2)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tests / Security</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>One delete for every door</t>
+          <t>Seven single-process tests that never ran under xdist were failing</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+          <t>Fix. The files marked skip-under-xdist only run with -n 0, so the normal suite never saw them; all 7 failed on 137bc230 too. One real regression: create_gst_invoice (fdb0e10d, 2026-10-08) read the whole tenant record, AI keys included, which the keys-stay-on-the-server guard forbids -- it now reads only name, invoice_prefix, state, currency, payment_terms_days. Six stale tests, each behind a deliberate change, updated with a dated comment: finance analysis x3 (Audit F-06, 1dc4bf39: a company with no records is answered without the AI and not stored -- the tests now put a sale on the books), Login verify x2 (a735f5b4: it sends `code`, the code as typed, not `otpCode`), owner exclusions (Audit B-10, 32d28bca: the only owner confirms a self-exclusion with confirm_self after a 409).</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4963,27 +5035,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-31. All 7 pass with -n 0; full suite and every single-process file green apart from the two known cross-loop flakes.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Single-process run 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4998,12 +5070,12 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -5013,7 +5085,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -5021,14 +5093,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5040,12 +5108,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5060,12 +5128,12 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -5085,7 +5153,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -5102,12 +5170,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -5117,17 +5185,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -5147,7 +5215,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -5164,12 +5232,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -5179,27 +5247,27 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -5226,12 +5294,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5246,12 +5314,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -5261,7 +5329,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5288,12 +5356,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -5303,27 +5371,27 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5350,12 +5418,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -5365,17 +5433,17 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -5393,7 +5461,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -5408,30 +5480,32 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5441,7 +5515,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -5449,27 +5523,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J66" s="4" t="n"/>
+      <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -5482,12 +5556,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5497,7 +5571,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5520,12 +5594,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5538,17 +5612,17 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5576,12 +5650,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5589,27 +5663,27 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -5632,12 +5706,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5650,22 +5724,22 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5688,12 +5762,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5701,27 +5775,27 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -5744,12 +5818,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5762,12 +5836,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -5800,12 +5874,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5818,12 +5892,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5833,7 +5907,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -5856,12 +5930,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5874,22 +5948,22 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -5912,12 +5986,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -5925,22 +5999,22 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5968,12 +6042,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -5981,22 +6055,22 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6024,12 +6098,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -6037,17 +6111,17 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -6057,7 +6131,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -6080,12 +6154,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -6093,27 +6167,27 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -6136,12 +6210,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -6149,17 +6223,17 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -6192,12 +6266,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -6210,12 +6284,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -6248,12 +6322,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -6266,22 +6340,22 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -6304,12 +6378,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6317,17 +6391,17 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6337,7 +6411,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -6360,12 +6434,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6373,22 +6447,22 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6416,12 +6490,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6429,22 +6503,22 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6454,13 +6528,13 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -6472,12 +6546,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6490,22 +6564,22 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -6528,68 +6602,68 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -6602,12 +6676,12 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -6617,7 +6691,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6640,12 +6714,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -6658,12 +6732,12 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -6673,7 +6747,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6696,12 +6770,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -6714,12 +6788,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6729,7 +6803,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6752,12 +6826,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6770,12 +6844,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6785,7 +6859,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6808,12 +6882,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6826,12 +6900,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6864,12 +6938,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6882,17 +6956,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -6920,12 +6994,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -6933,22 +7007,22 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -6976,12 +7050,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -6989,17 +7063,17 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -7009,7 +7083,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -7020,7 +7094,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -7032,12 +7106,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -7050,12 +7124,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -7076,7 +7150,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -7088,12 +7162,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -7101,17 +7175,17 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -7132,7 +7206,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -7144,12 +7218,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -7157,27 +7231,27 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -7188,7 +7262,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -7200,12 +7274,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -7213,22 +7287,22 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7244,7 +7318,7 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -7256,40 +7330,40 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -7300,24 +7374,24 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -7330,12 +7404,12 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -7368,12 +7442,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7381,17 +7455,17 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -7401,7 +7475,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -7412,7 +7486,7 @@
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -7424,12 +7498,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7437,22 +7511,22 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -7468,7 +7542,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -7480,12 +7554,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7493,17 +7567,17 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -7513,7 +7587,7 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -7524,7 +7598,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -7536,12 +7610,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7549,17 +7623,17 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -7569,7 +7643,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -7580,7 +7654,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7592,12 +7666,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7610,12 +7684,12 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7636,7 +7710,7 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7648,12 +7722,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7661,17 +7735,17 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -7704,12 +7778,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7722,22 +7796,22 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -7748,7 +7822,7 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -7760,12 +7834,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -7778,12 +7852,12 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -7793,7 +7867,7 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -7804,7 +7878,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7816,12 +7890,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
@@ -7829,17 +7903,17 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -7849,7 +7923,7 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -7860,7 +7934,7 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -7872,12 +7946,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
@@ -7890,22 +7964,22 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -7916,7 +7990,7 @@
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -7928,12 +8002,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -7946,17 +8020,17 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -7984,12 +8058,12 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
@@ -7997,27 +8071,27 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -8040,12 +8114,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
@@ -8053,17 +8127,17 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -8073,7 +8147,7 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -8084,7 +8158,7 @@
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -8096,12 +8170,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
@@ -8109,27 +8183,27 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -8140,7 +8214,7 @@
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
@@ -8152,12 +8226,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -8165,17 +8239,17 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -8196,7 +8270,7 @@
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -8208,12 +8282,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
@@ -8221,17 +8295,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -8241,7 +8315,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -8252,7 +8326,7 @@
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
@@ -8264,12 +8338,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
@@ -8282,17 +8356,17 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -8308,7 +8382,7 @@
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -8320,12 +8394,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -8333,22 +8407,22 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -8364,7 +8438,7 @@
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -8376,35 +8450,35 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-8.20</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+          <t>index.css (sky)</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Settings / Finance</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Financial year starts in (company setting)</t>
+          <t>No amber glow; Notifications wears Finance's sky</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -8417,31 +8491,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
@@ -8449,17 +8519,17 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Settings / Finance</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Overview opens on the financial year; every quarter and half</t>
+          <t>Financial year starts in (company setting)</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -8469,7 +8539,7 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -8479,7 +8549,7 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
@@ -8496,12 +8566,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>NF-9.3</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
@@ -8509,17 +8579,17 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Finance / UI</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>The period picker: kind, then which one</t>
+          <t>Overview opens on the financial year; every quarter and half</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -8556,12 +8626,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>NF-9.4</t>
+          <t>NF-9.3</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
@@ -8569,17 +8639,17 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / UI</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>It rolls over by itself</t>
+          <t>The period picker: kind, then which one</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -8589,7 +8659,7 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -8616,12 +8686,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>NF-9.5</t>
+          <t>NF-9.4</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
@@ -8629,17 +8699,17 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Date tests and checks</t>
+          <t>It rolls over by itself</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -8676,12 +8746,12 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>NF-9.6</t>
+          <t>NF-9.5</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
@@ -8689,17 +8759,17 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>One period for all of Finance</t>
+          <t>Date tests and checks</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -8709,7 +8779,7 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -8719,29 +8789,29 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>NF-9.7</t>
+          <t>NF-9.6</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
@@ -8749,17 +8819,17 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Finance / AI</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>A bill is read, then confirmed</t>
+          <t>One period for all of Finance</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -8779,59 +8849,57 @@
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>NF-10.1</t>
+          <t>NF-9.7</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Dex widget</t>
+          <t>Finance / AI</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Dex on the Android home screen</t>
+          <t>A bill is read, then confirmed</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -8839,27 +8907,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>NF-10.2</t>
+          <t>NF-10.1</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DexQuickActivity.java, AndroidManifest.xml</t>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -8869,27 +8941,27 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Dex widget</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>The widget layer opened black</t>
+          <t>Dex on the Android home screen</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -8900,7 +8972,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -8912,12 +8984,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>NF-10.3</t>
+          <t>NF-10.2</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -8927,22 +8999,22 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+          <t>The widget layer opened black</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -8958,7 +9030,7 @@
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -8970,12 +9042,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>NF-10.4</t>
+          <t>NF-10.3</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -8985,17 +9057,17 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Signup background: a drawn blueprint, not a photograph</t>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -9016,7 +9088,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -9028,12 +9100,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>NF-10.5</t>
+          <t>NF-10.4</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -9048,22 +9120,22 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>"Your OS, taking shape" beside every signup step</t>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -9074,7 +9146,7 @@
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -9086,12 +9158,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6</t>
+          <t>NF-10.5</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -9106,12 +9178,12 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Each interview answer names what it added to the OS</t>
+          <t>"Your OS, taking shape" beside every signup step</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -9121,7 +9193,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -9132,7 +9204,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -9144,12 +9216,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>NF-10.7</t>
+          <t>NF-10.6</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -9159,17 +9231,17 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Every wait says what is happening</t>
+          <t>Each interview answer names what it added to the OS</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -9190,7 +9262,7 @@
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -9202,12 +9274,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>NF-10.8</t>
+          <t>NF-10.7</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -9217,27 +9289,27 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume while answering the interview</t>
+          <t>Every wait says what is happening</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -9248,7 +9320,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -9260,12 +9332,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>NF-10.9</t>
+          <t>NF-10.8</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -9280,17 +9352,17 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Basics and the language pick: pictures, fewer words</t>
+          <t>Pause and resume while answering the interview</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -9306,7 +9378,7 @@
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -9318,12 +9390,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>NF-10.10</t>
+          <t>NF-10.9</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -9338,17 +9410,17 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>The build carries the picture on</t>
+          <t>Basics and the language pick: pictures, fewer words</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -9364,7 +9436,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -9376,12 +9448,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>NF-10.11</t>
+          <t>NF-10.10</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -9396,22 +9468,22 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>The last signup screen: KPIs and "What Dex built"</t>
+          <t>The build carries the picture on</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -9422,7 +9494,7 @@
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9434,12 +9506,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>NF-10.12</t>
+          <t>NF-10.11</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -9454,22 +9526,22 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>The team map: hand-offs along the ring, plain panel</t>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
@@ -9480,7 +9552,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - f65c54a.</t>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -9492,12 +9564,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>NF-10.13</t>
+          <t>NF-10.12</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -9507,17 +9579,17 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+          <t>The team map: hand-offs along the ring, plain panel</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -9527,7 +9599,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I138" s="11" t="inlineStr">
@@ -9538,7 +9610,7 @@
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 2b395c6.</t>
+          <t>Done 2026-10-29 - f65c54a.</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -9550,12 +9622,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>NF-10.14</t>
+          <t>NF-10.13</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -9565,27 +9637,27 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>The first-week tour, inside the real desktop app</t>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
@@ -9596,7 +9668,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+          <t>Done 2026-10-30 - 2b395c6.</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -9608,12 +9680,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>NF-10.15</t>
+          <t>NF-10.14</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -9623,17 +9695,17 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>The tour pointed at the wrong things and drew its own UI</t>
+          <t>The first-week tour, inside the real desktop app</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -9643,7 +9715,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I140" s="11" t="inlineStr">
@@ -9654,7 +9726,7 @@
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c.</t>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -9666,12 +9738,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>NF-10.16</t>
+          <t>NF-10.15</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -9681,17 +9753,17 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Desktop opens the phone's task view</t>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -9712,7 +9784,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+          <t>Done 2026-10-30 - 0f1438c.</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -9724,12 +9796,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>NF-10.17</t>
+          <t>NF-10.16</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -9744,17 +9816,17 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Desktop list cards are the phone's task card</t>
+          <t>Desktop opens the phone's task view</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -9770,7 +9842,7 @@
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
@@ -9782,12 +9854,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>NF-10.18</t>
+          <t>NF-10.17</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -9797,17 +9869,17 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>A proof photo tapped on the phone opened nothing</t>
+          <t>Desktop list cards are the phone's task card</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -9817,7 +9889,7 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
@@ -9840,12 +9912,12 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>NF-10.19</t>
+          <t>NF-10.18</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -9855,17 +9927,17 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>A camera button beside attach</t>
+          <t>A proof photo tapped on the phone opened nothing</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -9886,7 +9958,7 @@
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -9898,12 +9970,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>NF-10.20</t>
+          <t>NF-10.19</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -9913,22 +9985,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>The phone froze grey on Decide's "What you said"</t>
+          <t>A camera button beside attach</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -9944,7 +10016,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -9956,12 +10028,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>NF-10.21</t>
+          <t>NF-10.20</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -9971,17 +10043,17 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>DecisionOS 1.1.0 release build</t>
+          <t>The phone froze grey on Decide's "What you said"</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -10002,7 +10074,7 @@
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30.</t>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -10014,12 +10086,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>NF-10.22</t>
+          <t>NF-10.21</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -10029,22 +10101,22 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Decide and Ask show a translation, not the words spoken</t>
+          <t>DecisionOS 1.1.0 release build</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -10054,13 +10126,13 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Waiting on the founder's call (2026-10-30).</t>
+          <t>Done 2026-10-30.</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -10072,12 +10144,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>NF-10.23</t>
+          <t>NF-10.22</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Railway backend</t>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -10092,12 +10164,12 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Deploy the backend for the interview's live pieces</t>
+          <t>Decide and Ask show a translation, not the words spoken</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -10118,7 +10190,7 @@
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Needs a deploy go-ahead.</t>
+          <t>Waiting on the founder's call (2026-10-30).</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
@@ -10130,12 +10202,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>NF-10.24</t>
+          <t>NF-10.23</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
+          <t>Railway backend</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -10145,17 +10217,17 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Desktop task card: one steps bar, no Next action or buttons</t>
+          <t>Deploy the backend for the interview's live pieces</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -10170,30 +10242,30 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
+          <t>Needs a deploy go-ahead.</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>NF-10.25</t>
+          <t>NF-10.24</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -10203,22 +10275,22 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Desktop task cards all the same shape</t>
+          <t>Desktop task card: one steps bar, no Next action or buttons</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
+          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -10234,7 +10306,7 @@
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -10246,12 +10318,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>NF-10.26</t>
+          <t>NF-10.25</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -10266,12 +10338,12 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Priority as a glow along the card's bottom edge</t>
+          <t>Desktop task cards all the same shape</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
+          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -10292,7 +10364,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -10304,12 +10376,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>NF-10.27</t>
+          <t>NF-10.26</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -10319,27 +10391,27 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Desktop My Work becomes the Workspace</t>
+          <t>Priority as a glow along the card's bottom edge</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
+          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr">
@@ -10350,7 +10422,7 @@
       <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
         </is>
       </c>
       <c r="L152" s="4" t="inlineStr">
@@ -10362,12 +10434,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>NF-10.28</t>
+          <t>NF-10.27</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -10382,12 +10454,12 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>The owner's team board</t>
+          <t>Desktop My Work becomes the Workspace</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
+          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -10408,7 +10480,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -10420,40 +10492,42 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>NF-11.1</t>
+          <t>NF-10.28</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py Company.managers / level / ladder</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Team</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>The team's managers, from Reports to</t>
+          <t>The owner's team board</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
+          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I154" s="11" t="inlineStr">
@@ -10461,10 +10535,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J154" s="4" t="n"/>
+      <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
@@ -10476,12 +10550,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
+          <t>services/task_pickup.py Company.managers / level / ladder</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
@@ -10489,17 +10563,17 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Work</t>
+          <t>Decisions / Team</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Work nobody has goes to the team's queue</t>
+          <t>The team's managers, from Reports to</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
+          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -10509,7 +10583,7 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I155" s="11" t="inlineStr">
@@ -10517,14 +10591,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.1</t>
-        </is>
-      </c>
+      <c r="J155" s="4" t="n"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -10536,12 +10606,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>NF-11.3</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
+          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
@@ -10549,17 +10619,17 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Decisions / Work</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Take it</t>
+          <t>Work nobody has goes to the team's queue</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
+          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -10569,7 +10639,7 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I156" s="11" t="inlineStr">
@@ -10579,12 +10649,12 @@
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
@@ -10596,12 +10666,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.3</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
+          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
@@ -10609,17 +10679,17 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>It keeps asking until someone has it</t>
+          <t>Take it</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -10644,7 +10714,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -10656,12 +10726,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>NF-11.5</t>
+          <t>NF-11.4</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
+          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
@@ -10669,17 +10739,17 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Work / Notifications</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Needs a person on the Desk</t>
+          <t>It keeps asking until someone has it</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -10704,7 +10774,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
@@ -10716,12 +10786,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>NF-11.6</t>
+          <t>NF-11.5</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
@@ -10729,27 +10799,27 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>The review says where each task will go</t>
+          <t>Needs a person on the Desk</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr">
@@ -10764,7 +10834,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -10776,12 +10846,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>NF-11.7</t>
+          <t>NF-11.6</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
@@ -10789,27 +10859,27 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Decisions</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Older work joins its queue; tests and browser check</t>
+          <t>The review says where each task will go</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr">
@@ -10824,7 +10894,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
         </is>
       </c>
       <c r="L160" s="4" t="inlineStr">
@@ -10836,12 +10906,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>NF-11.8</t>
+          <t>NF-11.7</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
@@ -10849,17 +10919,17 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Reminders climb the reporting tree, one level a day</t>
+          <t>Older work joins its queue; tests and browser check</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -10879,12 +10949,12 @@
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -10896,12 +10966,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>NF-11.9</t>
+          <t>NF-11.8</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
@@ -10909,47 +10979,555 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
+          <t>Work / Notifications</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>Reminders climb the reporting tree, one level a day</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I162" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.4</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.9</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
           <t>Finance / Work</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
+      <c r="E163" s="4" t="inlineStr">
         <is>
           <t>Finance follow-ups join the Finance queue</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
         </is>
       </c>
-      <c r="G162" s="4" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H162" s="4" t="inlineStr">
+      <c r="H163" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I162" s="11" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
         <is>
           <t>NF-11.2</t>
         </is>
       </c>
-      <c r="K162" s="4" t="inlineStr">
+      <c r="K163" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
         </is>
       </c>
-      <c r="L162" s="4" t="inlineStr">
+      <c r="L163" s="4" t="inlineStr">
         <is>
           <t>Founder 2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.1</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>services/parties.py (new); services/ingestion.py</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Matching</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>One matcher decides who a customer or supplier is</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>Dex, New Task, the old-data review and Finance's bill import ask services/parties the same question, so a party is never made twice. It drops Pvt/Ltd/M/s, matches whole identifying words ('Toyota' = Toyota Kirloskar Pvt Ltd) and close spellings ('Kumar Exprts'); two possible records -&gt; 'Which one?', never a guess; one of the team, our own company or generic words ('the exporters') are never a party. It never writes.</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I164" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="n"/>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): variants, Which one?, kind settles it, team/own/generic guards, close spelling, whole-name scan.</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.2</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>prompts/extraction.py 1.5; services/voice.build_proposal</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>Decision Desk / Dex</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>Dex names who each task, meeting and workflow is about</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>Extraction 1.5 asks each task for party, party_kind (customer, dealer, supplier, prospect) and party_person, meetings for their party, workflow events for the counterparty's kind. A task Dex gave no party is scanned for a CRM name in its own words; a task tied to a workflow card takes the card's party.</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="n"/>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): linked, Which one?, new prospect with its person, a name in the title, 'tell Ravi' stays unlinked.</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.3</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>components/party/* (new); DecisionDialog.js; pages/desk/DexReview.jsx; PATCH /decisions/{id}/proposal/party</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Decision Desk / Review</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>The review shows the party and every guess can be changed</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>A chip per item: 'Kumar Exports · Customer' (with 'matched from Toyota'), 'New: ... · details needed', 'Which Kumar?', '2 customers named'. The party dialog: pick the record, add as new, change the kind, keep or drop the person at the firm, split a task naming several into one each, or 'Not a customer or supplier'. One answer applies to every item naming that party. Approving with a question open asks first: pick now, or approve and link later.</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="n"/>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25). Browser walk on the scratch DB: Which Kumar? picked, split into 2, kind -&gt; Dealer, approve.</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.4</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>services/parties.settle; services/voice.materialize_proposal; services/decision_flow</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>Decision Desk / CRM</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Approval links everything; a new party is one Needs-details record</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>On approval the tasks, meetings, workflow cards and the decision (contact_ids) get the CRM record. A party nobody had becomes ONE record marked Needs details, with the person named there and the decision it came from; found again first, so a second approval links. Nothing is created on reject; an open question is left unlinked for the review. The timeline says 'Added to CRM - details needed: ...'.</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="n"/>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); scratch DB: 5 tasks linked, Nippon Audiotronix made once (dealer, Sajith).</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.5</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>routers/contacts (needs-details, list filter, phone clears it); POST /tasks/{id}/party-details; NeedsDetailsCard; PartyDetailsPrompt; CRM.js</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Follow-up</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>Missing details are followed up</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Desk card '3 new customers/suppliers need details' (people with that side of CRM). When a task about one is done, the doer is asked for phone, GST and address (blank fields only, no CRM access needed; 'Later' or 'Nothing to add'). CRM has a Needs details filter that opens on the tab holding them. Saving a phone clears the flag.</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="n"/>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); browser: card -&gt; CRM filter (Partners tab), finish -&gt; prompt -&gt; saved, flag cleared.</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.6</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>pages/Tasks.js NewTaskDialog; pages/MyWork.js PartyLine; routers/tasks (_task_party); GET /parties/search</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>New Task and the task drawer carry a Customer / supplier field</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>Search CRM (name and kind only, so anyone who makes work can link it) or add new right there with its kind. The title is read as it is typed: 'Send the quote to Toyota Kirloskar' offers it in one tap. The drawer shows the chip and can change or remove it; only people with a say on the task, refused before any record is made.</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="n"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); browser: title suggestion linked Toyota Kirloskar Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.7</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>routers/finance.contact_profile; routers/crm activity; ContactProfile.js; ContactProfileMobile.jsx; PartyChip</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Contact page</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>The customer/supplier page reads links, opens for CRM, money stays Finance</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>It found tasks and decisions by searching titles for the name ('Ravi Traders' showed the employee Ravi's work) and opened only with Finance. Now: linked tasks, decisions, meetings and workflows, for anyone with that side of CRM; invoices, payments, bills, totals, prices and the AI score only with Finance ('Money is visible to Finance'). Chips on tasks and decisions open it.</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="n"/>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): links not titles, CRM sees no money, Finance does, other side refused.</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.8</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>GET/POST /crm/link-suggestions; components/party/LinkSuggestionsDialog; CRM.js 'Link old work'</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Old data</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Old data gets a review list, not silent changes</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>Tasks, decisions and workflow cards written before this name parties only in words. The review lists those naming exactly one CRM record by its whole name (never an employee's name, never two firms), grouped by record, all ticked; untick any, Link. A link made meanwhile is never replaced; only the sides of CRM the person holds.</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="n"/>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): suggested only on one whole name; applied only when ticked; never replaces.</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-31</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -546,6 +548,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -558,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -570,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
@@ -577,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -632,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -687,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
@@ -742,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -797,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -852,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
@@ -907,6 +918,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
@@ -1021,6 +1033,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
@@ -1076,6 +1089,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
@@ -1131,6 +1145,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
@@ -1202,7 +1217,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>services/parties.py (new), prompts/extraction.py, services/voice.py, services/decision_flow.py, services/enrich.py, services/tasks.py, services/ingestion.py, routers/contacts.py, routers/crm.py, routers/finance.py, routers/tasks.py, routers/decisions.py, components/party/* (new), lib/party.js (new), components/DecisionDialog.js, pages/desk/DexReview.jsx, pages/Tasks.js, pages/MyWork.js, pages/CRM.js, pages/ContactProfile.js, pages/mobile/ContactProfileMobile.jsx, pages/Desk.js, App.js</t>
+          <t>services/parties.py (new), prompts/extraction.py, services/voice.py, services/decision_flow.py, services/enrich.py, services/tasks.py, services/ingestion.py, routers/contacts.py, routers/crm.py, routers/finance.py, routers/tasks.py, routers/decisions.py, components/party/* (new), lib/party.js (new), components/DecisionDialog.js, pages/desk/DexReview.jsx, pages/Tasks.js, pages/MyWork.js, pages/CRM.js, pages/ContactProfile.js, pages/mobile/ContactProfileMobile.jsx, pages/Desk.js, App.js, components/party/PartySheet.jsx (new), pages/mywork/WorkDeck.jsx, pages/Workflows.js, pages/Calendar.js, routers/workflows.py, routers/calendar.py</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1253,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Done -- 8 of 8 (feature)</t>
+          <t>Done -- 12 of 12 (feature, then the follow-through NF-12.9..12.12)</t>
         </is>
       </c>
     </row>
@@ -1282,10 +1297,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 161 of 170 items Done  (95%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature), Sprint 12 Everything links to CRM (feature).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 11 progress: 165 of 174 items Done  (95%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature), Sprint 12 Everything links to CRM (feature).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1698,10 +1714,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1715,7 +1731,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Every decision, task, meeting and workflow about an outside party carries its CRM record: one matcher, Dex names the party, the review decides (every edge case changeable), approval links, Needs details followed up, New Task field, the page reads links, old data by review.</t>
+          <t>Every decision, task, meeting and workflow about an outside party carries its CRM record: one matcher, Dex names the party, the review decides (every edge case changeable), approval links, Needs details followed up, New Task field, the page reads links, old data by review. Then the follow-through: the details prompt from every way a task is finished, the party chip on every card, Details are complete in CRM, and the party windows as the app's own glass and phone sheets.</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:L175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11531,6 +11547,230 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.9</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>pages/mywork/WorkDeck.jsx TaskSummaryCard patch(); pages/MyWork.js bulk Complete and setStatus</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Follow-up</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>Finishing a task anywhere asks for the missing details</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>The details prompt was only asked from the task drawer's slider. Now also from the card's Mark complete (the phone's usual way to finish), the bulk Complete bar (asked once, for the first finished task whose party needs details) and the drawer's status picker. On a phone it follows the full-screen tick.</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="n"/>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (polish after the feature). tests/test_crm_links_reach_every_card.py (7); visual QA on desktop and phone.</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>Team brief 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.10</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>components/party/PartyChip.jsx, lib/party.js; WorkDeck card, MyWork tile, Workflows.js, Calendar.js; routers/workflows.py contact_summary, routers/calendar.py party, services/tasks.contact_chips</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Everywhere</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>Every card shows who the work is about</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>Task cards (phone deck, desktop list, approvals tile), workflow cards and calendar meetings wear the party chip with the record's own kind (a supplier is never called a customer); it opens their page. Additive API fields: GET /workflows contact_summary, GET /calendar party on meetings. The chip lets only the name shorten (the kind always shows), puts 'matched from' on its own line, and a question to answer (Which Kumar?) is ink, apart from the amber New.</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="n"/>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (polish after the feature). tests/test_crm_links_reach_every_card.py (7); visual QA on desktop and phone.</t>
+        </is>
+      </c>
+      <c r="L173" s="4" t="inlineStr">
+        <is>
+          <t>Team brief 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.11</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>pages/CRM.js CrmContactDialog, scope counts</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>CRM / Follow-up</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>CRM can say the details are complete without a phone</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>The edit window of a Details-needed record says so, with 'Details are complete' (PATCH needs_details false; anything typed in the form is kept). With the Needs details filter on, the tab counts count only those, so the badge's number can be found.</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="n"/>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (polish after the feature). tests/test_crm_links_reach_every_card.py (7); visual QA on desktop and phone.</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>Team brief 2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>NF-12.12</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>components/party/PartySheet.jsx (new), PartyDialog, OpenPartiesDialog, PartyDetailsPrompt, LinkSuggestionsDialog, PartyPicker</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>The customer/supplier windows are the app's own</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>One glass sheet for all four windows: the centred glass card on desktop, a bottom sheet on a phone clear of the home indicator and riding above the iOS keyboard. The kind is GlassSelect in the repeat picker's pill (no OS dropdown), Link old work uses DesignCheckbox, the search field rings as a pill. Copy pass on titles, buttons and the details prompt.</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="n"/>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>Done 2026-10-31 (polish after the feature). tests/test_crm_links_reach_every_card.py (7); visual QA on desktop and phone.</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>Team brief 2026-10-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic11_New_Features.xlsx
+++ b/docs/DecisionOS_Epic11_New_Features.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 23 of 24 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17), task steps drafted only when someone asks Dex (NF-4.18), Ops KPIs as rates (NF-4.19), New Task's team line, one place to approve requests, repeating tasks from the Decision Desk and the drawer, a Repeating filter (NF-4.20 to 4.24).</t>
+          <t>Sprint 1 Requests shipped (58ce262) - Phase 3 items open. Sprint 2 Notification history shipped (46bb6a0). Sprint 3 Preferred name shipped (6c9bdf1). Sprint 4 Bugs: 25 of 26 fixed (e46b7cc, e352141; invoice delete made fast 2026-10-29; first day of a period 2026-10-30); WhatsApp no-reply open. Sprint 5 Finance delete shipped (e352141). Sprint 6 Admin console redesign built and checked 2026-10-22 (18 of 20; view-as that opens the workspace and required 2FA for super admins are open). Sprint 7 Admin console v2: P1 data foundations pushed (1ea398d); P2 customers pushed (a6a8215); P3 analytics pushed (cf8da32); P4 support depth and P5 polish pushed (47e0335). Sprint 9 Finance periods and bill review (feature) built 2026-10-29: Finance follows the financial year; 2026-10-30 one period for all of Finance; bills read, then confirmed. Sprint 11 Decisions to owned work (feature) built 2026-10-30: a task with nobody goes to the team's one person or its queue (Take it); reminders climb the team's reporting tree one level a day, the owner last; Finance follow-ups too; the Desk lists what needs a person. Sprint 4 also: older members counted again (NF-4.16), a second company on the same number (NF-4.17), task steps drafted only when someone asks Dex (NF-4.18), Ops KPIs as rates (NF-4.19), New Task's team line, one place to approve requests, repeating tasks from the Decision Desk and the drawer, a Repeating filter (NF-4.20 to 4.24).</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In progress -- 24 of 25 Done</t>
+          <t>In progress -- 25 of 26 Done</t>
         </is>
       </c>
     </row>
@@ -1297,11 +1297,10 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 11 progress: 165 of 174 items Done  (95%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature), Sprint 12 Everything links to CRM (feature).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 11 progress: 166 of 175 items Done  (95%).  Sprint 1 Requests (shipped 58ce262; Phase 3 open), Sprint 2 Notification history (46bb6a0), Sprint 3 Preferred name (6c9bdf1), Sprint 4 Bugs (e46b7cc, e352141, delete speed; WhatsApp open), Sprint 5 Finance delete (e352141), Sprint 6 Admin console redesign (2 follow-ups open), Sprint 7 Admin console v2 (P1 1ea398d, P2 a6a8215, P3 cf8da32, P4 + P5 47e0335), Sprint 8 Phone redesign (3ecf7bf and the 2026-10-29 push), Sprint 9 Finance periods and bill review (feature), Sprint 10 Onboarding, first-week tour, Dex widget (7cc7d24 .. 8c9ae5f; 2 open), Sprint 11 Decisions to owned work (feature), Sprint 12 Everything links to CRM (feature).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1450,10 +1449,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1746,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5066,42 +5065,40 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-4.26</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>services/ingestion.commit_ingestion_records (_find_party, _fill_details); tests/test_everything_links_to_crm.py (3 new)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CRM / Finance</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>One delete for every door</t>
+          <t>A bill never makes a second copy of a customer or supplier Dex already knows</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
+          <t>Fix. Found validating Epic 11 Sprint 12 (2026-10-31): a bill's own party list (the parties read off the bill) still matched on the exact name only — only invoice lines asked the shared matcher — so a bill from 'Toyota Kirloskar Pvt. Ltd.' made a second Toyota beside 'Toyota Kirloskar Pvt Ltd'. Both paths now ask services/parties (read once per import, kept current as the bill adds records). A record Dex or a task added with only a name (Needs details) takes the bill's phone, email and address (blank fields only), and a phone number ends its Needs details — what the code's comment promised and no code did. Also the missing tests for two Sprint 12 promises: a reused task takes the decision's party but never loses its own; renaming a firm renames it on its tasks and meetings.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -5109,27 +5106,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Epic 11 S12</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
+          <t>Done 2026-10-31. test_everything_links_to_crm.py 3 new (a bill finds Toyota on the other side and fills the GSTIN; Nippon's Needs-details record takes the bill's phone and address and is done; reused task; rename cascade); all 24 bill-import tests pass.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Client 2026-10-22</t>
+          <t>Validation 2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
+          <t>services/finance_trash.py, routers/finance_trash.py, routers/ledger.py</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5144,12 +5145,12 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Every delete asks first, and has Undo</t>
+          <t>One delete for every door</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
+          <t>Plan (what goes with it, what changes on what stays) -&gt; remove (a copy in finance_trash_rows first, then put right what stays, then out of the books) -&gt; restore. Payment applications, invoice balances, a bill's expense and stock, an expense's asset, request links, standalone payments; the Brain's notes go too. The old DELETE endpoints route through it; an activity and an audit row each time.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -5159,7 +5160,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -5167,14 +5168,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>NF-5.1</t>
-        </is>
-      </c>
+      <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 - e352141.</t>
+          <t>Done 2026-10-22 - e352141. docs/FINANCE_DELETE_PLAN.md</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -5186,12 +5183,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NF-5.3</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
+          <t>pages/finance/FinanceDelete.jsx, pages/Ledger.js</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -5206,12 +5203,12 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Select and delete on every list</t>
+          <t>Every delete asks first, and has Undo</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
+          <t>The sheet lists what it deletes, what goes with it because they belong together, and what changes on what stays; the toast after it has Undo.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -5231,7 +5228,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>NF-5.2</t>
+          <t>NF-5.1</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -5248,12 +5245,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NF-5.4</t>
+          <t>NF-5.3</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
+          <t>components/neuglass/DataList.jsx, pages/finance/FinanceRecords.jsx, MoneyActions.jsx, routers/ledger.py list_payables</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -5263,17 +5260,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Finance / Inbox</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Undo this import</t>
+          <t>Select and delete on every list</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
+          <t>Select, tick (cards on a phone, a column on a laptop), a bar above the dock. Supplier bills and payments made can be deleted; Payments made is listed under Expenses.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -5293,7 +5290,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>NF-5.1</t>
+          <t>NF-5.2</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -5310,12 +5307,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NF-5.5</t>
+          <t>NF-5.4</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
+          <t>routers/finance_trash.py imports, services/ingestion.py, routers/finance.py, pages/Captures.js</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5325,27 +5322,27 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / Inbox</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Recently deleted, for 30 days</t>
+          <t>Undo this import</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
+          <t>On each filed upload in Money &gt; Inbox &gt; Filed: everything the import filed goes, with the payments it matched to older invoices taken off them; contacts used elsewhere and tasks already started are kept. The card then says Undone, with Put back. Imports now stamp their id on stock and follow-up tasks; older imports are found by the moments they were filed.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5372,12 +5369,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>NF-5.6</t>
+          <t>NF-5.5</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>routers/finance_trash.py everything / export</t>
+          <t>services/finance_trash.py list_trash / restore / purge_expired, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -5392,12 +5389,12 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Delete all Finance records (owner)</t>
+          <t>Recently deleted, for 30 days</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
+          <t>Finance &gt; ... &gt; Recently deleted puts any delete back for 30 days; the scheduler empties older ones.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5407,7 +5404,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5434,12 +5431,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NF-5.7</t>
+          <t>NF-5.6</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
+          <t>routers/finance_trash.py everything / export</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -5449,27 +5446,27 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Finance / GST</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Issued GST invoices kept; their numbers never reissued</t>
+          <t>Delete all Finance records (owner)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
+          <t>A copy first (a one-time link to the books as a spreadsheet), then the company's name typed. Contacts, tasks and requests are not touched.</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -5496,12 +5493,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NF-5.8</t>
+          <t>NF-5.7</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+          <t>services/finance_trash.py is_issued, routers/invoicing.py _next_number</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5511,17 +5508,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance / GST</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Tests and checks</t>
+          <t>Issued GST invoices kept; their numbers never reissued</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
+          <t>Kept by default with credit-note advice; only the owner can override. A retired number, or one in Recently deleted, is skipped by the next number and refused when typed.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5539,7 +5536,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>NF-5.1</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>Done 2026-10-22 - e352141.</t>
@@ -5554,30 +5555,32 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NF-6.1</t>
+          <t>NF-5.8</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>6</v>
+          <t>tests/test_finance_records_can_be_deleted_and_put_back.py, browser, Android emulator</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Grouped sidebar with an address for every place</t>
+          <t>Tests and checks</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
+          <t>11 tests on a throwaway database plus the route baseline; checked in the browser at phone size and on the Android emulator.</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5587,7 +5590,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5595,27 +5598,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n"/>
+      <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
+          <t>Done 2026-10-22 - e352141.</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-22 (admin UI audit)</t>
+          <t>Client 2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NF-6.2</t>
+          <t>NF-6.1</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -5628,12 +5631,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Find (Ctrl K)</t>
+          <t>Grouped sidebar with an address for every place</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
+          <t>17 tabs in one scrolling row -&gt; 13 places in 6 groups (Customers, Support, Money, Platform, Security) plus Overview. /admin/workspaces/&lt;id&gt;, /admin/support/&lt;ticket&gt;: refresh, Back and links work. Old tab names (tenant360, impersonation, observability) land where their content went.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -5643,7 +5646,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5666,12 +5669,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>NF-6.3</t>
+          <t>NF-6.2</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js</t>
+          <t>pages/admin/adminUi.jsx FindDialog; routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -5684,17 +5687,17 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>One-line provider alert and counts on the sidebar</t>
+          <t>Find (Ctrl K)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
+          <t>Any workspace, person or page by name, email, phone or id, from anywhere. What is typed is escaped before it reaches the database query (A+B, '(' no longer error or mismatch).</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5722,12 +5725,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>NF-6.4</t>
+          <t>NF-6.3</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
+          <t>pages/admin/AdminPortal.js</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -5735,27 +5738,27 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>The app's own design language, finished</t>
+          <t>One-line provider alert and counts on the sidebar</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
+          <t>The full-size red banner on every tab is one line under the header ('Claude: out of credits ... Open Health'); Health, Support desk, Reports, Billing and Audit log carry counts of what is waiting.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5778,12 +5781,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>NF-6.5</t>
+          <t>NF-6.4</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
+          <t>pages/admin/adminUi.jsx, adminLabels.js, every section</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -5796,22 +5799,22 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Phone width</t>
+          <t>The app's own design language, finished</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
+          <t>Urbanist for text (mono only for ids and keys); GlassSelect for every list (no &lt;option&gt; left in the console); the app's chips; human labels for plans, roles, providers, tasks, audit actions; empty states that say what to do; one shared table with sort and paging.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -5834,12 +5837,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NF-6.6</t>
+          <t>NF-6.5</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
+          <t>pages/admin/AdminPortal.js, adminUi.jsx Toggle</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -5847,27 +5850,27 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Test workspaces told apart, and hidden by default</t>
+          <t>Phone width</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
+          <t>Sidebar becomes a menu sheet; no sideways scroll at 390 px; wide columns hide; the switch keeps its 44 px touch target without drawing as a black disc.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5890,12 +5893,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NF-6.7</t>
+          <t>NF-6.6</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js WorkspaceList</t>
+          <t>services/admin_workspaces.py; routers/admin.py test-flag</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -5908,12 +5911,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Workspaces list</t>
+          <t>Test workspaces told apart, and hidden by default</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
+          <t>Rule: an admin's mark wins, then the demo workspace, then a name that says test/qa/demo/e2e/sandbox. Mark as test / Mark as customer (audited). Hidden by default on Workspaces, Users, AI usage and Overview; one switch shows them.</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5946,12 +5949,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NF-6.8</t>
+          <t>NF-6.7</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
+          <t>pages/admin/AdminSections.js WorkspaceList</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -5964,12 +5967,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>One workspace page</t>
+          <t>Workspaces list</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
+          <t>Search, status, plan, sort, paging 25, plan and trial end, last active; a row opens the workspace page; mark-as-test in the row menu with Undo. Suspend and Delete are no longer on every row.</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -5979,7 +5982,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -6002,12 +6005,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NF-6.9</t>
+          <t>NF-6.8</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/AdminSections.js UsersSection</t>
+          <t>pages/admin/WorkspacePage.js (was Tenant360Section.js); routers/admin_tenant360.py</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -6020,22 +6023,22 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Users directory</t>
+          <t>One workspace page</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
+          <t>Merges Tenant 360, the workspace's billing (plan, trial, seats, payments), AI spend in rupees, data retention, export, consent export, per-person data download and view-as. Counts agree: People = everyone with a sign-in; the address book is Contacts. Changes show at once (the 360 reload takes seconds on the hosted DB).</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -6058,12 +6061,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NF-6.10</t>
+          <t>NF-6.9</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
+          <t>pages/admin/AdminSections.js UsersSection</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -6071,22 +6074,22 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>An Overview that leads with what needs an operator</t>
+          <t>Users directory</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
+          <t>Search name, email, phone or workspace; status filter; test accounts hidden; workspace links; Suspend asks why (audited), Reset access asks first; the owner can't be suspended here.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6114,12 +6117,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NF-6.11</t>
+          <t>NF-6.10</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
+          <t>routers/admin_overview.py; AdminSections.js OverviewSection</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -6127,22 +6130,22 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Health with Observability; Audit log with view-as sessions</t>
+          <t>An Overview that leads with what needs an operator</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
+          <t>GET /api/admin/overview: needs attention (outages, tickets, reports, live view-as, trials ending, failed payments), last 7 days vs the 7 before (active workspaces, sign-ups, AI spend), MRR and paying workspaces counted on customers only, most active, gone quiet, trials ending. Test workspaces left out unless asked.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6170,12 +6173,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NF-6.12</t>
+          <t>NF-6.11</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
+          <t>AdminSections.js HealthSection, AuditSection; ImpersonationSection.js</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -6183,17 +6186,17 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>AI cost in rupees</t>
+          <t>Health with Observability; Audit log with view-as sessions</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
+          <t>Health shows platform status, provider problems, key sources, AI reliability by window, by provider and task, recent errors, outage timeline (ObservabilitySection.js removed). Audit log: search, kind filter, human labels; view-as sessions as its second tab, ended with a confirm.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -6203,7 +6206,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -6226,12 +6229,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NF-6.13</t>
+          <t>NF-6.12</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
+          <t>routers/admin.py usage; services/platform_config.usd_inr_rate; ConfigSection.js</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -6239,27 +6242,27 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Reasons in the audit log; typed delete; no browser prompts</t>
+          <t>AI cost in rupees</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
+          <t>Runtime usd_inr (default 84) set in Config -&gt; Currency; Overview, AI usage and the workspace page show rupees with the dollar figure in small print. /admin/usage gains include_test.</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -6282,12 +6285,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NF-6.14</t>
+          <t>NF-6.13</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
+          <t>WorkspacePage.js, AdminSections.js, SupportDeskSection.js, routers/admin.py</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -6295,17 +6298,17 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Admin invite links</t>
+          <t>Reasons in the audit log; typed delete; no browser prompts</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
+          <t>Suspend (workspace and person), plan change and view-as ask why; the answer is written to the audit log. Delete asks for the workspace's name and offers a full copy first (erasure receipt). window.prompt removed from all four places. Deleting a workspace is super-admin only (any admin could before).</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -6338,12 +6341,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NF-6.15</t>
+          <t>NF-6.14</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
+          <t>routers/admin_rbac.py invite; routers/admin_invites.py; services/admin_invites.py; AdminInvite.js</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -6356,12 +6359,12 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and two-step sign-in fixed</t>
+          <t>Admin invite links</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
+          <t>A super admin invites by email and gets a link (256-bit, stored as a hash, single use, 7 days); the new admin sets their own password at /admin/invite/&lt;token&gt;. Pending admins show as Invited; a new link can be copied (the old one stops working). Public routes live under /api/invites, outside the admin gate.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6394,12 +6397,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>NF-6.16</t>
+          <t>NF-6.15</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>pages/admin/*</t>
+          <t>AdminLogin.js; routers/admin.py login; services/auth/totp.py; AdminRbacSection.js</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -6412,22 +6415,22 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Each admin sees only what they can do</t>
+          <t>Sign-in and two-step sign-in fixed</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
+          <t>An admin with 2FA hung on 'Loading console...' (the code step was never asked) - fixed. Neutral email placeholder. A deactivated admin is refused at the door. Backup codes were issued but never accepted - sign-in and turning 2FA off now take one, once. QR-code setup; turning off asks for a code in the app. Every sign-in asks a password-only admin to turn 2FA on.</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -6450,12 +6453,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>NF-6.17</t>
+          <t>NF-6.16</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
+          <t>pages/admin/*</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -6463,17 +6466,17 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>The rest of the sections redone</t>
+          <t>Each admin sees only what they can do</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
+          <t>Read-only admins see no write controls; Delete, AI keys, Admins and the live retention purge only for super admins. The console reads the role from /admin/me after sign-in (the login answer carries none).</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6483,7 +6486,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -6506,12 +6509,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>NF-6.18</t>
+          <t>NF-6.17</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
+          <t>BillingSection.js, SupportDeskSection.js, ReportsSection.js, AnnouncementsSection.js, ComplianceSection.js, ConfigSection.js</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -6519,22 +6522,22 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Tests and a browser check</t>
+          <t>The rest of the sections redone</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
+          <t>Billing is read-only (plan changes on the workspace page, with a reason). Each ticket has an address; status and priority are app lists. Reports: next-step buttons and notes. Announcements: audience picked (everyone / a plan / a workspace) and read back in words. Compliance: a DPDP desk for workspaces and people. Config: task names in words, flags as switches, model search.</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6562,12 +6565,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NF-6.19</t>
+          <t>NF-6.18</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>routers/admin_impersonation.py, the tenant app's auth</t>
+          <t>tests/test_admin_redesign.py; test_admin_parity.py; fake_mongo.py; browser (scratch DB)</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -6575,22 +6578,22 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>View as actually opens the workspace</t>
+          <t>Tests and a browser check</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
+          <t>25 tests (test rule, mark, reasons, deactivated sign-in, Overview shape and customers-only numbers, AI usage filter, escaped search, delete gate, invites, backup codes). Admin route count 71 -&gt; 75; read-gate; API baseline; FakeDB gains aggregate. Browser flow on dos_engine_0921c: 28/28 (2FA on, code, backup code, off; invite accepted by a Support admin; suspend/plan with reasons and undo; typed delete; audit reasons; mark test; old addresses; refresh).</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6600,13 +6603,13 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Found during the redesign 2026-10-22; not started.</t>
+          <t>Done 2026-10-22 (awaiting push). docs/ADMIN_UI_REDESIGN_PLAN.md</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6618,12 +6621,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NF-6.20</t>
+          <t>NF-6.19</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>routers/admin.py login, AdminPortal.js</t>
+          <t>routers/admin_impersonation.py, the tenant app's auth</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -6636,22 +6639,22 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Require two-step sign-in for super admins</t>
+          <t>View as actually opens the workspace</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
+          <t>Found in the audit: starting a view-as session records it and returns a token, but nothing in the UI uses the token, so an admin cannot see the workspace. Needs the tenant app to accept the read-only session (an auth change of its own).</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -6674,68 +6677,68 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NF-7.1</t>
+          <t>NF-6.20</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
+          <t>routers/admin.py login, AdminPortal.js</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>P1 Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Sign-in and last seen, phone code included</t>
+          <t>Require two-step sign-in for super admins</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
+          <t>Today every sign-in asks; the plan's optional step is to require it for super admins.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
+          <t>Found during the redesign 2026-10-22; not started.</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-23 (admin console v2)</t>
+          <t>Founder 2026-10-22 (admin UI audit)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NF-7.2</t>
+          <t>NF-7.1</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>services/presence.py presence_days</t>
+          <t>services/presence.py; routers/auth_otp.py, routers/auth.py; core/deps.py</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
@@ -6748,12 +6751,12 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Who was here each day, kept for good</t>
+          <t>Sign-in and last seen, phone code included</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
+          <t>The phone-code sign-in (the main one) left no audit row, no session and no last seen. Now every sign-in (phone code, password, 2FA, sign-up) writes login_success with its method, a session row and last_login_at / last_seen_at on the person and their membership. Requests add no writes (a request already refreshes its session; the scheduler turns sessions into presence and last-seen every 3 hours, and the console reads the live session time) -- the Desk-load latency guard stays green.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -6763,7 +6766,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6786,12 +6789,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NF-7.3</t>
+          <t>NF-7.2</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
+          <t>services/presence.py presence_days</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -6804,12 +6807,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Daily count per workspace, kept for good</t>
+          <t>Who was here each day, kept for good</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
+          <t>One row per person per company per IST day (sign-ins counted on it), never purged: daily / weekly / monthly active people are counted from it.</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6819,7 +6822,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6842,12 +6845,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>NF-7.4</t>
+          <t>NF-7.3</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>services/rollups.backfill; routers/admin_analytics.py</t>
+          <t>services/rollups.py tenant_daily; workers/schedulers.py</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -6860,12 +6863,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Backfill from what still exists</t>
+          <t>Daily count per workspace, kept for good</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
+          <t>One row per company per IST day: active people, sign-ins, actions by product area, AI calls and cost, voice notes, Brain questions, and plan / seats / test mark for today. Re-counted every 3 hours by the scheduler leader; retention never touches it. Counts streamed once per source for the whole window.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6875,7 +6878,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6898,12 +6901,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>NF-7.5</t>
+          <t>NF-7.4</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
+          <t>services/rollups.backfill; routers/admin_analytics.py</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -6916,12 +6919,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Lifecycle events</t>
+          <t>Backfill from what still exists</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
+          <t>First scheduler run counts back 180 days and fills milestones and sign-up events; a super admin can count again from Health (runs in the background). Milestone backfill is one grouped query per source for all companies (101 s -&gt; 15 s on the scratch database).</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6931,7 +6934,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6954,12 +6957,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>NF-7.6</t>
+          <t>NF-7.5</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>services/milestones.py; core/__init__.log_activity</t>
+          <t>services/lifecycle.py; routers/billing.py, admin_billing.py, admin.py, auth.py</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -6972,12 +6975,12 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>First-value milestones and activation</t>
+          <t>Lifecycle events</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
+          <t>signed_up, plan_changed (from/to, source, by, reason), payment_received, payment_failed, subscription_halted, suspended (reason), reactivated -- written where each happens. Suspension also keeps suspended_at / reason / by on the company.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -7010,12 +7013,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NF-7.7</t>
+          <t>NF-7.6</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
+          <t>services/milestones.py; core/__init__.log_activity</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -7028,17 +7031,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>The console shows the foundations</t>
+          <t>First-value milestones and activation</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
+          <t>Each first (decision, decision approved, task, task done, teammate invited, capture, voice, finance, request, workflow, contact, WhatsApp, Brain document, payment) lands once on the company. Activated = a decision approved and a teammate invited within 14 days of signing up (founder-approved recommendation).</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7066,12 +7069,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NF-7.8</t>
+          <t>NF-7.7</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
+          <t>WorkspacePage.js, AdminSections.js (Users, Health), admin_tenant360.py, admin.py users</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -7079,22 +7082,22 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>P1 Data</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Tests and a scratch check</t>
+          <t>The console shows the foundations</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
+          <t>Workspace page: each person's last seen, an Activation checklist, a History of lifecycle events, suspension since/why, Last active counts presence. Users: Last seen column. Health: Analytics data panel (last count, people here today / week / month, activated workspaces, events kept, Count again).</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7122,12 +7125,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NF-7.9</t>
+          <t>NF-7.8</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Customers list, health score, stages</t>
+          <t>tests/test_admin_analytics_foundations.py; fake_mongo.py; parity; baseline; browser (scratch)</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -7135,17 +7138,17 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>P2 Customers</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Health score, stage and the customer list</t>
+          <t>Tests and a scratch check</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
+          <t>24 tests (presence throttle, sign-in trail, milestones and activation, backfill, lifecycle, IST day counting, roll-up, platform series, retention exclusion, console reads). FakeDB gains $setOnInsert. Admin routes 75 -&gt; 77; tenant wipe covers the 3 new collections. Scratch: a phone-code sign-in leaves audit + session + presence; Health and the workspace page show the data.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -7155,7 +7158,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -7166,7 +7169,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
+          <t>Done 2026-10-23, pushed 1ea398d. docs/ADMIN_CONSOLE_V2_PLAN.md</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -7178,12 +7181,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>NF-7.10</t>
+          <t>NF-7.9</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Customer page tabs; notes, tags, owner</t>
+          <t>Customers list, health score, stages</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -7196,12 +7199,12 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Customer page in tabs, with timeline and notes</t>
+          <t>Health score, stage and the customer list</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
+          <t>Explainable 0-100 health (activity, breadth, momentum, setup, friction; weights in Config), lifecycle stage, choosable columns, saved views shared by the team, bulk tag / owner / export.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -7222,7 +7225,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
+          <t>Done 2026-10-23, pushed a6a8215. services/customer_health.py, routers/admin_customers.py GET /customers, CustomersList.js: health 0-100 in five parts (weights from runtime health_weights), stage (test, suspended, churned, at risk, paying, activated, not activated), 7 built-in views + saved views shared by the team, column chooser, bulk tag / untag / owner / test / customer, CSV export.</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -7234,12 +7237,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NF-7.11</t>
+          <t>NF-7.10</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
+          <t>Customer page tabs; notes, tags, owner</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -7247,17 +7250,17 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>P3 Analytics</t>
+          <t>P2 Customers</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Analytics pages and Home</t>
+          <t>Customer page in tabs, with timeline and notes</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
+          <t>Overview, Timeline, People, Usage, Billing, Support, Data, Notes; notes / tags / account owner / next follow-up (F8).</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -7278,7 +7281,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
+          <t>Done 2026-10-23, pushed a6a8215. Customer page in tabs with addresses (/admin/workspaces/&lt;id&gt;/&lt;tab&gt;): Overview (health breakdown, 30-day chart, activation, account), Timeline (lifecycle, activity, admin actions, tickets, notes, people, payments), People, Usage (adoption grid by week), Billing, Support, Data, Notes; notes, tags, account owner and follow-up date, all audited. tests/test_admin_customers.py (13).</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -7290,12 +7293,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>NF-7.12</t>
+          <t>NF-7.11</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Outbound message log, ticket SLA, NPS</t>
+          <t>Analytics: Growth, Engagement, Retention, Revenue, AI economics; Home</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -7303,27 +7306,27 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>P4 Support</t>
+          <t>P3 Analytics</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Support depth</t>
+          <t>Analytics pages and Home</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
+          <t>Sign-ups and activation funnel, DAU/WAU/MAU and feature adoption, weekly cohorts, MRR movement, AI cost vs revenue; Home with 'needs you today' and sparklines. recharts.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -7334,7 +7337,7 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
+          <t>Done 2026-10-23, pushed cf8da32. services/analytics.py + routers/admin_analytics.py (/analytics/growth, engagement, retention, revenue, ai, /home); HomeSection.js, AnalyticsPages.js, analyticsKit.jsx (recharts). Home: ranked needs (outages, failed payments, tickets waiting 24 h+, paying customers slipping or gone quiet, trials ending, follow-ups, reports), KPIs with sparklines, health movers from a daily health snapshot in the roll-up. Funnel only narrows. MRR rebuilt from plan_changed events (history from 23 Oct 2026). tests/test_admin_analytics_pages.py (8).</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -7346,12 +7349,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>NF-7.13</t>
+          <t>NF-7.12</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Density, dark mode, detail drawer</t>
+          <t>Outbound message log, ticket SLA, NPS</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -7359,22 +7362,22 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>P5 Polish</t>
+          <t>P4 Support</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Support depth</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
+          <t>Log every email / SMS / WhatsApp / push sent (no body), first-response and resolve times on tickets, optional in-app NPS.</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7390,7 +7393,7 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
+          <t>Done 2026-10-23, pushed 47e0335. core/outbound.py: one row per email / SMS / WhatsApp / push (channel, kind, company, person, masked recipient, sent / failed / skipped; never the text; 180-day TTL), hooked in integrations/email.send_email (callers label kind + company), integrations/whatsapp.send_wa_reply (now checks the HTTP status), services/push_fcm.send_push_to_users and services/otp._issue_otp (OTP scopes are not companies). Tickets: first_response_at on our first reply, resolved_at on resolve, cleared on reopen; SLA targets urgent 4h / high 8h / normal 24h / low 72h; inbox strip (past target, due soon, replied in time, typical first reply), late tickets first. routers/admin_messages.py (/admin/messages, /admin/nps); routers/nps.py (/nps/ask, /nps) behind global flag nps, off by default; RecommendCard in the app shell. supportKit.jsx, SupportDeskSection (Tickets / Messages sent / Recommend score), customer Support tab shows messages. tests/test_admin_support_p4.py (14). Admin routes 96 -&gt; 98.</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -7402,40 +7405,40 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>NF-8.1</t>
+          <t>NF-7.13</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
+          <t>Density, dark mode, detail drawer</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>P5 Polish</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
+          <t>Compact density, dark mode, a side drawer for quick looks, keyboard shortcuts, quiet-week states.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7446,24 +7449,24 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-23, pushed 47e0335. adminShell.jsx: Display menu (light / dark / match this computer; comfortable / compact), saved per browser; dark mode is a generated, scoped stylesheet (adminTheme.css, html.admin-dark) so portalled dialogs follow and the product app is untouched; keys G+letter, /, ?, Shift D with a key list. QuickLook.jsx: a customer at a glance from the list (health, numbers, pinned note, open tickets, latest events). Home: 'while it's quiet' shortcuts; stage bars open the list filtered by stage (?stage=, ?view=).</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (phone redesign)</t>
+          <t>Founder 2026-10-23 (admin console v2)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>NF-8.2</t>
+          <t>NF-8.1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (mobileTaskView)</t>
+          <t>pages/MyWork.js, pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -7476,12 +7479,12 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>The task, full screen: four tabs and the checklist as a flow</t>
+          <t>My Work on the phone: tiles, bands, a sheet of cards</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
+          <t>Filter tiles (Showing, Status, Department, Person) on the sky; High / Medium / Low priority bands as the default view; the work in a black sheet that scrolls as usual; each task a summary card (status, due, assigned ago, people three then +N, attachments, Next action, Mark as Doing / Open task).</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -7514,12 +7517,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>NF-8.3</t>
+          <t>NF-8.2</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
+          <t>pages/MyWork.js (mobileTaskView)</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -7527,17 +7530,17 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>My Work / Dex</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Dex drafts every task's checklist by itself</t>
+          <t>The task, full screen: four tabs and the checklist as a flow</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
+          <t>Hero, approval, assignees (three, View all), AI Execution Guide, then Steps (numbered flow, line fills as steps are ticked), Documents (file, photo, voice), Activity (status at the top, the timeline, the task's facts) and Notes.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -7547,7 +7550,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -7558,7 +7561,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -7570,12 +7573,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>NF-8.4</t>
+          <t>NF-8.3</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
+          <t>services/auto_plan.py, routers/tasks.py, services/voice.py, routers/decisions.py, workers/schedulers.py</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -7583,22 +7586,22 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>My Work / Dex</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>A request card that says where it stands</t>
+          <t>Dex drafts every task's checklist by itself</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
+          <t>On creation (task, decision, hand-off, approval, routine copy), consent-gated, once, three tries at most; the placeholder answer counts as a failed try; POST /tasks/auto-plan asks for the open tasks on screen without one, so a card names its real first step; the Redraft stays.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -7614,7 +7617,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py, tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -7626,12 +7629,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>NF-8.5</t>
+          <t>NF-8.4</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>public/landing/, landing-v2/, landing-v3/</t>
+          <t>components/requests/RequestCard.jsx, RequestsPanel.jsx, lib/requests.js, lib/format.js</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -7639,17 +7642,17 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Plan prices read Coming soon</t>
+          <t>A request card that says where it stands</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
+          <t>Status, type and needed-by chips, number and menu, title and amount, requester to approver with faces, the question, first item and reason, file tiles, and the actions (Approve / Reject / Ask, Mark paid, View details) pinned to the foot; on the Requests page and in My Work's My requests.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -7659,7 +7662,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -7670,7 +7673,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_a_request_card_says_where_it_stands.py.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7682,12 +7685,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>NF-8.6</t>
+          <t>NF-8.5</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/DexWave.jsx</t>
+          <t>public/landing/, landing-v2/, landing-v3/</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -7695,17 +7698,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Dex</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
+          <t>Plan prices read Coming soon</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
+          <t>Every plan keeps its name and what it includes; the price slot says Coming soon on all three landing pages.</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -7715,7 +7718,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -7726,7 +7729,7 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_landing_prices_are_not_public_yet.py.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7738,12 +7741,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NF-8.7</t>
+          <t>NF-8.6</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
+          <t>components/mobile/DexWave.jsx</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -7756,12 +7759,12 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Pause and carry on while speaking</t>
+          <t>The voice wave: one blurred light, wide, and it follows the voice</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
+          <t>The three ribbons melt into one (a horizontal motion blur aura + softened bodies); wide lobes spread across the bar (frequencies 0.42-0.95, flat edge envelope); reads only the newest samples, learns the room's floor and the voice's ceiling, gates and expands, so quiet stays low and speech rises (about 1.5 to 30 of 44).</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -7782,7 +7785,7 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: Measured in the browser with a synthetic mic.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -7794,12 +7797,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NF-8.8</t>
+          <t>NF-8.7</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
+          <t>hooks/useDexCapture.js, components/neuglass/DexSlider.jsx, components/mobile/DockSlider.jsx, components/Layout.js, pages/desk/DeskDexWell.jsx</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
@@ -7807,17 +7810,17 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Dex</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Dex is reading it: a checklist under Dex as a figure</t>
+          <t>Pause and carry on while speaking</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
+          <t>A round pause at the free end of the bar while a take is live; the recorder pauses (not stops), the wave settles and says Paused, play carries on into the same take; Send still sends what was said; no second take can start while one is paused.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -7850,12 +7853,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NF-8.9</t>
+          <t>NF-8.8</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
+          <t>pages/desk/DexCapturePopup.jsx, pages/onboarding/DexBuilder.jsx</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
@@ -7868,22 +7871,22 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
+          <t>Dex is reading it: a checklist under Dex as a figure</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
+          <t>Understanding your request, Identifying the decision, Breaking it into tasks, Matching the people, Preparing the summary; the first ticks on the server's word, the rest pace through the one structuring call and the last holds until it answers. Dex: the forge as its head, an ink body holding a board, the hands tapping three workflow steps in turn.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -7894,7 +7897,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7906,12 +7909,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>NF-8.10</t>
+          <t>NF-8.9</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>components/DecisionDialog.js</t>
+          <t>pages/desk/DexReview.jsx, services/decision_flow.py, models/decisions.py, routers/decisions.py, services/voice.py</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
@@ -7924,12 +7927,12 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Desk decisions open in the new review on the phone</t>
+          <t>The review on the phone: Review &amp; approve, the tasks, one task</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
+          <t>Decision card with priority, four counts, execution timeline, key settings, Approve full width over Save as draft / Reject; Tasks created by Dex as numbered nodes; one task with who, priority, details, tags, due, approval, approver, proof, priority bar, Waits for and Activity. New: details, tags and dependencies held on the proposal and applied on approval; POST /decisions/{id}/proposal/tasks (Add another task); approving to start keeps a task blocked while it still waits for another.</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -7939,7 +7942,7 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -7950,7 +7953,7 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -7962,12 +7965,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>NF-8.11</t>
+          <t>NF-8.10</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
+          <t>components/DecisionDialog.js</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
@@ -7975,17 +7978,17 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Phone-wide</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Every toast is full screen on the phone</t>
+          <t>Desk decisions open in the new review on the phone</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
+          <t>Opening a decision from the Desk (or a notification) on a phone shows the same three screens, full screen, with Send a note and the decision's history added; the desktop keeps its two-column panel.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -7995,7 +7998,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -8006,7 +8009,7 @@
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -8018,12 +8021,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>NF-8.12</t>
+          <t>NF-8.11</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
+          <t>components/mobile/Affirmation.jsx, App.js, and 15 toast() calls -&gt; toast.message()</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -8036,22 +8039,22 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Pop-ups open in place</t>
+          <t>Every toast is full screen on the phone</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
+          <t>Success a tick on the black disc, errors an exclamation on maroon with a nudge, info an i, loading a turning ring replaced by its result; an Undo / Refresh / Review is a real button; tap to clear; the desktop keeps its toasts.</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -8062,7 +8065,7 @@
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_decide_review_shapes_each_task.py.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -8074,12 +8077,12 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>NF-8.13</t>
+          <t>NF-8.12</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
+          <t>components/ui/dialog.jsx, alert-dialog.jsx</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
@@ -8092,17 +8095,17 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>The Ask panel see-through; the page blurs behind More</t>
+          <t>Pop-ups open in place</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
+          <t>No zoom from a corner below lg: dialogs and confirm boxes appear straight in the centre.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8130,12 +8133,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>NF-8.14</t>
+          <t>NF-8.13</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
+          <t>index.css (.ng-dock-chat), components/mobile/DockSlider.jsx</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
@@ -8143,27 +8146,27 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Preferences</t>
+          <t>Phone-wide</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Your dock: choose its three places</t>
+          <t>The Ask panel see-through; the page blurs behind More</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
+          <t>The Ask conversation panel 92% -&gt; 72% ink with a stronger blur; More dims and blurs the page behind it.</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -8186,12 +8189,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>NF-8.15</t>
+          <t>NF-8.14</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
+          <t>components/mobile/dockChoice.js, components/settings/DockCard.jsx, components/mobile/DockSlider.jsx, pages/Settings.js</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
@@ -8199,17 +8202,17 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Preferences</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Blue buttons are the app's ink</t>
+          <t>Your dock: choose its three places</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
+          <t>A mock dock in Preferences; tap a place, pick another from the pop-up, and the live dock changes; Dex and More stay fixed; whatever leaves the dock is in More; Reset to the default.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -8219,7 +8222,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -8230,7 +8233,7 @@
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
@@ -8242,12 +8245,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>NF-8.16</t>
+          <t>NF-8.15</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
+          <t>index.css (--primary-action), components/ProfileDialog.js, ui/button.jsx, pages/desk/WorkflowsTile.jsx and others</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -8255,27 +8258,27 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>The task view's foot is one slider; Details becomes Notes</t>
+          <t>Blue buttons are the app's ink</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
+          <t>The primary colour token is the ink, so every bg-primary button, switch and selected pill follows; blue hovers fixed; Call on a contact; the Desk's Open in Workflows is the black gradient pill; Medium priority is amber.</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -8286,7 +8289,7 @@
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_the_workflows_tile_opens_the_card_it_names.py.</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -8298,12 +8301,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>NF-8.17</t>
+          <t>NF-8.16</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
+          <t>pages/mywork/TaskActionSlider.jsx, pages/mywork/TaskNotes.jsx, pages/MyWork.js</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
@@ -8311,17 +8314,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>The owner hears when work is finished</t>
+          <t>The task view's foot is one slider; Details becomes Notes</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
+          <t>Swipe right to complete (proof and sign-off rules kept), left to raise the Log note / Hand off / Escalate card from just above the bar, the page blurred behind from the bottom up; attach / photo / voice leave the foot (Documents has them); Notes kept only on the phone, typed or dictated.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -8342,7 +8345,7 @@
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_my_work_is_one_task_at_a_time.py.</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
@@ -8354,12 +8357,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>NF-8.18</t>
+          <t>NF-8.17</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>routers/tasks.py (save_execution_plan)</t>
+          <t>routers/tasks.py (_tell_owners_done, /finished-tasks), services/notifications.py, pages/desk/FinishedWorkCard.jsx, pages/Desk.js</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
@@ -8367,17 +8370,17 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>A checklist never moves a task to Doing</t>
+          <t>The owner hears when work is finished</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
+          <t>Every owner but the one who closed it gets a notice and a push (task_done). On opening the app the Desk shows a floating card of what was finished since they last looked - owners the company's, anyone else what they asked for - each once; tap one to open it.</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -8387,7 +8390,7 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -8398,7 +8401,7 @@
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_finished_work_reaches_the_owner.py.</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -8410,12 +8413,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>NF-8.19</t>
+          <t>NF-8.18</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>pages/mywork/WorkDeck.jsx</t>
+          <t>routers/tasks.py (save_execution_plan)</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -8428,17 +8431,17 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>The card's steps: a row of numbers above Next action</t>
+          <t>A checklist never moves a task to Doing</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
+          <t>A drafted checklist or a ticked step no longer turns To do into Doing; only Mark as Doing or the status picker does. The last step still completes it.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -8454,7 +8457,7 @@
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_dex_drafts_the_checklist_on_its_own.py.</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -8466,12 +8469,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>NF-8.20</t>
+          <t>NF-8.19</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>index.css (sky)</t>
+          <t>pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
@@ -8479,22 +8482,22 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>No amber glow; Notifications wears Finance's sky</t>
+          <t>The card's steps: a row of numbers above Next action</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
+          <t>One row of numbered nodes (done in ink) just above the Next action box; tapping a number shows that step there in full, Step N of M; no progress bar; the box a soft grey; the four tiles one soft grey gradient.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -8510,7 +8513,7 @@
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit).</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -8522,35 +8525,35 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-8.20</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
+          <t>index.css (sky)</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Settings / Finance</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Financial year starts in (company setting)</t>
+          <t>No amber glow; Notifications wears Finance's sky</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
+          <t>The default sky's amber stops are gone from the source (the Finance palette instead); Notifications uses the Finance picture.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -8563,31 +8566,27 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="J120" s="4" t="n"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
+          <t>Done 2026-10-29 (pushed with the Sprint 8 commit). Tests: tests/test_requests_wears_money_and_the_more_menu_fits.py.</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29 (client: records not reflecting)</t>
+          <t>Founder 2026-10-29 (phone redesign)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
+          <t>models/tenant.py fy_start_month; routers/tenant_settings.py PATCH /tenant; components/CompanyDetails.js</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
@@ -8595,17 +8594,17 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Settings / Finance</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Overview opens on the financial year; every quarter and half</t>
+          <t>Financial year starts in (company setting)</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
+          <t>Settings &gt; Company details &gt; Financial year starts in: any month, April when unset. Finance's year, halves and quarters follow it; invoice numbering keeps the April-March GST year.</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -8615,7 +8614,7 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -8625,7 +8624,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -8642,12 +8641,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>NF-9.3</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
+          <t>pages/finance/ledgerMath.js periodWindow, periodChoices, financeMetrics; pages/finance/FinanceOverview.jsx</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
@@ -8655,17 +8654,17 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Finance / UI</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>The period picker: kind, then which one</t>
+          <t>Overview opens on the financial year; every quarter and half</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
+          <t>Default This financial year (was Last 30 days, which hid back-dated records: the client's 'not reflecting in revenue / received / profit'). Periods: FY (this or any earlier), H1/H2 and Q1-Q4 of any year back to the oldest record, last 30 days, custom From-To, all time. Standard labels: 'FY 2026-27', 'Q2 FY 2026-27' ('FY 2026' for a January year). A running window compares with the same point of the one before; a finished one with the whole of the one before; asset and stock value for a finished window are what they stood at when it ended.</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -8702,12 +8701,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>NF-9.4</t>
+          <t>NF-9.3</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
+          <t>pages/finance/PeriodPicker.jsx; pages/Ledger.js</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
@@ -8715,17 +8714,17 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance / UI</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>It rolls over by itself</t>
+          <t>The period picker: kind, then which one</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
+          <t>Not a long dropdown: a panel of big buttons - Financial year, Half year, Quarter, Last 30 days, Custom range, All time - then which one, with a year switcher (&lt; FY 2026-27 &gt;) for halves and quarters. A half or quarter that hasn't started is shown, not pickable; a custom range can't pass today. Desktop and phone.</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -8735,7 +8734,7 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -8762,12 +8761,12 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>NF-9.5</t>
+          <t>NF-9.4</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
+          <t>ledgerMath.js (relative 'fy', year-stamped picks); Ledger.js useToday, sessionStorage</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
@@ -8775,17 +8774,17 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Date tests and checks</t>
+          <t>It rolls over by itself</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
+          <t>Nothing names a year: on 1 April 2027 the default is FY 2027-28 and last year's Q4 is one tap away. A pick names its year (Q3 FY 2026-27 stays that quarter); a choice lasts the visit and every new visit opens on the current year; a page left open over midnight moves to the new day; choices saved by older versions still open.</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -8822,12 +8821,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>NF-9.6</t>
+          <t>NF-9.5</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
+          <t>tests/test_finance_period_dates.py, tests/test_finance_periods_follow_the_financial_year.py</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
@@ -8835,17 +8834,17 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>One period for all of Finance</t>
+          <t>Date tests and checks</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
+          <t>The real period code under Node on fixed dates: midnight on 31 March, January and July years, leap-year February, old saved choices, custom capped at today, each period counting its own records (8); the setting, picker and wiring (5). Browser: every kind, Q1-Q4, H1-H2, last year's quarters, custom, Settings relabelling.</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -8855,7 +8854,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -8865,29 +8864,29 @@
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>NF-9.2</t>
+          <t>NF-9.1</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
+          <t>Done 2026-10-29 (feature). docs/FINANCE_PERIODS.md</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29</t>
+          <t>Founder 2026-10-29 (client: records not reflecting)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>NF-9.7</t>
+          <t>NF-9.6</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+          <t>pages/Ledger.js PERIOD_TABS; pages/finance/FinanceRecords.jsx RevenueTab, ExpensesTab, PeriodLine; ledgerMath inPeriod</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
@@ -8895,17 +8894,17 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Finance / AI</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>A bill is read, then confirmed</t>
+          <t>One period for all of Finance</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
+          <t>Founder 2026-10-29: picked once, it reflects everywhere. The period picker is on Overview, Revenue and Expenses, one value: the invoice, payment, expense and payments-made lists and Billed / Received follow it. Assets, Inventory and Inbox show everything (no picker). What is owed is never hidden: Outstanding and Overdue count every unpaid invoice ('all dates'); a line says how many unpaid invoices fall outside the period, with Show all dates; Bills to pay, approved purchases and payments to match are never filtered.</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -8925,59 +8924,57 @@
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>NF-9.1</t>
+          <t>NF-9.2</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
+          <t>Done 2026-10-30 (feature). Browser: Q2 on Overview -&gt; Revenue shows Q2; Q3 on Revenue -&gt; Expenses and Overview show Q3, with the unpaid July invoice called out; Show all dates -&gt; All time everywhere; no picker on Assets. Test: test_one_period_for_every_tab_that_reports_money_moving.</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>NF-10.1</t>
+          <t>NF-9.7</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>routers/ledger.py read_bill (POST /ledger/read-bill), _read_attachment, _reviewed_attachment; pages/finance/FinanceForms.jsx useBillReader, BillNote</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Dex widget</t>
+          <t>Finance / AI</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Dex on the Android home screen</t>
+          <t>A bill is read, then confirmed</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
+          <t>Founder 2026-10-30: in Add income / expense / asset / stock an attached bill went to the AI on Save and was filed with whatever it read - a wrong amount or customer reached the books unchecked. Now choosing the bill reads it first (stored once, read once, nothing saved): the AI's values fill the empty fields, highlighted and tagged 'AI' until changed, with a note saying how many it filled (or why it couldn't, e.g. AI off); Save waits for the read and files what the person checked, attaching the stored bill without reading it again. Only this company's ledger uploads can be attached that way; older app builds still send the bill to be read on save.</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -8985,27 +8982,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>NF-9.1</t>
+        </is>
+      </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
+          <t>Done 2026-10-30 (feature). Browser, real AI read of a sample invoice: 6 fields filled (title, Rs 49,560, ST-2026-0457, customer, both dates), 0 records before Save; amount corrected to Rs 42,000 and saved with the bill attached, not read again. Tests: test_finance_bills_are_read_then_confirmed.py (6); test_ai_off_everywhere updated (the reason shows before saving).</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-29/30</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>NF-10.2</t>
+          <t>NF-10.1</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>DexQuickActivity.java, AndroidManifest.xml</t>
+          <t>android: DexWidgetProvider.java, DexQuickActivity.java, res/layout/widget_dex.xml, res/drawable/widget_*.xml, res/xml/dex_widget_info.xml, AndroidManifest.xml, values/styles.xml; frontend/src/lib/native/quick.js, components/Layout.js, App.js (/quick)</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -9015,27 +9016,27 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Dex widget</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>The widget layer opened black</t>
+          <t>Dex on the Android home screen</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
+          <t>A home-screen widget: Ask, the app icon, Decide on a dark glass rectangle (black at ~60%, small radius). Ask and Decide open the real flows in a see-through layer over the launcher (DexQuickActivity, a translucent BridgeActivity started at /quick?mode=ask|decide; Layout draws only the dock and the tapped flow; closing returns to the home screen). The icon knob opens the app itself.</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -9046,7 +9047,7 @@
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Checked on the OnePlus: widget placed, Ask and Decide over the wallpaper, knob opens the app.</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -9058,12 +9059,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>NF-10.3</t>
+          <t>NF-10.2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
+          <t>DexQuickActivity.java, AndroidManifest.xml</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -9073,22 +9074,22 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Dex Decide</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>One centred, glowing "Transcribing what you said" in step 1</t>
+          <t>The widget layer opened black</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
+          <t>On Android 17 the translucent theme alone left the window marked as covering what is under it, so the launcher stopped drawing and the clear ground showed black. The activity now asks for translucency outright (setTranslucent(true)) and drops the fixed portrait orientation that cannot coexist with it.</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -9104,7 +9105,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Verified on device (occludesParent=false).</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -9116,12 +9117,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>NF-10.4</t>
+          <t>NF-10.3</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx, index.css (.ng-glow-text)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -9131,17 +9132,17 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Dex Decide</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Signup background: a drawn blueprint, not a photograph</t>
+          <t>One centred, glowing "Transcribing what you said" in step 1</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
+          <t>The spinner row above the field and the pulse inside it were two loaders for one wait. Now a single line sits centred in the field and glows on a slow loop; nothing spins (held still under reduced motion).</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -9162,7 +9163,7 @@
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Seen on the phone.</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -9174,12 +9175,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>NF-10.5</t>
+          <t>NF-10.4</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
+          <t>frontend/src/pages/Signup.js, index.css (.ob-backdrop, .ob-orb)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -9194,22 +9195,22 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>"Your OS, taking shape" beside every signup step</t>
+          <t>Signup background: a drawn blueprint, not a photograph</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
+          <t>A cool paper with a dot grid and two slow ink-blue and gold lights replace the signup photo, giving the glass cards their midtone; reduced motion holds it still.</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -9220,7 +9221,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -9232,12 +9233,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6</t>
+          <t>NF-10.5</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
+          <t>frontend/src/pages/onboarding/OsAssembly.jsx, pages/Signup.js</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -9252,12 +9253,12 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Each interview answer names what it added to the OS</t>
+          <t>"Your OS, taking shape" beside every signup step</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
+          <t>The company at the centre; pieces land round it as the founder answers - owner and team from Basics, trade, sales model and website, then the departments, workflows, approvals and rules each interview answer adds. While Dex works the hub ring turns, links carry light and a ghost slot marks the next piece. Desktop orbit (two staggered rings past six pieces, max 8 shown); phone strip, newest first.</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -9267,7 +9268,7 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -9278,7 +9279,7 @@
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
+          <t>Done 2026-10-29 - 7cc7d24; ring/label fixes 2b395c6.</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -9290,12 +9291,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>NF-10.7</t>
+          <t>NF-10.6</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
+          <t>backend: services/ai/onboarding.py (_built_pieces), routers/signup.py (/interview/answer -&gt; built)</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -9305,17 +9306,17 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Client feedback</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Every wait says what is happening</t>
+          <t>Each interview answer names what it added to the OS</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
+          <t>The same model call that picks the next question also returns up to three {kind, label} pieces (department, workflow, approval, task, rule, metric) from the last answer - no second request, no extra wait. Unknown kinds dropped, labels cut to 48 chars.</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -9336,7 +9337,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Tests: tests/test_onboarding_builds_as_you_answer.py. Needs the Railway backend deploy to show on the live app (NF-10.23).</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -9348,12 +9349,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>NF-10.8</t>
+          <t>NF-10.7</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
+          <t>frontend/src/pages/onboarding/WaitStory.jsx, VoiceInterview.js, BuildReveal.js</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -9363,27 +9364,27 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Client feedback</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume while answering the interview</t>
+          <t>Every wait says what is happening</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
+          <t>Client: "the user is waiting so long with no prompt". Writing down a spoken answer, Dex choosing the next question and finding its voice, the interview warming up, the final build and the workflow layout each show a glowing line, a short story that moves on with the wait (not looping) and an easing gold line - in place of small spinners on buttons.</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -9394,7 +9395,7 @@
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -9406,12 +9407,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>NF-10.9</t>
+          <t>NF-10.8</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
+          <t>frontend/src/pages/onboarding/voice.js (useAnswerRecorder), VoiceInterview.js</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -9426,17 +9427,17 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Basics and the language pick: pictures, fewer words</t>
+          <t>Pause and resume while answering the interview</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
+          <t>While speaking, Pause/Resume sits beside Stop; resuming records into the same answer (MediaRecorder pause/resume).</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -9452,7 +9453,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
+          <t>Done 2026-10-29 - 7cc7d24. Not tried with a real microphone in the browser pane.</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -9464,12 +9465,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>NF-10.10</t>
+          <t>NF-10.9</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
+          <t>frontend/src/pages/onboarding/BasicsFlow.js, VoiceInterview.js</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -9484,17 +9485,17 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>The build carries the picture on</t>
+          <t>Basics and the language pick: pictures, fewer words</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
+          <t>Each Basics question wears an icon tile of what it asks for instead of a step number; supporting lines cut to a few words; the language pick says one line, not two.</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -9510,7 +9511,7 @@
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 7cc7d24.</t>
+          <t>Done 2026-10-29 - 7cc7d24. Test pin updated (test_p2_p3_polish_batch).</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9522,12 +9523,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>NF-10.11</t>
+          <t>NF-10.10</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js (building stage)</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -9542,22 +9543,22 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>The last signup screen: KPIs and "What Dex built"</t>
+          <t>The build carries the picture on</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
+          <t>While Dex builds, the OS canvas keeps assembling with the interview's pieces beside the progress story, in place of a separate forge animation.</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
@@ -9568,7 +9569,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
+          <t>Done 2026-10-29 - 7cc7d24.</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -9580,12 +9581,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>NF-10.12</t>
+          <t>NF-10.11</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
+          <t>frontend/src/pages/onboarding/BuildReveal.js, OsMap.jsx, walkthrough/journey.js</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -9600,22 +9601,22 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>The team map: hand-offs along the ring, plain panel</t>
+          <t>The last signup screen: KPIs and "What Dex built"</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
+          <t>Counts first (teams, workflows, steps, tasks set up, sign-offs, routines - the three that wait on the workflows glow "..." until laid out), then an explorer with a tab per kind: Workflows (the route, step by step), Teams (the map), Sign-offs (gates leading to "You", removable), Routines (as My Work rows). Tell Dex and Enter unchanged.</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I138" s="11" t="inlineStr">
@@ -9626,7 +9627,7 @@
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - f65c54a.</t>
+          <t>Done 2026-10-29/30 - 7cc7d24, f65c54a, ebb52b9. Checked on local test companies (Verma Spices, Nilgiri Leaf Co, Coastal Cashew Exports).</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -9638,12 +9639,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>NF-10.13</t>
+          <t>NF-10.12</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -9653,17 +9654,17 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
+          <t>The team map: hand-offs along the ring, plain panel</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
+          <t>Teams round the company; hand-offs drawn as arcs of the ring (two-way pairs on either side), a legend under the map; a team's panel names every step of each workflow in order with its own dark, plus who it gets work from and hands work to.</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -9673,7 +9674,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
@@ -9684,7 +9685,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 2b395c6.</t>
+          <t>Done 2026-10-29 - f65c54a.</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -9696,12 +9697,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>NF-10.14</t>
+          <t>NF-10.13</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
+          <t>frontend/src/pages/onboarding/OsMap.jsx, walkthrough/scenes.jsx</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -9711,27 +9712,27 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>The first-week tour, inside the real desktop app</t>
+          <t>Teams and the cycle sat off their circles; the ring ran through words</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
+          <t>An entrance's inline transform (and framer's own) replaced the centring classes, so each node sat half its size down and right of its point. Placing moved to a plain wrapper with the icon centre on the ring; names ride on white cards clear of the line.</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I140" s="11" t="inlineStr">
@@ -9742,7 +9743,7 @@
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
+          <t>Done 2026-10-30 - 2b395c6.</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -9754,12 +9755,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>NF-10.15</t>
+          <t>NF-10.14</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx, lib/firstTour.js, pages/onboarding/walkthrough/{journey.js,scenes.jsx,Player.jsx}, components/Layout.js (mount + "Take the tour")</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -9769,17 +9770,17 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>The tour pointed at the wrong things and drew its own UI</t>
+          <t>The first-week tour, inside the real desktop app</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
+          <t>Pressing Enter keeps the company's script (filled from the draft). The app plays it once, after any welcome or Terms card: their company at a glance, then spotlights on real elements - the Desk board, its numbers, the Dex well, the first workflow column, the routines bar, the My Work list, the approvals area, the Dex pill, the nav - each with a small preview in the note card filled from their company (their rule waiting, their words and the tasks Dex drafts, an order walking their workflow, a checklist ticking, the approval, Dex answering). The cycle closes it; "Start using DecisionOS" leaves the live app. Mocks only: nothing read from or written to the server. Replay from the account menu. Desktop only; the phone keeps its short walkthrough ending at the guide.</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -9789,7 +9790,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
@@ -9800,7 +9801,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c.</t>
+          <t>Done 2026-10-30 - 01aa146, 0f1438c. All 11 steps checked at full size on the real pages. Superseded on the way: a mock-up video walkthrough on the summary (0683789, 5e821f7, ebb52b9, a489dc9), removed.</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -9812,12 +9813,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>NF-10.16</t>
+          <t>NF-10.15</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
+          <t>frontend/src/components/tour/FirstWeekTour.jsx</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -9827,17 +9828,17 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Desktop opens the phone's task view</t>
+          <t>The tour pointed at the wrong things and drew its own UI</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
+          <t>Founder: "many parts showed something else, or invented UI instead of the actual page". The Decide step looked for an element the desktop Desk does not have and fell back to the whole page, covering it with a mock; the Dex step hit a hidden duplicate test id. Targets are now measured on the real pages (desk-insight, header-scoped nav-brain), nothing is drawn over the page, and a step whose element never appears is passed over.</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -9858,7 +9859,7 @@
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
+          <t>Done 2026-10-30 - 0f1438c.</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
@@ -9870,12 +9871,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>NF-10.17</t>
+          <t>NF-10.16</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
+          <t>frontend/src/pages/MyWork.js (mobileTaskView at every width, LEGACY_TASK_BODY off)</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -9890,17 +9891,17 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Desktop list cards are the phone's task card</t>
+          <t>Desktop opens the phone's task view</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
+          <t>The task drawer on desktop holds the phone's view: hero, AI Execution Guide, Steps / Documents / Activity / Notes, status at the top of Activity, the Complete / Update slider; desktop keeps manual progress % and the workflow stage on its chip. The checklist drafts itself on open at every width. The old desktop body is kept behind a flag for a week, then deleted.</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -9916,7 +9917,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-29 - 56e7d44.</t>
+          <t>Done 2026-10-29 - 56e7d44. Tests: My Work suite (243 passed).</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -9928,12 +9929,12 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>NF-10.18</t>
+          <t>NF-10.17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
+          <t>frontend/src/pages/MyWork.js (TaskCell), pages/mywork/WorkDeck.jsx (TaskSummaryCard bulk tick)</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -9943,17 +9944,17 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>A proof photo tapped on the phone opened nothing</t>
+          <t>Desktop list cards are the phone's task card</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
+          <t>In the High / Medium / Low columns and the grid, each task is the phone's card (status, due, title, people, numbered steps, Next action, Mark as Doing / Open task) and opens the same drawer; desktop's bulk-select tick comes along.</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -9963,7 +9964,7 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I144" s="11" t="inlineStr">
@@ -9986,12 +9987,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>NF-10.19</t>
+          <t>NF-10.18</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
+          <t>frontend/src/pages/MyWork.js (lightboxDialog), pages/mywork/TaskNotes.jsx</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -10001,17 +10002,17 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>A camera button beside attach</t>
+          <t>A proof photo tapped on the phone opened nothing</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
+          <t>The full-size photo dialog lived only in the desktop body, while the phone's attachment blocks set it. It is the view's own now, at every width. Notes say "this device", not "this phone".</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -10032,7 +10033,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
+          <t>Done 2026-10-29 - 56e7d44.</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -10044,12 +10045,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>NF-10.20</t>
+          <t>NF-10.19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, DexCapturePopup.jsx, components/requests/NewRequestDialog.jsx</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -10059,22 +10060,22 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>The phone froze grey on Decide's "What you said"</t>
+          <t>A camera button beside attach</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
+          <t>Founder: "when I click attach in Dex Decide it only shows documents - I want a camera button for live shooting". Decide's "What you said" card and the new-request dialog get a camera button beside the paperclip that opens the camera straight away (capture="environment"), same upload. Ask's chat and the task view already had one.</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -10090,7 +10091,7 @@
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
+          <t>Done 2026-10-30 - 0f1438c. In the 1.1.0 release build; not pressed in the browser pane (camera blocked there).</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -10102,12 +10103,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>NF-10.21</t>
+          <t>NF-10.20</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
+          <t>frontend/src/index.css (.ui-scale [data-dialog-overlay][data-state=closed])</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -10117,17 +10118,17 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>DecisionOS 1.1.0 release build</t>
+          <t>The phone froze grey on Decide's "What you said"</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
+          <t>Read off the device over the WebView debugger: Decide's card was open with a dialog scrim - open, taking taps - after it in &lt;body&gt; at the same z-50. The card had closed and reopened inside its wrapper's 210ms exit hold: the wrapper was reused in place while the scrim, unmounted at once on a phone, was mounted again at the end of &lt;body&gt; and painted over the card. The scrim is held for the same 210ms, so a quick close-and-reopen keeps it under its card.</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -10148,7 +10149,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30.</t>
+          <t>Done 2026-10-30 - 8c9ae5f. Root cause confirmed on device; the fix not yet seen under the same timing.</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -10160,12 +10161,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>NF-10.22</t>
+          <t>NF-10.21</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
+          <t>android: release build (keystore.properties + release.keystore, gitignored)</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -10175,22 +10176,22 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Decide and Ask show a translation, not the words spoken</t>
+          <t>DecisionOS 1.1.0 release build</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
+          <t>Signed release APK, version 1.1.0 (code 11), pointing at Railway, carrying everything above. Installed on the test phone after the debug build was uninstalled (debug and release keys differ). File: Claude outputs/releases/DecisionOS-1.1.0-release-railway-2026-10-30.apk (not committed).</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -10200,13 +10201,13 @@
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Waiting on the founder's call (2026-10-30).</t>
+          <t>Done 2026-10-30.</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
@@ -10218,12 +10219,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>NF-10.23</t>
+          <t>NF-10.22</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Railway backend</t>
+          <t>backend: integrations/stt.py (SARVAM_STT_MODEL saaras:v3, mode=translate)</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -10238,12 +10239,12 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Deploy the backend for the interview's live pieces</t>
+          <t>Decide and Ask show a translation, not the words spoken</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
+          <t>Founder saw a transcript that was not what he said. Not demo data: speech goes to Sarvam saaras:v3 in translate mode with the language auto-detected, so any language comes back as an English translation (and a noisy clip can come back invented). Founder to decide: keep translation, or switch Decide and Ask to word-for-word transcription.</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -10264,7 +10265,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Needs a deploy go-ahead.</t>
+          <t>Waiting on the founder's call (2026-10-30).</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -10276,12 +10277,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>NF-10.24</t>
+          <t>NF-10.23</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
+          <t>Railway backend</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -10291,17 +10292,17 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Desktop parity</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Desktop task card: one steps bar, no Next action or buttons</t>
+          <t>Deploy the backend for the interview's live pieces</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
+          <t>NF-10.6 ships in backend/services/ai/onboarding.py and routers/signup.py; the phone and live web need it deployed to show pieces landing during the interview. Everything else in Sprint 10 works against the current server.</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -10316,30 +10317,30 @@
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
+          <t>Needs a deploy go-ahead.</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30</t>
+          <t>Founder 2026-10-29/30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>NF-10.25</t>
+          <t>NF-10.24</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (TaskSummaryCard desk, StepProgress), pages/MyWork.js (TaskCell)</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -10349,22 +10350,22 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Desktop parity</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Desktop task cards all the same shape</t>
+          <t>Desktop task card: one steps bar, no Next action or buttons</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
+          <t>Founder (screenshot, three areas marked): on desktop the Next action box, Mark as Doing and Open task are gone - a click anywhere on the card opens the task; the numbered step row is one bar, 'Steps n of m', that fills to match and opens the task on Steps. The tick box still only selects. The phone card is unchanged.</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -10380,7 +10381,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Checked on the local test company: card body, steps bar and tick box each do their own thing.</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -10392,12 +10393,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>NF-10.26</t>
+          <t>NF-10.25</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -10412,12 +10413,12 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Priority as a glow along the card's bottom edge</t>
+          <t>Desktop task cards all the same shape</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
+          <t>Founder: cards uneven inside. Title and description at most two lines each, ending in '...' (full text on hover), fonts unchanged (20px / 15px); the description sits in a light glass well and 'No description' holds its place; the title, the header and the people row keep their room whether filled or not, so every card is the same height (383px across all 22 local cards) and every row lines up.</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -10438,7 +10439,7 @@
       <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L152" s="4" t="inlineStr">
@@ -10450,12 +10451,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>NF-10.27</t>
+          <t>NF-10.26</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
+          <t>frontend/src/pages/mywork/WorkDeck.jsx (PRIO_GLOW)</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -10465,27 +10466,27 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Desktop My Work becomes the Workspace</t>
+          <t>Priority as a glow along the card's bottom edge</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
+          <t>The old desktop card's stripe came back beside the title (then shortened to the title alone), but users found it unconvincing. Priority is now a soft glow along the inside of the card's bottom edge with a 1px line - red high, orange medium, grey low - made subtler on the founder's second look. Screen readers still hear the priority.</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
@@ -10496,7 +10497,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Iterations: stripe beside title and people -&gt; title only -&gt; bottom glow -&gt; subtler glow, thinner line.</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -10508,12 +10509,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>NF-10.28</t>
+          <t>NF-10.27</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (StatusFence, WorkTree), pages/MyWork.js (desktop header, one scroll)</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -10528,12 +10529,12 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>The owner's team board</t>
+          <t>Desktop My Work becomes the Workspace</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
+          <t>Client ask via the founder. Title 'Workspace'. The Status dropdown is a fence of count tiles (All open, To do, Doing, Waiting on someone, Needs approval, Overdue, Due today, No due date, Done - '500+' where the list holds only the newest 500 finished). The switcher is a work tree: the reader's own face in the middle, My Tasks, Asked by me, All Tasks (under the owner), My requests and Approvals on branches, the path in use drawn in ink. Smart priority and + New in the header; the fence and tree scroll away with the list. Desktop only; the Approvals page keeps its room; same ?view= addresses and testids.</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -10554,7 +10555,7 @@
       <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 - 4a2edc2.</t>
+          <t>Done 2026-10-30 - 4a2edc2. Walked as the owner (all views) and a member (own face, three branches); phone unchanged. Tests: tests/test_the_workspace_puts_the_team_first.py.</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
@@ -10566,40 +10567,42 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>NF-11.1</t>
+          <t>NF-10.28</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py Company.managers / level / ladder</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="n">
-        <v>11</v>
+          <t>frontend/src/pages/mywork/WorkspaceHub.jsx (TeamBoard, personStats, PersonBar), pages/MyWork.js (boardOn, goBoard, deptBar)</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Team</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>The team's managers, from Reports to</t>
+          <t>The owner's team board</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
+          <t>The owner's desktop opens on All Tasks as a ranked board: one card per person with Open (and how many wait on someone), Overdue, Done in 30 days, On time (dated work finished by its date), a Behind / On track / Free badge, a bar of all they were given that is finished, and when work last reached them and they last finished. Rank by Delivered, On time or Overdue. The client's reference counted Total / Completed / In progress / Pending, which overlap, with a bar that did not follow from them - replaced. Team totals count tasks once. Work held by a team or nobody gets its own way in. A person opens their cards under 'Team'; Department is a segment bar here only. Counted from the list the page holds - no new endpoint.</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I155" s="11" t="inlineStr">
@@ -10607,10 +10610,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J155" s="4" t="n"/>
+      <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
+          <t>Done 2026-10-30 - 4a2edc2.</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -10622,12 +10625,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
+          <t>services/task_pickup.py Company.managers / level / ladder</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
@@ -10635,17 +10638,17 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Decisions / Work</t>
+          <t>Decisions / Team</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Work nobody has goes to the team's queue</t>
+          <t>The team's managers, from Reports to</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
+          <t>A team's managers are whoever in it reports straight to an owner (its head) or has people reporting to them (Team &gt; Reports to); their level is how far they are from the owner. No manager setting (founder: later, once a client confirms). No managers: their steps go to the owner. Two at a level: both asked.</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -10655,7 +10658,7 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I156" s="11" t="inlineStr">
@@ -10663,14 +10666,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>NF-11.1</t>
-        </is>
-      </c>
+      <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: heads, two heads, Priya (reports to Ravi) not a head.</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
@@ -10682,12 +10681,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>NF-11.3</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
+          <t>services/task_pickup.py route/place/announce; voice.build_proposal; decision_flow.approve_decision_flow; workflow_engine.on_stage_enter; routers/tasks.py create_task, reassign; routers/decisions.py add_decision_task; services/deprovisioning.py</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
@@ -10695,17 +10694,17 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Decisions / Work</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Take it</t>
+          <t>Work nobody has goes to the team's queue</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
+          <t>Founder: a decision makes its tasks and they land with nobody; and 'I can't say we should assign to the least number of tasks'. Now, with no person named: the team's one person; else the team's QUEUE (everyone in it sees it); high priority -&gt; the head is asked (still queued); no team or nobody in it -&gt; the owner is asked. Never by load. Same for decisions, workflow stages, New Task for a team, a task added to a decision, a task moved to another team, and someone leaving with work handed to nobody (it keeps its team now). One message per person per team.</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -10715,7 +10714,7 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr">
@@ -10725,12 +10724,12 @@
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.1</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: every kind of team, approval end to end (one message each, approver not told), New Task, stage, leaver, added task. Dev data: 93 of 148 open decision/workflow tasks had nobody.</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -10742,12 +10741,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.3</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
+          <t>POST /tasks/{id}/take; services/task_pickup.take; MyWork.js TakeItBar</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
@@ -10755,17 +10754,17 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>It keeps asking until someone has it</t>
+          <t>Take it</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
+          <t>Anyone in the team (or an owner) takes a queued task in one tap from the My Work drawer. One write wins; the second gets 'Priya Nair already has this task.' The head hears who took it; the decision's timeline says so.</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -10790,7 +10789,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: team only, owner for no team, finished, two at once -&gt; one wins.</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
@@ -10802,12 +10801,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>NF-11.5</t>
+          <t>NF-11.4</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
+          <t>services/task_pickup.warn_unpicked (follow-up sweep); Settings &gt; Deadlines &gt; Work nobody has</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
@@ -10815,17 +10814,17 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Work / Notifications</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Needs a person on the Desk</t>
+          <t>It keeps asking until someone has it</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
+          <t>While a task has nobody it is asked about again, one notification per person per step however many tasks; step length is the company's own (Settings &gt; Deadlines &gt; Work nobody has). Who each step asks: NF-11.8.</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -10850,7 +10849,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: each step, one message for three tasks, no repeats, no head, own days.</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -10862,12 +10861,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>NF-11.6</t>
+          <t>NF-11.5</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
+          <t>GET /tasks/needs-person; pages/desk/NeedsPersonSheet.jsx; Desk.js card; lib/notif.js</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
@@ -10875,27 +10874,27 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>The review says where each task will go</t>
+          <t>Needs a person on the Desk</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
+          <t>Owners see every task with nobody, a head their own team's, oldest first: where it waits, how long, assign on the spot (team first) or Take it. A head may assign from their own queue. 'Assign it' notifications open the list.</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr">
@@ -10910,7 +10909,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: owner / head / member scopes, head assigns, others refused.</t>
         </is>
       </c>
       <c r="L160" s="4" t="inlineStr">
@@ -10922,12 +10921,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>NF-11.7</t>
+          <t>NF-11.6</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
+          <t>services/enrich.py goes_to; DecisionDialog.js; DexReview.jsx; decision_flow.task_assigned_line</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
@@ -10935,27 +10934,27 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Decisions</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Older work joins its queue; tests and browser check</t>
+          <t>The review says where each task will go</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
+          <t>Before approving, each task nobody is named for says where it will wait ('Sales queue - anyone in Sales can take it', 'Karthik assigns it - high priority, Sales head', 'The owner assigns it - no team named'); the timeline after.</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr">
@@ -10970,7 +10969,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: labels and timeline lines.</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -10982,12 +10981,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>NF-11.8</t>
+          <t>NF-11.7</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
+          <t>tests/test_work_nobody_has_finds_its_person.py; docs/WORK_NOBODY_HAS.md</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
@@ -10995,17 +10994,17 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Work / Notifications</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Reminders climb the reporting tree, one level a day</t>
+          <t>Older work joins its queue; tests and browser check</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
+          <t>Tasks that already had nobody join their queue quietly; their days start then (the July backlog does not hit the owner at once) and nothing is handed out silently. Who counts as here is judged per person (NF-4.16).</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -11025,12 +11024,12 @@
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>NF-11.4</t>
+          <t>NF-11.2</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
+          <t>Done 2026-10-30 (feature). Browser, demo workspace (scratch DB) with two extra Sales people: review labels; approval placed 4 tasks (queue / head / owner / Amit the only one) and told the right people; Desk card + sheet, assigned to Divya; Priya took from the queue in My Work, head told, second take 409.</t>
         </is>
       </c>
       <c r="L162" s="4" t="inlineStr">
@@ -11042,12 +11041,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>NF-11.9</t>
+          <t>NF-11.8</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
+          <t>services/task_pickup.py steps_for, warn_unpicked, needs_person, take; routers/tasks.py _heads_its_queue</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
@@ -11055,17 +11054,17 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Finance / Work</t>
+          <t>Work / Notifications</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Finance follow-ups join the Finance queue</t>
+          <t>Reminders climb the reporting tree, one level a day</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
+          <t>Founder 2026-10-30: 'rather than nudging the owner with a lot of notifications' - the owner has 5 departments, each with 2 reporting, who have their own people. A task with nobody now climbs its team's reporting tree one level a day: the deepest managers first (team leads), then the next level (the head), the owner last. High priority starts at once (team leads told when it is made). Work already waiting on the owner is not chased again - it stays on the Desk. Only the step now due is asked. Every manager of the team sees and may assign its queue. Settings: one step length (pickup_step_days) instead of head/owner days.</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -11075,7 +11074,7 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr">
@@ -11085,12 +11084,12 @@
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>NF-11.2</t>
+          <t>NF-11.4</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: three-level Sales (leads day 1, head day 2, owner day 3, then nothing), high priority from the leads at once, any manager sees/assigns, chain that never reaches the owner. Browser: high priority went to Divya (level 2), not Karthik.</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -11102,30 +11101,30 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>NF-12.1</t>
+          <t>NF-11.9</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>services/parties.py (new); services/ingestion.py</t>
+          <t>services/finance_signals.py _finance_assignee, run_finance_actions</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>CRM / Matching</t>
+          <t>Finance / Work</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>One matcher decides who a customer or supplier is</t>
+          <t>Finance follow-ups join the Finance queue</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Dex, New Task, the old-data review and Finance's bill import ask services/parties the same question, so a party is never made twice. It drops Pvt/Ltd/M/s, matches whole identifying words ('Toyota' = Toyota Kirloskar Pvt Ltd) and close spellings ('Kumar Exprts'); two possible records -&gt; 'Which one?', never a guess; one of the team, our own company or generic words ('the exporters') are never a party. It never writes.</t>
+          <t>Founder 2026-10-30: the automatic Finance follow-ups (chase an overdue invoice, pay a bill) went to whoever in Finance had the fewest tasks. Now they follow the same rule: Finance's one person, else the Finance queue (a chase is high priority, so Finance's nearest managers are asked at once), no Finance team -&gt; the owner; then the ladder.</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -11135,7 +11134,7 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I164" s="11" t="inlineStr">
@@ -11143,27 +11142,31 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J164" s="4" t="n"/>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>NF-11.2</t>
+        </is>
+      </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): variants, Which one?, kind settles it, team/own/generic guards, close spelling, whole-name scan.</t>
+          <t>Done 2026-10-30 (feature). test_work_nobody_has_finds_its_person.py: Finance queue + manager asked, a team of one, no Finance team -&gt; owner.</t>
         </is>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>Founder 2026-10-31</t>
+          <t>Founder 2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>NF-12.2</t>
+          <t>NF-12.1</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>prompts/extraction.py 1.5; services/voice.build_proposal</t>
+          <t>services/parties.py (new); services/ingestion.py</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
@@ -11171,17 +11174,17 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Decision Desk / Dex</t>
+          <t>CRM / Matching</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Dex names who each task, meeting and workflow is about</t>
+          <t>One matcher decides who a customer or supplier is</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Extraction 1.5 asks each task for party, party_kind (customer, dealer, supplier, prospect) and party_person, meetings for their party, workflow events for the counterparty's kind. A task Dex gave no party is scanned for a CRM name in its own words; a task tied to a workflow card takes the card's party.</t>
+          <t>Dex, New Task, the old-data review and Finance's bill import ask services/parties the same question, so a party is never made twice. It drops Pvt/Ltd/M/s, matches whole identifying words ('Toyota' = Toyota Kirloskar Pvt Ltd) and close spellings ('Kumar Exprts'); two possible records -&gt; 'Which one?', never a guess; one of the team, our own company or generic words ('the exporters') are never a party. It never writes.</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -11202,7 +11205,7 @@
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): linked, Which one?, new prospect with its person, a name in the title, 'tell Ravi' stays unlinked.</t>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): variants, Which one?, kind settles it, team/own/generic guards, close spelling, whole-name scan.</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -11214,12 +11217,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>NF-12.3</t>
+          <t>NF-12.2</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>components/party/* (new); DecisionDialog.js; pages/desk/DexReview.jsx; PATCH /decisions/{id}/proposal/party</t>
+          <t>prompts/extraction.py 1.5; services/voice.build_proposal</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
@@ -11227,17 +11230,17 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Decision Desk / Review</t>
+          <t>Decision Desk / Dex</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>The review shows the party and every guess can be changed</t>
+          <t>Dex names who each task, meeting and workflow is about</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>A chip per item: 'Kumar Exports · Customer' (with 'matched from Toyota'), 'New: ... · details needed', 'Which Kumar?', '2 customers named'. The party dialog: pick the record, add as new, change the kind, keep or drop the person at the firm, split a task naming several into one each, or 'Not a customer or supplier'. One answer applies to every item naming that party. Approving with a question open asks first: pick now, or approve and link later.</t>
+          <t>Extraction 1.5 asks each task for party, party_kind (customer, dealer, supplier, prospect) and party_person, meetings for their party, workflow events for the counterparty's kind. A task Dex gave no party is scanned for a CRM name in its own words; a task tied to a workflow card takes the card's party.</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -11247,7 +11250,7 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I166" s="11" t="inlineStr">
@@ -11258,7 +11261,7 @@
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25). Browser walk on the scratch DB: Which Kumar? picked, split into 2, kind -&gt; Dealer, approve.</t>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25): linked, Which one?, new prospect with its person, a name in the title, 'tell Ravi' stays unlinked.</t>
         </is>
       </c>
       <c r="L166" s="4" t="inlineStr">
@@ -11270,12 +11273,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>NF-12.4</t>
+          <t>NF-12.3</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>services/parties.settle; services/voice.materialize_proposal; services/decision_flow</t>
+          <t>components/party/* (new); DecisionDialog.js; pages/desk/DexReview.jsx; PATCH /decisions/{id}/proposal/party</t>
         </is>
       </c>
       <c r="C167" s="4" t="n">
@@ -11283,17 +11286,17 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Decision Desk / CRM</t>
+          <t>Decision Desk / Review</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Approval links everything; a new party is one Needs-details record</t>
+          <t>The review shows the party and every guess can be changed</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>On approval the tasks, meetings, workflow cards and the decision (contact_ids) get the CRM record. A party nobody had becomes ONE record marked Needs details, with the person named there and the decision it came from; found again first, so a second approval links. Nothing is created on reject; an open question is left unlinked for the review. The timeline says 'Added to CRM - details needed: ...'.</t>
+          <t>A chip per item: 'Kumar Exports · Customer' (with 'matched from Toyota'), 'New: ... · details needed', 'Which Kumar?', '2 customers named'. The party dialog: pick the record, add as new, change the kind, keep or drop the person at the firm, split a task naming several into one each, or 'Not a customer or supplier'. One answer applies to every item naming that party. Approving with a question open asks first: pick now, or approve and link later.</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -11303,7 +11306,7 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I167" s="11" t="inlineStr">
@@ -11314,7 +11317,7 @@
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); scratch DB: 5 tasks linked, Nippon Audiotronix made once (dealer, Sajith).</t>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25). Browser walk on the scratch DB: Which Kumar? picked, split into 2, kind -&gt; Dealer, approve.</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -11326,12 +11329,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>NF-12.5</t>
+          <t>NF-12.4</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>routers/contacts (needs-details, list filter, phone clears it); POST /tasks/{id}/party-details; NeedsDetailsCard; PartyDetailsPrompt; CRM.js</t>
+          <t>services/parties.settle; services/voice.materialize_proposal; services/decision_flow</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
@@ -11339,17 +11342,17 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>CRM / Follow-up</t>
+          <t>Decision Desk / CRM</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Missing details are followed up</t>
+          <t>Approval links everything; a new party is one Needs-details record</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Desk card '3 new customers/suppliers need details' (people with that side of CRM). When a task about one is done, the doer is asked for phone, GST and address (blank fields only, no CRM access needed; 'Later' or 'Nothing to add'). CRM has a Needs details filter that opens on the tab holding them. Saving a phone clears the flag.</t>
+          <t>On approval the tasks, meetings, workflow cards and the decision (contact_ids) get the CRM record. A party nobody had becomes ONE record marked Needs details, with the person named there and the decision it came from; found again first, so a second approval links. Nothing is created on reject; an open question is left unlinked for the review. The timeline says 'Added to CRM - details needed: ...'.</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -11370,7 +11373,7 @@
       <c r="J168" s="4" t="n"/>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); browser: card -&gt; CRM filter (Partners tab), finish -&gt; prompt -&gt; saved, flag cleared.</t>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); scratch DB: 5 tasks linked, Nippon Audiotronix made once (dealer, Sajith).</t>
         </is>
       </c>
       <c r="L168" s="4" t="inlineStr">
@@ -11382,12 +11385,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>NF-12.6</t>
+          <t>NF-12.5</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>pages/Tasks.js NewTaskDialog; pages/MyWork.js PartyLine; routers/tasks (_task_party); GET /parties/search</t>
+          <t>routers/contacts (needs-details, list filter, phone clears it); POST /tasks/{id}/party-details; NeedsDetailsCard; PartyDetailsPrompt; CRM.js</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
@@ -11395,22 +11398,22 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>CRM / Follow-up</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>New Task and the task drawer carry a Customer / supplier field</t>
+          <t>Missing details are followed up</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Search CRM (name and kind only, so anyone who makes work can link it) or add new right there with its kind. The title is read as it is typed: 'Send the quote to Toyota Kirloskar' offers it in one tap. The drawer shows the chip and can change or remove it; only people with a say on the task, refused before any record is made.</t>
+          <t>Desk card '3 new customers/suppliers need details' (people with that side of CRM). When a task about one is done, the doer is asked for phone, GST and address (blank fields only, no CRM access needed; 'Later' or 'Nothing to add'). CRM has a Needs details filter that opens on the tab holding them. Saving a phone clears the flag.</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -11426,7 +11429,7 @@
       <c r="J169" s="4" t="n"/>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); browser: title suggestion linked Toyota Kirloskar Pvt Ltd.</t>
+          <t>Done 2026-10-31 (feature). tests/test_everything_links_to_crm.py (25); browser: card -&gt; CRM filter (Partners tab), finish -&gt; prompt -&gt; saved, flag cleared.</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -11438,12 +11441,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>NF-12.7</t>
+          <t>NF-12.6</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>routers/finance.contact_profile; routers/crm activity; ContactProfile.js; ContactProfileMobile.jsx; PartyChip</t>
+          <t>pages/Tasks.js NewTaskDialog; pages/MyWork.js PartyLine; routers/tasks (_task_party); GET /parties/search</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
@@ -11451,22 +11454,22 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>CRM / Contact page</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>The customer/supplier page reads links, opens for CRM, money stays Finance</t>
+          <t>New Task and the task drawer carry a Customer / supplier field</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>It found tasks and decisions by searching titles for the name ('Ravi Traders' showed the employee Ravi's work) and opened only with Finance. Now: linked tasks, decisions, meetings and workflows, for anyone with that side of CRM; invoices, payments, bills, totals, prices and the AI score only with Finance ('Money is visible to Finance'). Chips on tasks and decisions open it.</t>
+          <t>Search CRM (name and kind only, so anyone who makes work can link it) or add new right there with its kind. The title is read as it is typed: 'Send the quote to Toyota Kirloskar' offers it in one tap. The drawer shows the chip and can change 